--- a/downloads/CardShow_Inventory_Template.xlsx
+++ b/downloads/CardShow_Inventory_Template.xlsx
@@ -293,7 +293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -330,6 +330,10 @@
       <bottom style="thin">
         <color rgb="FFD1D5DB"/>
       </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -798,16 +802,18 @@
     <col width="16" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
     <col width="22" bestFit="1" customWidth="1" style="35" min="8" max="8"/>
     <col width="24" customWidth="1" style="35" min="9" max="9"/>
-    <col width="12.5" customWidth="1" style="35" min="10" max="10"/>
-    <col width="16" bestFit="1" customWidth="1" style="35" min="11" max="11"/>
-    <col width="16" customWidth="1" style="35" min="12" max="12"/>
-    <col width="18" customWidth="1" style="35" min="13" max="14"/>
-    <col width="15.5" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" style="35" min="15" max="15"/>
-    <col width="20" customWidth="1" style="35" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" style="35" min="10" max="10"/>
+    <col width="22" bestFit="1" customWidth="1" style="35" min="11" max="11"/>
+    <col width="12.5" customWidth="1" style="35" min="12" max="12"/>
+    <col width="16" customWidth="1" style="35" min="13" max="14"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" style="35" min="15" max="15"/>
+    <col width="15.5" customWidth="1" style="35" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
@@ -858,56 +864,64 @@
       </c>
       <c r="J1" s="37" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="K1" s="37" t="inlineStr">
+        <is>
+          <t>Subcategory</t>
+        </is>
+      </c>
+      <c r="L1" s="37" t="inlineStr">
+        <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="K1" s="37" t="inlineStr">
+      <c r="M1" s="37" t="inlineStr">
         <is>
           <t>Grader</t>
         </is>
       </c>
-      <c r="L1" s="37" t="inlineStr">
+      <c r="N1" s="37" t="inlineStr">
         <is>
           <t>Cert #</t>
         </is>
       </c>
-      <c r="M1" s="37" t="inlineStr">
+      <c r="O1" s="37" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="N1" s="37" t="inlineStr">
+      <c r="P1" s="37" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="O1" s="37" t="inlineStr">
+      <c r="Q1" s="37" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="P1" s="37" t="inlineStr">
+      <c r="R1" s="37" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="Q1" s="37" t="inlineStr">
+      <c r="S1" s="37" t="inlineStr">
         <is>
           <t>Seller</t>
         </is>
       </c>
-      <c r="R1" s="37" t="inlineStr">
+      <c r="T1" s="37" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="S1" s="37" t="inlineStr">
+      <c r="U1" s="37" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="T1" s="38" t="n"/>
-      <c r="U1" s="38" t="n"/>
       <c r="V1" s="38" t="n"/>
       <c r="W1" s="38" t="n"/>
     </row>
@@ -959,56 +973,64 @@
       </c>
       <c r="J2" s="39" t="inlineStr">
         <is>
+          <t>Sports, TCG, or Non-Sport</t>
+        </is>
+      </c>
+      <c r="K2" s="39" t="inlineStr">
+        <is>
+          <t>Sport/game/franchise — e.g. Baseball, Pokémon, Marvel (see Column Guide for the full list)</t>
+        </is>
+      </c>
+      <c r="L2" s="39" t="inlineStr">
+        <is>
           <t>Numeric: 9 · 9.5 · 10  (blank = raw)</t>
         </is>
       </c>
-      <c r="K2" s="39" t="inlineStr">
+      <c r="M2" s="39" t="inlineStr">
         <is>
           <t>PSA · BGS · CGC · SGC · TAG · HGA · GMA · Arena Club  (blank = raw, or type any other grading company)</t>
         </is>
       </c>
-      <c r="L2" s="39" t="inlineStr">
+      <c r="N2" s="39" t="inlineStr">
         <is>
           <t>Slab cert/serial number from the label</t>
         </is>
       </c>
-      <c r="M2" s="39" t="inlineStr">
+      <c r="O2" s="39" t="inlineStr">
         <is>
           <t>Near Mint · Lightly Played · Moderately Played…</t>
         </is>
       </c>
-      <c r="N2" s="39" t="inlineStr">
+      <c r="P2" s="39" t="inlineStr">
         <is>
           <t>Asking price — numbers only, no $ sign</t>
         </is>
       </c>
-      <c r="O2" s="39" t="inlineStr">
+      <c r="Q2" s="39" t="inlineStr">
         <is>
           <t>Available (default) · Sold · On Hold</t>
         </is>
       </c>
-      <c r="P2" s="39" t="inlineStr">
+      <c r="R2" s="39" t="inlineStr">
         <is>
           <t>Box 3 · Binder A — private, not shown to buyers</t>
         </is>
       </c>
-      <c r="Q2" s="39" t="inlineStr">
+      <c r="S2" s="39" t="inlineStr">
         <is>
           <t>Your handle — auto-filled, can leave blank</t>
         </is>
       </c>
-      <c r="R2" s="39" t="inlineStr">
+      <c r="T2" s="39" t="inlineStr">
         <is>
           <t>Optional public CDN URL for card image</t>
         </is>
       </c>
-      <c r="S2" s="39" t="inlineStr">
+      <c r="U2" s="39" t="inlineStr">
         <is>
           <t>Internal notes — not shown to buyers</t>
         </is>
       </c>
-      <c r="T2" s="38" t="n"/>
-      <c r="U2" s="38" t="n"/>
       <c r="V2" s="38" t="n"/>
       <c r="W2" s="38" t="n"/>
     </row>
@@ -1048,36 +1070,44 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="J3" s="43" t="n">
+      <c r="J3" s="40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="K3" s="40" t="inlineStr">
+        <is>
+          <t>Baseball</t>
+        </is>
+      </c>
+      <c r="L3" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="K3" s="40" t="inlineStr">
+      <c r="M3" s="40" t="inlineStr">
         <is>
           <t>PSA</t>
         </is>
       </c>
-      <c r="L3" s="40" t="n">
+      <c r="N3" s="40" t="n">
         <v>100039513</v>
       </c>
-      <c r="M3" s="40" t="n"/>
-      <c r="N3" s="44" t="n">
+      <c r="O3" s="40" t="n"/>
+      <c r="P3" s="44" t="n">
         <v>148</v>
       </c>
-      <c r="O3" s="40" t="inlineStr">
+      <c r="Q3" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P3" s="40" t="inlineStr">
+      <c r="R3" s="40" t="inlineStr">
         <is>
           <t>Box 1</t>
         </is>
       </c>
-      <c r="Q3" s="40" t="n"/>
-      <c r="R3" s="40" t="n"/>
       <c r="S3" s="40" t="n"/>
-      <c r="T3" s="38" t="n"/>
-      <c r="U3" s="38" t="n"/>
+      <c r="T3" s="40" t="n"/>
+      <c r="U3" s="40" t="n"/>
       <c r="V3" s="38" t="n"/>
       <c r="W3" s="38" t="n"/>
     </row>
@@ -1115,36 +1145,44 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="J4" s="43" t="n">
+      <c r="J4" s="40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="K4" s="40" t="inlineStr">
+        <is>
+          <t>Basketball</t>
+        </is>
+      </c>
+      <c r="L4" s="43" t="n">
         <v>9.5</v>
       </c>
-      <c r="K4" s="40" t="inlineStr">
+      <c r="M4" s="40" t="inlineStr">
         <is>
           <t>BGS</t>
         </is>
       </c>
-      <c r="L4" s="40" t="n">
+      <c r="N4" s="40" t="n">
         <v>55443322</v>
       </c>
-      <c r="M4" s="40" t="n"/>
-      <c r="N4" s="44" t="n">
+      <c r="O4" s="40" t="n"/>
+      <c r="P4" s="44" t="n">
         <v>320</v>
       </c>
-      <c r="O4" s="40" t="inlineStr">
+      <c r="Q4" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P4" s="40" t="inlineStr">
+      <c r="R4" s="40" t="inlineStr">
         <is>
           <t>Box 1</t>
         </is>
       </c>
-      <c r="Q4" s="40" t="n"/>
-      <c r="R4" s="40" t="n"/>
       <c r="S4" s="40" t="n"/>
-      <c r="T4" s="38" t="n"/>
-      <c r="U4" s="38" t="n"/>
+      <c r="T4" s="40" t="n"/>
+      <c r="U4" s="40" t="n"/>
       <c r="V4" s="38" t="n"/>
       <c r="W4" s="38" t="n"/>
     </row>
@@ -1182,32 +1220,40 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="J5" s="43" t="n"/>
-      <c r="K5" s="40" t="n"/>
-      <c r="L5" s="40" t="n"/>
-      <c r="M5" s="40" t="inlineStr">
+      <c r="J5" s="40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="K5" s="40" t="inlineStr">
+        <is>
+          <t>Basketball</t>
+        </is>
+      </c>
+      <c r="L5" s="43" t="n"/>
+      <c r="M5" s="40" t="n"/>
+      <c r="N5" s="40" t="n"/>
+      <c r="O5" s="40" t="inlineStr">
         <is>
           <t>Near Mint</t>
         </is>
       </c>
-      <c r="N5" s="44" t="n">
+      <c r="P5" s="44" t="n">
         <v>45</v>
       </c>
-      <c r="O5" s="40" t="inlineStr">
+      <c r="Q5" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P5" s="40" t="inlineStr">
+      <c r="R5" s="40" t="inlineStr">
         <is>
           <t>Binder A</t>
         </is>
       </c>
-      <c r="Q5" s="40" t="n"/>
-      <c r="R5" s="40" t="n"/>
       <c r="S5" s="40" t="n"/>
-      <c r="T5" s="38" t="n"/>
-      <c r="U5" s="38" t="n"/>
+      <c r="T5" s="40" t="n"/>
+      <c r="U5" s="40" t="n"/>
       <c r="V5" s="38" t="n"/>
       <c r="W5" s="38" t="n"/>
     </row>
@@ -1245,36 +1291,44 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="J6" s="43" t="n">
+      <c r="J6" s="40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="K6" s="40" t="inlineStr">
+        <is>
+          <t>Basketball</t>
+        </is>
+      </c>
+      <c r="L6" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="40" t="inlineStr">
+      <c r="M6" s="40" t="inlineStr">
         <is>
           <t>PSA</t>
         </is>
       </c>
-      <c r="L6" s="40" t="n">
+      <c r="N6" s="40" t="n">
         <v>77665544</v>
       </c>
-      <c r="M6" s="40" t="n"/>
-      <c r="N6" s="44" t="n">
+      <c r="O6" s="40" t="n"/>
+      <c r="P6" s="44" t="n">
         <v>18500</v>
       </c>
-      <c r="O6" s="40" t="inlineStr">
+      <c r="Q6" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P6" s="40" t="inlineStr">
+      <c r="R6" s="40" t="inlineStr">
         <is>
           <t>Case 1</t>
         </is>
       </c>
-      <c r="Q6" s="40" t="n"/>
-      <c r="R6" s="40" t="n"/>
       <c r="S6" s="40" t="n"/>
-      <c r="T6" s="38" t="n"/>
-      <c r="U6" s="38" t="n"/>
+      <c r="T6" s="40" t="n"/>
+      <c r="U6" s="40" t="n"/>
       <c r="V6" s="38" t="n"/>
       <c r="W6" s="38" t="n"/>
     </row>
@@ -1314,36 +1368,44 @@
         </is>
       </c>
       <c r="I7" s="40" t="n"/>
-      <c r="J7" s="43" t="n">
+      <c r="J7" s="40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="K7" s="40" t="inlineStr">
+        <is>
+          <t>Football</t>
+        </is>
+      </c>
+      <c r="L7" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="K7" s="40" t="inlineStr">
+      <c r="M7" s="40" t="inlineStr">
         <is>
           <t>PSA</t>
         </is>
       </c>
-      <c r="L7" s="40" t="n">
+      <c r="N7" s="40" t="n">
         <v>22334455</v>
       </c>
-      <c r="M7" s="40" t="n"/>
-      <c r="N7" s="44" t="n">
+      <c r="O7" s="40" t="n"/>
+      <c r="P7" s="44" t="n">
         <v>1800</v>
       </c>
-      <c r="O7" s="40" t="inlineStr">
+      <c r="Q7" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P7" s="40" t="inlineStr">
+      <c r="R7" s="40" t="inlineStr">
         <is>
           <t>Box 2</t>
         </is>
       </c>
-      <c r="Q7" s="40" t="n"/>
-      <c r="R7" s="40" t="n"/>
       <c r="S7" s="40" t="n"/>
-      <c r="T7" s="38" t="n"/>
-      <c r="U7" s="38" t="n"/>
+      <c r="T7" s="40" t="n"/>
+      <c r="U7" s="40" t="n"/>
       <c r="V7" s="38" t="n"/>
       <c r="W7" s="38" t="n"/>
     </row>
@@ -1379,36 +1441,44 @@
         </is>
       </c>
       <c r="I8" s="40" t="n"/>
-      <c r="J8" s="43" t="n">
+      <c r="J8" s="40" t="inlineStr">
+        <is>
+          <t>TCG</t>
+        </is>
+      </c>
+      <c r="K8" s="40" t="inlineStr">
+        <is>
+          <t>Pokémon</t>
+        </is>
+      </c>
+      <c r="L8" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="K8" s="40" t="inlineStr">
+      <c r="M8" s="40" t="inlineStr">
         <is>
           <t>PSA</t>
         </is>
       </c>
-      <c r="L8" s="40" t="n">
+      <c r="N8" s="40" t="n">
         <v>33221144</v>
       </c>
-      <c r="M8" s="40" t="n"/>
-      <c r="N8" s="44" t="n">
+      <c r="O8" s="40" t="n"/>
+      <c r="P8" s="44" t="n">
         <v>580</v>
       </c>
-      <c r="O8" s="40" t="inlineStr">
+      <c r="Q8" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P8" s="40" t="inlineStr">
+      <c r="R8" s="40" t="inlineStr">
         <is>
           <t>Box 3</t>
         </is>
       </c>
-      <c r="Q8" s="40" t="n"/>
-      <c r="R8" s="40" t="n"/>
       <c r="S8" s="40" t="n"/>
-      <c r="T8" s="38" t="n"/>
-      <c r="U8" s="38" t="n"/>
+      <c r="T8" s="40" t="n"/>
+      <c r="U8" s="40" t="n"/>
       <c r="V8" s="38" t="n"/>
       <c r="W8" s="38" t="n"/>
     </row>
@@ -1444,32 +1514,40 @@
         </is>
       </c>
       <c r="I9" s="40" t="n"/>
-      <c r="J9" s="43" t="n"/>
-      <c r="K9" s="40" t="n"/>
-      <c r="L9" s="40" t="n"/>
-      <c r="M9" s="40" t="inlineStr">
+      <c r="J9" s="40" t="inlineStr">
+        <is>
+          <t>TCG</t>
+        </is>
+      </c>
+      <c r="K9" s="40" t="inlineStr">
+        <is>
+          <t>Pokémon</t>
+        </is>
+      </c>
+      <c r="L9" s="43" t="n"/>
+      <c r="M9" s="40" t="n"/>
+      <c r="N9" s="40" t="n"/>
+      <c r="O9" s="40" t="inlineStr">
         <is>
           <t>Near Mint</t>
         </is>
       </c>
-      <c r="N9" s="44" t="n">
+      <c r="P9" s="44" t="n">
         <v>4800</v>
       </c>
-      <c r="O9" s="40" t="inlineStr">
+      <c r="Q9" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P9" s="40" t="inlineStr">
+      <c r="R9" s="40" t="inlineStr">
         <is>
           <t>Case 2</t>
         </is>
       </c>
-      <c r="Q9" s="40" t="n"/>
-      <c r="R9" s="40" t="n"/>
       <c r="S9" s="40" t="n"/>
-      <c r="T9" s="38" t="n"/>
-      <c r="U9" s="38" t="n"/>
+      <c r="T9" s="40" t="n"/>
+      <c r="U9" s="40" t="n"/>
       <c r="V9" s="38" t="n"/>
       <c r="W9" s="38" t="n"/>
     </row>
@@ -1505,36 +1583,44 @@
         </is>
       </c>
       <c r="I10" s="40" t="n"/>
-      <c r="J10" s="43" t="n">
+      <c r="J10" s="40" t="inlineStr">
+        <is>
+          <t>TCG</t>
+        </is>
+      </c>
+      <c r="K10" s="40" t="inlineStr">
+        <is>
+          <t>Pokémon</t>
+        </is>
+      </c>
+      <c r="L10" s="43" t="n">
         <v>9.5</v>
       </c>
-      <c r="K10" s="40" t="inlineStr">
+      <c r="M10" s="40" t="inlineStr">
         <is>
           <t>CGC</t>
         </is>
       </c>
-      <c r="L10" s="40" t="n">
+      <c r="N10" s="40" t="n">
         <v>44556677</v>
       </c>
-      <c r="M10" s="40" t="n"/>
-      <c r="N10" s="44" t="n">
+      <c r="O10" s="40" t="n"/>
+      <c r="P10" s="44" t="n">
         <v>1200</v>
       </c>
-      <c r="O10" s="40" t="inlineStr">
+      <c r="Q10" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P10" s="40" t="inlineStr">
+      <c r="R10" s="40" t="inlineStr">
         <is>
           <t>Box 3</t>
         </is>
       </c>
-      <c r="Q10" s="40" t="n"/>
-      <c r="R10" s="40" t="n"/>
       <c r="S10" s="40" t="n"/>
-      <c r="T10" s="38" t="n"/>
-      <c r="U10" s="38" t="n"/>
+      <c r="T10" s="40" t="n"/>
+      <c r="U10" s="40" t="n"/>
       <c r="V10" s="38" t="n"/>
       <c r="W10" s="38" t="n"/>
     </row>
@@ -1570,32 +1656,40 @@
         </is>
       </c>
       <c r="I11" s="40" t="n"/>
-      <c r="J11" s="43" t="n"/>
-      <c r="K11" s="40" t="n"/>
-      <c r="L11" s="40" t="n"/>
-      <c r="M11" s="40" t="inlineStr">
+      <c r="J11" s="40" t="inlineStr">
+        <is>
+          <t>TCG</t>
+        </is>
+      </c>
+      <c r="K11" s="40" t="inlineStr">
+        <is>
+          <t>Pokémon</t>
+        </is>
+      </c>
+      <c r="L11" s="43" t="n"/>
+      <c r="M11" s="40" t="n"/>
+      <c r="N11" s="40" t="n"/>
+      <c r="O11" s="40" t="inlineStr">
         <is>
           <t>Lightly Played</t>
         </is>
       </c>
-      <c r="N11" s="44" t="n">
+      <c r="P11" s="44" t="n">
         <v>185</v>
       </c>
-      <c r="O11" s="40" t="inlineStr">
+      <c r="Q11" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P11" s="40" t="inlineStr">
+      <c r="R11" s="40" t="inlineStr">
         <is>
           <t>Box 4</t>
         </is>
       </c>
-      <c r="Q11" s="40" t="n"/>
-      <c r="R11" s="40" t="n"/>
       <c r="S11" s="40" t="n"/>
-      <c r="T11" s="38" t="n"/>
-      <c r="U11" s="38" t="n"/>
+      <c r="T11" s="40" t="n"/>
+      <c r="U11" s="40" t="n"/>
       <c r="V11" s="38" t="n"/>
       <c r="W11" s="38" t="n"/>
     </row>
@@ -1623,32 +1717,40 @@
         </is>
       </c>
       <c r="I12" s="40" t="n"/>
-      <c r="J12" s="43" t="n"/>
-      <c r="K12" s="40" t="n"/>
-      <c r="L12" s="40" t="n"/>
-      <c r="M12" s="40" t="inlineStr">
+      <c r="J12" s="40" t="inlineStr">
+        <is>
+          <t>TCG</t>
+        </is>
+      </c>
+      <c r="K12" s="40" t="inlineStr">
+        <is>
+          <t>Pokémon</t>
+        </is>
+      </c>
+      <c r="L12" s="43" t="n"/>
+      <c r="M12" s="40" t="n"/>
+      <c r="N12" s="40" t="n"/>
+      <c r="O12" s="40" t="inlineStr">
         <is>
           <t>Factory Sealed</t>
         </is>
       </c>
-      <c r="N12" s="44" t="n">
+      <c r="P12" s="44" t="n">
         <v>145</v>
       </c>
-      <c r="O12" s="40" t="inlineStr">
+      <c r="Q12" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P12" s="40" t="inlineStr">
+      <c r="R12" s="40" t="inlineStr">
         <is>
           <t>Shelf 1</t>
         </is>
       </c>
-      <c r="Q12" s="40" t="n"/>
-      <c r="R12" s="40" t="n"/>
       <c r="S12" s="40" t="n"/>
-      <c r="T12" s="38" t="n"/>
-      <c r="U12" s="38" t="n"/>
+      <c r="T12" s="40" t="n"/>
+      <c r="U12" s="40" t="n"/>
       <c r="V12" s="38" t="n"/>
       <c r="W12" s="38" t="n"/>
     </row>
@@ -1680,32 +1782,40 @@
         </is>
       </c>
       <c r="I13" s="40" t="n"/>
-      <c r="J13" s="43" t="n"/>
-      <c r="K13" s="40" t="n"/>
-      <c r="L13" s="40" t="n"/>
-      <c r="M13" s="40" t="inlineStr">
+      <c r="J13" s="40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="K13" s="40" t="inlineStr">
+        <is>
+          <t>Basketball</t>
+        </is>
+      </c>
+      <c r="L13" s="43" t="n"/>
+      <c r="M13" s="40" t="n"/>
+      <c r="N13" s="40" t="n"/>
+      <c r="O13" s="40" t="inlineStr">
         <is>
           <t>Near Mint</t>
         </is>
       </c>
-      <c r="N13" s="44" t="n">
+      <c r="P13" s="44" t="n">
         <v>120</v>
       </c>
-      <c r="O13" s="40" t="inlineStr">
+      <c r="Q13" s="40" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="P13" s="40" t="inlineStr">
+      <c r="R13" s="40" t="inlineStr">
         <is>
           <t>Box 5</t>
         </is>
       </c>
-      <c r="Q13" s="40" t="n"/>
-      <c r="R13" s="40" t="n"/>
       <c r="S13" s="40" t="n"/>
-      <c r="T13" s="38" t="n"/>
-      <c r="U13" s="38" t="n"/>
+      <c r="T13" s="40" t="n"/>
+      <c r="U13" s="40" t="n"/>
       <c r="V13" s="38" t="n"/>
       <c r="W13" s="38" t="n"/>
     </row>
@@ -1745,32 +1855,40 @@
           <t>RC, Auto</t>
         </is>
       </c>
-      <c r="J14" s="43" t="n"/>
-      <c r="K14" s="40" t="n"/>
-      <c r="L14" s="40" t="n"/>
-      <c r="M14" s="40" t="inlineStr">
+      <c r="J14" s="40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="K14" s="40" t="inlineStr">
+        <is>
+          <t>Baseball</t>
+        </is>
+      </c>
+      <c r="L14" s="43" t="n"/>
+      <c r="M14" s="40" t="n"/>
+      <c r="N14" s="40" t="n"/>
+      <c r="O14" s="40" t="inlineStr">
         <is>
           <t>Near Mint</t>
         </is>
       </c>
-      <c r="N14" s="44" t="n">
+      <c r="P14" s="44" t="n">
         <v>890</v>
       </c>
-      <c r="O14" s="40" t="inlineStr">
+      <c r="Q14" s="40" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="P14" s="40" t="inlineStr">
+      <c r="R14" s="40" t="inlineStr">
         <is>
           <t>Box 2</t>
         </is>
       </c>
-      <c r="Q14" s="40" t="n"/>
-      <c r="R14" s="40" t="n"/>
       <c r="S14" s="40" t="n"/>
-      <c r="T14" s="38" t="n"/>
-      <c r="U14" s="38" t="n"/>
+      <c r="T14" s="40" t="n"/>
+      <c r="U14" s="40" t="n"/>
       <c r="V14" s="38" t="n"/>
       <c r="W14" s="38" t="n"/>
     </row>
@@ -1814,36 +1932,44 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="J15" s="43" t="n">
+      <c r="J15" s="40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="K15" s="40" t="inlineStr">
+        <is>
+          <t>Baseball</t>
+        </is>
+      </c>
+      <c r="L15" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="K15" s="40" t="inlineStr">
+      <c r="M15" s="40" t="inlineStr">
         <is>
           <t>PSA</t>
         </is>
       </c>
-      <c r="L15" s="40" t="n">
+      <c r="N15" s="40" t="n">
         <v>12345678</v>
       </c>
-      <c r="M15" s="40" t="n"/>
-      <c r="N15" s="44" t="n">
+      <c r="O15" s="40" t="n"/>
+      <c r="P15" s="44" t="n">
         <v>75000</v>
       </c>
-      <c r="O15" s="40" t="inlineStr">
+      <c r="Q15" s="40" t="inlineStr">
         <is>
           <t>Sold</t>
         </is>
       </c>
-      <c r="P15" s="40" t="inlineStr">
+      <c r="R15" s="40" t="inlineStr">
         <is>
           <t>Case 1</t>
         </is>
       </c>
-      <c r="Q15" s="40" t="n"/>
-      <c r="R15" s="40" t="n"/>
       <c r="S15" s="40" t="n"/>
-      <c r="T15" s="38" t="n"/>
-      <c r="U15" s="38" t="n"/>
+      <c r="T15" s="40" t="n"/>
+      <c r="U15" s="40" t="n"/>
       <c r="V15" s="38" t="n"/>
       <c r="W15" s="38" t="n"/>
     </row>
@@ -1857,18 +1983,18 @@
       <c r="G16" s="47" t="n"/>
       <c r="H16" s="45" t="n"/>
       <c r="I16" s="45" t="n"/>
-      <c r="J16" s="48" t="n"/>
+      <c r="J16" s="45" t="n"/>
       <c r="K16" s="45" t="n"/>
-      <c r="L16" s="45" t="n"/>
+      <c r="L16" s="48" t="n"/>
       <c r="M16" s="45" t="n"/>
-      <c r="N16" s="49" t="n"/>
+      <c r="N16" s="45" t="n"/>
       <c r="O16" s="45" t="n"/>
-      <c r="P16" s="45" t="n"/>
+      <c r="P16" s="49" t="n"/>
       <c r="Q16" s="45" t="n"/>
       <c r="R16" s="45" t="n"/>
       <c r="S16" s="45" t="n"/>
-      <c r="T16" s="38" t="n"/>
-      <c r="U16" s="38" t="n"/>
+      <c r="T16" s="45" t="n"/>
+      <c r="U16" s="45" t="n"/>
       <c r="V16" s="38" t="n"/>
       <c r="W16" s="38" t="n"/>
     </row>
@@ -1882,18 +2008,18 @@
       <c r="G17" s="52" t="n"/>
       <c r="H17" s="50" t="n"/>
       <c r="I17" s="50" t="n"/>
-      <c r="J17" s="53" t="n"/>
+      <c r="J17" s="50" t="n"/>
       <c r="K17" s="50" t="n"/>
-      <c r="L17" s="50" t="n"/>
+      <c r="L17" s="53" t="n"/>
       <c r="M17" s="50" t="n"/>
-      <c r="N17" s="54" t="n"/>
+      <c r="N17" s="50" t="n"/>
       <c r="O17" s="50" t="n"/>
-      <c r="P17" s="50" t="n"/>
+      <c r="P17" s="54" t="n"/>
       <c r="Q17" s="50" t="n"/>
       <c r="R17" s="50" t="n"/>
       <c r="S17" s="50" t="n"/>
-      <c r="T17" s="38" t="n"/>
-      <c r="U17" s="38" t="n"/>
+      <c r="T17" s="50" t="n"/>
+      <c r="U17" s="50" t="n"/>
       <c r="V17" s="38" t="n"/>
       <c r="W17" s="38" t="n"/>
     </row>
@@ -1907,18 +2033,18 @@
       <c r="G18" s="47" t="n"/>
       <c r="H18" s="45" t="n"/>
       <c r="I18" s="45" t="n"/>
-      <c r="J18" s="48" t="n"/>
+      <c r="J18" s="45" t="n"/>
       <c r="K18" s="45" t="n"/>
-      <c r="L18" s="45" t="n"/>
+      <c r="L18" s="48" t="n"/>
       <c r="M18" s="45" t="n"/>
-      <c r="N18" s="49" t="n"/>
+      <c r="N18" s="45" t="n"/>
       <c r="O18" s="45" t="n"/>
-      <c r="P18" s="45" t="n"/>
+      <c r="P18" s="49" t="n"/>
       <c r="Q18" s="45" t="n"/>
       <c r="R18" s="45" t="n"/>
       <c r="S18" s="45" t="n"/>
-      <c r="T18" s="38" t="n"/>
-      <c r="U18" s="38" t="n"/>
+      <c r="T18" s="45" t="n"/>
+      <c r="U18" s="45" t="n"/>
       <c r="V18" s="38" t="n"/>
       <c r="W18" s="38" t="n"/>
     </row>
@@ -1932,18 +2058,18 @@
       <c r="G19" s="52" t="n"/>
       <c r="H19" s="50" t="n"/>
       <c r="I19" s="50" t="n"/>
-      <c r="J19" s="53" t="n"/>
+      <c r="J19" s="50" t="n"/>
       <c r="K19" s="50" t="n"/>
-      <c r="L19" s="50" t="n"/>
+      <c r="L19" s="53" t="n"/>
       <c r="M19" s="50" t="n"/>
-      <c r="N19" s="54" t="n"/>
+      <c r="N19" s="50" t="n"/>
       <c r="O19" s="50" t="n"/>
-      <c r="P19" s="50" t="n"/>
+      <c r="P19" s="54" t="n"/>
       <c r="Q19" s="50" t="n"/>
       <c r="R19" s="50" t="n"/>
       <c r="S19" s="50" t="n"/>
-      <c r="T19" s="38" t="n"/>
-      <c r="U19" s="38" t="n"/>
+      <c r="T19" s="50" t="n"/>
+      <c r="U19" s="50" t="n"/>
       <c r="V19" s="38" t="n"/>
       <c r="W19" s="38" t="n"/>
     </row>
@@ -1957,18 +2083,18 @@
       <c r="G20" s="47" t="n"/>
       <c r="H20" s="45" t="n"/>
       <c r="I20" s="45" t="n"/>
-      <c r="J20" s="48" t="n"/>
+      <c r="J20" s="45" t="n"/>
       <c r="K20" s="45" t="n"/>
-      <c r="L20" s="45" t="n"/>
+      <c r="L20" s="48" t="n"/>
       <c r="M20" s="45" t="n"/>
-      <c r="N20" s="49" t="n"/>
+      <c r="N20" s="45" t="n"/>
       <c r="O20" s="45" t="n"/>
-      <c r="P20" s="45" t="n"/>
+      <c r="P20" s="49" t="n"/>
       <c r="Q20" s="45" t="n"/>
       <c r="R20" s="45" t="n"/>
       <c r="S20" s="45" t="n"/>
-      <c r="T20" s="38" t="n"/>
-      <c r="U20" s="38" t="n"/>
+      <c r="T20" s="45" t="n"/>
+      <c r="U20" s="45" t="n"/>
       <c r="V20" s="38" t="n"/>
       <c r="W20" s="38" t="n"/>
     </row>
@@ -1982,18 +2108,18 @@
       <c r="G21" s="52" t="n"/>
       <c r="H21" s="50" t="n"/>
       <c r="I21" s="50" t="n"/>
-      <c r="J21" s="53" t="n"/>
+      <c r="J21" s="50" t="n"/>
       <c r="K21" s="50" t="n"/>
-      <c r="L21" s="50" t="n"/>
+      <c r="L21" s="53" t="n"/>
       <c r="M21" s="50" t="n"/>
-      <c r="N21" s="54" t="n"/>
+      <c r="N21" s="50" t="n"/>
       <c r="O21" s="50" t="n"/>
-      <c r="P21" s="50" t="n"/>
+      <c r="P21" s="54" t="n"/>
       <c r="Q21" s="50" t="n"/>
       <c r="R21" s="50" t="n"/>
       <c r="S21" s="50" t="n"/>
-      <c r="T21" s="38" t="n"/>
-      <c r="U21" s="38" t="n"/>
+      <c r="T21" s="50" t="n"/>
+      <c r="U21" s="50" t="n"/>
       <c r="V21" s="38" t="n"/>
       <c r="W21" s="38" t="n"/>
     </row>
@@ -2007,18 +2133,18 @@
       <c r="G22" s="47" t="n"/>
       <c r="H22" s="45" t="n"/>
       <c r="I22" s="45" t="n"/>
-      <c r="J22" s="48" t="n"/>
+      <c r="J22" s="45" t="n"/>
       <c r="K22" s="45" t="n"/>
-      <c r="L22" s="45" t="n"/>
+      <c r="L22" s="48" t="n"/>
       <c r="M22" s="45" t="n"/>
-      <c r="N22" s="49" t="n"/>
+      <c r="N22" s="45" t="n"/>
       <c r="O22" s="45" t="n"/>
-      <c r="P22" s="45" t="n"/>
+      <c r="P22" s="49" t="n"/>
       <c r="Q22" s="45" t="n"/>
       <c r="R22" s="45" t="n"/>
       <c r="S22" s="45" t="n"/>
-      <c r="T22" s="38" t="n"/>
-      <c r="U22" s="38" t="n"/>
+      <c r="T22" s="45" t="n"/>
+      <c r="U22" s="45" t="n"/>
       <c r="V22" s="38" t="n"/>
       <c r="W22" s="38" t="n"/>
     </row>
@@ -2032,18 +2158,18 @@
       <c r="G23" s="52" t="n"/>
       <c r="H23" s="50" t="n"/>
       <c r="I23" s="50" t="n"/>
-      <c r="J23" s="53" t="n"/>
+      <c r="J23" s="50" t="n"/>
       <c r="K23" s="50" t="n"/>
-      <c r="L23" s="50" t="n"/>
+      <c r="L23" s="53" t="n"/>
       <c r="M23" s="50" t="n"/>
-      <c r="N23" s="54" t="n"/>
+      <c r="N23" s="50" t="n"/>
       <c r="O23" s="50" t="n"/>
-      <c r="P23" s="50" t="n"/>
+      <c r="P23" s="54" t="n"/>
       <c r="Q23" s="50" t="n"/>
       <c r="R23" s="50" t="n"/>
       <c r="S23" s="50" t="n"/>
-      <c r="T23" s="38" t="n"/>
-      <c r="U23" s="38" t="n"/>
+      <c r="T23" s="50" t="n"/>
+      <c r="U23" s="50" t="n"/>
       <c r="V23" s="38" t="n"/>
       <c r="W23" s="38" t="n"/>
     </row>
@@ -2057,18 +2183,18 @@
       <c r="G24" s="47" t="n"/>
       <c r="H24" s="45" t="n"/>
       <c r="I24" s="45" t="n"/>
-      <c r="J24" s="48" t="n"/>
+      <c r="J24" s="45" t="n"/>
       <c r="K24" s="45" t="n"/>
-      <c r="L24" s="45" t="n"/>
+      <c r="L24" s="48" t="n"/>
       <c r="M24" s="45" t="n"/>
-      <c r="N24" s="49" t="n"/>
+      <c r="N24" s="45" t="n"/>
       <c r="O24" s="45" t="n"/>
-      <c r="P24" s="45" t="n"/>
+      <c r="P24" s="49" t="n"/>
       <c r="Q24" s="45" t="n"/>
       <c r="R24" s="45" t="n"/>
       <c r="S24" s="45" t="n"/>
-      <c r="T24" s="38" t="n"/>
-      <c r="U24" s="38" t="n"/>
+      <c r="T24" s="45" t="n"/>
+      <c r="U24" s="45" t="n"/>
       <c r="V24" s="38" t="n"/>
       <c r="W24" s="38" t="n"/>
     </row>
@@ -2082,18 +2208,18 @@
       <c r="G25" s="52" t="n"/>
       <c r="H25" s="50" t="n"/>
       <c r="I25" s="50" t="n"/>
-      <c r="J25" s="53" t="n"/>
+      <c r="J25" s="50" t="n"/>
       <c r="K25" s="50" t="n"/>
-      <c r="L25" s="50" t="n"/>
+      <c r="L25" s="53" t="n"/>
       <c r="M25" s="50" t="n"/>
-      <c r="N25" s="54" t="n"/>
+      <c r="N25" s="50" t="n"/>
       <c r="O25" s="50" t="n"/>
-      <c r="P25" s="50" t="n"/>
+      <c r="P25" s="54" t="n"/>
       <c r="Q25" s="50" t="n"/>
       <c r="R25" s="50" t="n"/>
       <c r="S25" s="50" t="n"/>
-      <c r="T25" s="38" t="n"/>
-      <c r="U25" s="38" t="n"/>
+      <c r="T25" s="50" t="n"/>
+      <c r="U25" s="50" t="n"/>
       <c r="V25" s="38" t="n"/>
       <c r="W25" s="38" t="n"/>
     </row>
@@ -2107,18 +2233,18 @@
       <c r="G26" s="47" t="n"/>
       <c r="H26" s="45" t="n"/>
       <c r="I26" s="45" t="n"/>
-      <c r="J26" s="48" t="n"/>
+      <c r="J26" s="45" t="n"/>
       <c r="K26" s="45" t="n"/>
-      <c r="L26" s="45" t="n"/>
+      <c r="L26" s="48" t="n"/>
       <c r="M26" s="45" t="n"/>
-      <c r="N26" s="49" t="n"/>
+      <c r="N26" s="45" t="n"/>
       <c r="O26" s="45" t="n"/>
-      <c r="P26" s="45" t="n"/>
+      <c r="P26" s="49" t="n"/>
       <c r="Q26" s="45" t="n"/>
       <c r="R26" s="45" t="n"/>
       <c r="S26" s="45" t="n"/>
-      <c r="T26" s="38" t="n"/>
-      <c r="U26" s="38" t="n"/>
+      <c r="T26" s="45" t="n"/>
+      <c r="U26" s="45" t="n"/>
       <c r="V26" s="38" t="n"/>
       <c r="W26" s="38" t="n"/>
     </row>
@@ -2132,18 +2258,18 @@
       <c r="G27" s="52" t="n"/>
       <c r="H27" s="50" t="n"/>
       <c r="I27" s="50" t="n"/>
-      <c r="J27" s="53" t="n"/>
+      <c r="J27" s="50" t="n"/>
       <c r="K27" s="50" t="n"/>
-      <c r="L27" s="50" t="n"/>
+      <c r="L27" s="53" t="n"/>
       <c r="M27" s="50" t="n"/>
-      <c r="N27" s="54" t="n"/>
+      <c r="N27" s="50" t="n"/>
       <c r="O27" s="50" t="n"/>
-      <c r="P27" s="50" t="n"/>
+      <c r="P27" s="54" t="n"/>
       <c r="Q27" s="50" t="n"/>
       <c r="R27" s="50" t="n"/>
       <c r="S27" s="50" t="n"/>
-      <c r="T27" s="38" t="n"/>
-      <c r="U27" s="38" t="n"/>
+      <c r="T27" s="50" t="n"/>
+      <c r="U27" s="50" t="n"/>
       <c r="V27" s="38" t="n"/>
       <c r="W27" s="38" t="n"/>
     </row>
@@ -2157,18 +2283,18 @@
       <c r="G28" s="47" t="n"/>
       <c r="H28" s="45" t="n"/>
       <c r="I28" s="45" t="n"/>
-      <c r="J28" s="48" t="n"/>
+      <c r="J28" s="45" t="n"/>
       <c r="K28" s="45" t="n"/>
-      <c r="L28" s="45" t="n"/>
+      <c r="L28" s="48" t="n"/>
       <c r="M28" s="45" t="n"/>
-      <c r="N28" s="49" t="n"/>
+      <c r="N28" s="45" t="n"/>
       <c r="O28" s="45" t="n"/>
-      <c r="P28" s="45" t="n"/>
+      <c r="P28" s="49" t="n"/>
       <c r="Q28" s="45" t="n"/>
       <c r="R28" s="45" t="n"/>
       <c r="S28" s="45" t="n"/>
-      <c r="T28" s="38" t="n"/>
-      <c r="U28" s="38" t="n"/>
+      <c r="T28" s="45" t="n"/>
+      <c r="U28" s="45" t="n"/>
       <c r="V28" s="38" t="n"/>
       <c r="W28" s="38" t="n"/>
     </row>
@@ -2182,18 +2308,18 @@
       <c r="G29" s="52" t="n"/>
       <c r="H29" s="50" t="n"/>
       <c r="I29" s="50" t="n"/>
-      <c r="J29" s="53" t="n"/>
+      <c r="J29" s="50" t="n"/>
       <c r="K29" s="50" t="n"/>
-      <c r="L29" s="50" t="n"/>
+      <c r="L29" s="53" t="n"/>
       <c r="M29" s="50" t="n"/>
-      <c r="N29" s="54" t="n"/>
+      <c r="N29" s="50" t="n"/>
       <c r="O29" s="50" t="n"/>
-      <c r="P29" s="50" t="n"/>
+      <c r="P29" s="54" t="n"/>
       <c r="Q29" s="50" t="n"/>
       <c r="R29" s="50" t="n"/>
       <c r="S29" s="50" t="n"/>
-      <c r="T29" s="38" t="n"/>
-      <c r="U29" s="38" t="n"/>
+      <c r="T29" s="50" t="n"/>
+      <c r="U29" s="50" t="n"/>
       <c r="V29" s="38" t="n"/>
       <c r="W29" s="38" t="n"/>
     </row>
@@ -2207,18 +2333,18 @@
       <c r="G30" s="47" t="n"/>
       <c r="H30" s="45" t="n"/>
       <c r="I30" s="45" t="n"/>
-      <c r="J30" s="48" t="n"/>
+      <c r="J30" s="45" t="n"/>
       <c r="K30" s="45" t="n"/>
-      <c r="L30" s="45" t="n"/>
+      <c r="L30" s="48" t="n"/>
       <c r="M30" s="45" t="n"/>
-      <c r="N30" s="49" t="n"/>
+      <c r="N30" s="45" t="n"/>
       <c r="O30" s="45" t="n"/>
-      <c r="P30" s="45" t="n"/>
+      <c r="P30" s="49" t="n"/>
       <c r="Q30" s="45" t="n"/>
       <c r="R30" s="45" t="n"/>
       <c r="S30" s="45" t="n"/>
-      <c r="T30" s="38" t="n"/>
-      <c r="U30" s="38" t="n"/>
+      <c r="T30" s="45" t="n"/>
+      <c r="U30" s="45" t="n"/>
       <c r="V30" s="38" t="n"/>
       <c r="W30" s="38" t="n"/>
     </row>
@@ -2232,18 +2358,18 @@
       <c r="G31" s="52" t="n"/>
       <c r="H31" s="50" t="n"/>
       <c r="I31" s="50" t="n"/>
-      <c r="J31" s="53" t="n"/>
+      <c r="J31" s="50" t="n"/>
       <c r="K31" s="50" t="n"/>
-      <c r="L31" s="50" t="n"/>
+      <c r="L31" s="53" t="n"/>
       <c r="M31" s="50" t="n"/>
-      <c r="N31" s="54" t="n"/>
+      <c r="N31" s="50" t="n"/>
       <c r="O31" s="50" t="n"/>
-      <c r="P31" s="50" t="n"/>
+      <c r="P31" s="54" t="n"/>
       <c r="Q31" s="50" t="n"/>
       <c r="R31" s="50" t="n"/>
       <c r="S31" s="50" t="n"/>
-      <c r="T31" s="38" t="n"/>
-      <c r="U31" s="38" t="n"/>
+      <c r="T31" s="50" t="n"/>
+      <c r="U31" s="50" t="n"/>
       <c r="V31" s="38" t="n"/>
       <c r="W31" s="38" t="n"/>
     </row>
@@ -2257,18 +2383,18 @@
       <c r="G32" s="47" t="n"/>
       <c r="H32" s="45" t="n"/>
       <c r="I32" s="45" t="n"/>
-      <c r="J32" s="48" t="n"/>
+      <c r="J32" s="45" t="n"/>
       <c r="K32" s="45" t="n"/>
-      <c r="L32" s="45" t="n"/>
+      <c r="L32" s="48" t="n"/>
       <c r="M32" s="45" t="n"/>
-      <c r="N32" s="49" t="n"/>
+      <c r="N32" s="45" t="n"/>
       <c r="O32" s="45" t="n"/>
-      <c r="P32" s="45" t="n"/>
+      <c r="P32" s="49" t="n"/>
       <c r="Q32" s="45" t="n"/>
       <c r="R32" s="45" t="n"/>
       <c r="S32" s="45" t="n"/>
-      <c r="T32" s="38" t="n"/>
-      <c r="U32" s="38" t="n"/>
+      <c r="T32" s="45" t="n"/>
+      <c r="U32" s="45" t="n"/>
       <c r="V32" s="38" t="n"/>
       <c r="W32" s="38" t="n"/>
     </row>
@@ -2282,18 +2408,18 @@
       <c r="G33" s="52" t="n"/>
       <c r="H33" s="50" t="n"/>
       <c r="I33" s="50" t="n"/>
-      <c r="J33" s="53" t="n"/>
+      <c r="J33" s="50" t="n"/>
       <c r="K33" s="50" t="n"/>
-      <c r="L33" s="50" t="n"/>
+      <c r="L33" s="53" t="n"/>
       <c r="M33" s="50" t="n"/>
-      <c r="N33" s="54" t="n"/>
+      <c r="N33" s="50" t="n"/>
       <c r="O33" s="50" t="n"/>
-      <c r="P33" s="50" t="n"/>
+      <c r="P33" s="54" t="n"/>
       <c r="Q33" s="50" t="n"/>
       <c r="R33" s="50" t="n"/>
       <c r="S33" s="50" t="n"/>
-      <c r="T33" s="38" t="n"/>
-      <c r="U33" s="38" t="n"/>
+      <c r="T33" s="50" t="n"/>
+      <c r="U33" s="50" t="n"/>
       <c r="V33" s="38" t="n"/>
       <c r="W33" s="38" t="n"/>
     </row>
@@ -2307,18 +2433,18 @@
       <c r="G34" s="47" t="n"/>
       <c r="H34" s="45" t="n"/>
       <c r="I34" s="45" t="n"/>
-      <c r="J34" s="48" t="n"/>
+      <c r="J34" s="45" t="n"/>
       <c r="K34" s="45" t="n"/>
-      <c r="L34" s="45" t="n"/>
+      <c r="L34" s="48" t="n"/>
       <c r="M34" s="45" t="n"/>
-      <c r="N34" s="49" t="n"/>
+      <c r="N34" s="45" t="n"/>
       <c r="O34" s="45" t="n"/>
-      <c r="P34" s="45" t="n"/>
+      <c r="P34" s="49" t="n"/>
       <c r="Q34" s="45" t="n"/>
       <c r="R34" s="45" t="n"/>
       <c r="S34" s="45" t="n"/>
-      <c r="T34" s="38" t="n"/>
-      <c r="U34" s="38" t="n"/>
+      <c r="T34" s="45" t="n"/>
+      <c r="U34" s="45" t="n"/>
       <c r="V34" s="38" t="n"/>
       <c r="W34" s="38" t="n"/>
     </row>
@@ -2332,18 +2458,18 @@
       <c r="G35" s="52" t="n"/>
       <c r="H35" s="50" t="n"/>
       <c r="I35" s="50" t="n"/>
-      <c r="J35" s="53" t="n"/>
+      <c r="J35" s="50" t="n"/>
       <c r="K35" s="50" t="n"/>
-      <c r="L35" s="50" t="n"/>
+      <c r="L35" s="53" t="n"/>
       <c r="M35" s="50" t="n"/>
-      <c r="N35" s="54" t="n"/>
+      <c r="N35" s="50" t="n"/>
       <c r="O35" s="50" t="n"/>
-      <c r="P35" s="50" t="n"/>
+      <c r="P35" s="54" t="n"/>
       <c r="Q35" s="50" t="n"/>
       <c r="R35" s="50" t="n"/>
       <c r="S35" s="50" t="n"/>
-      <c r="T35" s="38" t="n"/>
-      <c r="U35" s="38" t="n"/>
+      <c r="T35" s="50" t="n"/>
+      <c r="U35" s="50" t="n"/>
       <c r="V35" s="38" t="n"/>
       <c r="W35" s="38" t="n"/>
     </row>
@@ -2357,18 +2483,18 @@
       <c r="G36" s="47" t="n"/>
       <c r="H36" s="45" t="n"/>
       <c r="I36" s="45" t="n"/>
-      <c r="J36" s="48" t="n"/>
+      <c r="J36" s="45" t="n"/>
       <c r="K36" s="45" t="n"/>
-      <c r="L36" s="45" t="n"/>
+      <c r="L36" s="48" t="n"/>
       <c r="M36" s="45" t="n"/>
-      <c r="N36" s="49" t="n"/>
+      <c r="N36" s="45" t="n"/>
       <c r="O36" s="45" t="n"/>
-      <c r="P36" s="45" t="n"/>
+      <c r="P36" s="49" t="n"/>
       <c r="Q36" s="45" t="n"/>
       <c r="R36" s="45" t="n"/>
       <c r="S36" s="45" t="n"/>
-      <c r="T36" s="38" t="n"/>
-      <c r="U36" s="38" t="n"/>
+      <c r="T36" s="45" t="n"/>
+      <c r="U36" s="45" t="n"/>
       <c r="V36" s="38" t="n"/>
       <c r="W36" s="38" t="n"/>
     </row>
@@ -2382,18 +2508,18 @@
       <c r="G37" s="52" t="n"/>
       <c r="H37" s="50" t="n"/>
       <c r="I37" s="50" t="n"/>
-      <c r="J37" s="53" t="n"/>
+      <c r="J37" s="50" t="n"/>
       <c r="K37" s="50" t="n"/>
-      <c r="L37" s="50" t="n"/>
+      <c r="L37" s="53" t="n"/>
       <c r="M37" s="50" t="n"/>
-      <c r="N37" s="54" t="n"/>
+      <c r="N37" s="50" t="n"/>
       <c r="O37" s="50" t="n"/>
-      <c r="P37" s="50" t="n"/>
+      <c r="P37" s="54" t="n"/>
       <c r="Q37" s="50" t="n"/>
       <c r="R37" s="50" t="n"/>
       <c r="S37" s="50" t="n"/>
-      <c r="T37" s="38" t="n"/>
-      <c r="U37" s="38" t="n"/>
+      <c r="T37" s="50" t="n"/>
+      <c r="U37" s="50" t="n"/>
       <c r="V37" s="38" t="n"/>
       <c r="W37" s="38" t="n"/>
     </row>
@@ -2407,18 +2533,18 @@
       <c r="G38" s="47" t="n"/>
       <c r="H38" s="45" t="n"/>
       <c r="I38" s="45" t="n"/>
-      <c r="J38" s="48" t="n"/>
+      <c r="J38" s="45" t="n"/>
       <c r="K38" s="45" t="n"/>
-      <c r="L38" s="45" t="n"/>
+      <c r="L38" s="48" t="n"/>
       <c r="M38" s="45" t="n"/>
-      <c r="N38" s="49" t="n"/>
+      <c r="N38" s="45" t="n"/>
       <c r="O38" s="45" t="n"/>
-      <c r="P38" s="45" t="n"/>
+      <c r="P38" s="49" t="n"/>
       <c r="Q38" s="45" t="n"/>
       <c r="R38" s="45" t="n"/>
       <c r="S38" s="45" t="n"/>
-      <c r="T38" s="38" t="n"/>
-      <c r="U38" s="38" t="n"/>
+      <c r="T38" s="45" t="n"/>
+      <c r="U38" s="45" t="n"/>
       <c r="V38" s="38" t="n"/>
       <c r="W38" s="38" t="n"/>
     </row>
@@ -2432,18 +2558,18 @@
       <c r="G39" s="52" t="n"/>
       <c r="H39" s="50" t="n"/>
       <c r="I39" s="50" t="n"/>
-      <c r="J39" s="53" t="n"/>
+      <c r="J39" s="50" t="n"/>
       <c r="K39" s="50" t="n"/>
-      <c r="L39" s="50" t="n"/>
+      <c r="L39" s="53" t="n"/>
       <c r="M39" s="50" t="n"/>
-      <c r="N39" s="54" t="n"/>
+      <c r="N39" s="50" t="n"/>
       <c r="O39" s="50" t="n"/>
-      <c r="P39" s="50" t="n"/>
+      <c r="P39" s="54" t="n"/>
       <c r="Q39" s="50" t="n"/>
       <c r="R39" s="50" t="n"/>
       <c r="S39" s="50" t="n"/>
-      <c r="T39" s="38" t="n"/>
-      <c r="U39" s="38" t="n"/>
+      <c r="T39" s="50" t="n"/>
+      <c r="U39" s="50" t="n"/>
       <c r="V39" s="38" t="n"/>
       <c r="W39" s="38" t="n"/>
     </row>
@@ -2457,18 +2583,18 @@
       <c r="G40" s="47" t="n"/>
       <c r="H40" s="45" t="n"/>
       <c r="I40" s="45" t="n"/>
-      <c r="J40" s="48" t="n"/>
+      <c r="J40" s="45" t="n"/>
       <c r="K40" s="45" t="n"/>
-      <c r="L40" s="45" t="n"/>
+      <c r="L40" s="48" t="n"/>
       <c r="M40" s="45" t="n"/>
-      <c r="N40" s="49" t="n"/>
+      <c r="N40" s="45" t="n"/>
       <c r="O40" s="45" t="n"/>
-      <c r="P40" s="45" t="n"/>
+      <c r="P40" s="49" t="n"/>
       <c r="Q40" s="45" t="n"/>
       <c r="R40" s="45" t="n"/>
       <c r="S40" s="45" t="n"/>
-      <c r="T40" s="38" t="n"/>
-      <c r="U40" s="38" t="n"/>
+      <c r="T40" s="45" t="n"/>
+      <c r="U40" s="45" t="n"/>
       <c r="V40" s="38" t="n"/>
       <c r="W40" s="38" t="n"/>
     </row>
@@ -2482,18 +2608,18 @@
       <c r="G41" s="52" t="n"/>
       <c r="H41" s="50" t="n"/>
       <c r="I41" s="50" t="n"/>
-      <c r="J41" s="53" t="n"/>
+      <c r="J41" s="50" t="n"/>
       <c r="K41" s="50" t="n"/>
-      <c r="L41" s="50" t="n"/>
+      <c r="L41" s="53" t="n"/>
       <c r="M41" s="50" t="n"/>
-      <c r="N41" s="54" t="n"/>
+      <c r="N41" s="50" t="n"/>
       <c r="O41" s="50" t="n"/>
-      <c r="P41" s="50" t="n"/>
+      <c r="P41" s="54" t="n"/>
       <c r="Q41" s="50" t="n"/>
       <c r="R41" s="50" t="n"/>
       <c r="S41" s="50" t="n"/>
-      <c r="T41" s="38" t="n"/>
-      <c r="U41" s="38" t="n"/>
+      <c r="T41" s="50" t="n"/>
+      <c r="U41" s="50" t="n"/>
       <c r="V41" s="38" t="n"/>
       <c r="W41" s="38" t="n"/>
     </row>
@@ -2507,18 +2633,18 @@
       <c r="G42" s="47" t="n"/>
       <c r="H42" s="45" t="n"/>
       <c r="I42" s="45" t="n"/>
-      <c r="J42" s="48" t="n"/>
+      <c r="J42" s="45" t="n"/>
       <c r="K42" s="45" t="n"/>
-      <c r="L42" s="45" t="n"/>
+      <c r="L42" s="48" t="n"/>
       <c r="M42" s="45" t="n"/>
-      <c r="N42" s="49" t="n"/>
+      <c r="N42" s="45" t="n"/>
       <c r="O42" s="45" t="n"/>
-      <c r="P42" s="45" t="n"/>
+      <c r="P42" s="49" t="n"/>
       <c r="Q42" s="45" t="n"/>
       <c r="R42" s="45" t="n"/>
       <c r="S42" s="45" t="n"/>
-      <c r="T42" s="38" t="n"/>
-      <c r="U42" s="38" t="n"/>
+      <c r="T42" s="45" t="n"/>
+      <c r="U42" s="45" t="n"/>
       <c r="V42" s="38" t="n"/>
       <c r="W42" s="38" t="n"/>
     </row>
@@ -2532,18 +2658,18 @@
       <c r="G43" s="52" t="n"/>
       <c r="H43" s="50" t="n"/>
       <c r="I43" s="50" t="n"/>
-      <c r="J43" s="53" t="n"/>
+      <c r="J43" s="50" t="n"/>
       <c r="K43" s="50" t="n"/>
-      <c r="L43" s="50" t="n"/>
+      <c r="L43" s="53" t="n"/>
       <c r="M43" s="50" t="n"/>
-      <c r="N43" s="54" t="n"/>
+      <c r="N43" s="50" t="n"/>
       <c r="O43" s="50" t="n"/>
-      <c r="P43" s="50" t="n"/>
+      <c r="P43" s="54" t="n"/>
       <c r="Q43" s="50" t="n"/>
       <c r="R43" s="50" t="n"/>
       <c r="S43" s="50" t="n"/>
-      <c r="T43" s="38" t="n"/>
-      <c r="U43" s="38" t="n"/>
+      <c r="T43" s="50" t="n"/>
+      <c r="U43" s="50" t="n"/>
       <c r="V43" s="38" t="n"/>
       <c r="W43" s="38" t="n"/>
     </row>
@@ -2557,18 +2683,18 @@
       <c r="G44" s="47" t="n"/>
       <c r="H44" s="45" t="n"/>
       <c r="I44" s="45" t="n"/>
-      <c r="J44" s="48" t="n"/>
+      <c r="J44" s="45" t="n"/>
       <c r="K44" s="45" t="n"/>
-      <c r="L44" s="45" t="n"/>
+      <c r="L44" s="48" t="n"/>
       <c r="M44" s="45" t="n"/>
-      <c r="N44" s="49" t="n"/>
+      <c r="N44" s="45" t="n"/>
       <c r="O44" s="45" t="n"/>
-      <c r="P44" s="45" t="n"/>
+      <c r="P44" s="49" t="n"/>
       <c r="Q44" s="45" t="n"/>
       <c r="R44" s="45" t="n"/>
       <c r="S44" s="45" t="n"/>
-      <c r="T44" s="38" t="n"/>
-      <c r="U44" s="38" t="n"/>
+      <c r="T44" s="45" t="n"/>
+      <c r="U44" s="45" t="n"/>
       <c r="V44" s="38" t="n"/>
       <c r="W44" s="38" t="n"/>
     </row>
@@ -2582,18 +2708,18 @@
       <c r="G45" s="52" t="n"/>
       <c r="H45" s="50" t="n"/>
       <c r="I45" s="50" t="n"/>
-      <c r="J45" s="53" t="n"/>
+      <c r="J45" s="50" t="n"/>
       <c r="K45" s="50" t="n"/>
-      <c r="L45" s="50" t="n"/>
+      <c r="L45" s="53" t="n"/>
       <c r="M45" s="50" t="n"/>
-      <c r="N45" s="54" t="n"/>
+      <c r="N45" s="50" t="n"/>
       <c r="O45" s="50" t="n"/>
-      <c r="P45" s="50" t="n"/>
+      <c r="P45" s="54" t="n"/>
       <c r="Q45" s="50" t="n"/>
       <c r="R45" s="50" t="n"/>
       <c r="S45" s="50" t="n"/>
-      <c r="T45" s="38" t="n"/>
-      <c r="U45" s="38" t="n"/>
+      <c r="T45" s="50" t="n"/>
+      <c r="U45" s="50" t="n"/>
       <c r="V45" s="38" t="n"/>
       <c r="W45" s="38" t="n"/>
     </row>
@@ -2607,18 +2733,18 @@
       <c r="G46" s="47" t="n"/>
       <c r="H46" s="45" t="n"/>
       <c r="I46" s="45" t="n"/>
-      <c r="J46" s="48" t="n"/>
+      <c r="J46" s="45" t="n"/>
       <c r="K46" s="45" t="n"/>
-      <c r="L46" s="45" t="n"/>
+      <c r="L46" s="48" t="n"/>
       <c r="M46" s="45" t="n"/>
-      <c r="N46" s="49" t="n"/>
+      <c r="N46" s="45" t="n"/>
       <c r="O46" s="45" t="n"/>
-      <c r="P46" s="45" t="n"/>
+      <c r="P46" s="49" t="n"/>
       <c r="Q46" s="45" t="n"/>
       <c r="R46" s="45" t="n"/>
       <c r="S46" s="45" t="n"/>
-      <c r="T46" s="38" t="n"/>
-      <c r="U46" s="38" t="n"/>
+      <c r="T46" s="45" t="n"/>
+      <c r="U46" s="45" t="n"/>
       <c r="V46" s="38" t="n"/>
       <c r="W46" s="38" t="n"/>
     </row>
@@ -2632,18 +2758,18 @@
       <c r="G47" s="52" t="n"/>
       <c r="H47" s="50" t="n"/>
       <c r="I47" s="50" t="n"/>
-      <c r="J47" s="53" t="n"/>
+      <c r="J47" s="50" t="n"/>
       <c r="K47" s="50" t="n"/>
-      <c r="L47" s="50" t="n"/>
+      <c r="L47" s="53" t="n"/>
       <c r="M47" s="50" t="n"/>
-      <c r="N47" s="54" t="n"/>
+      <c r="N47" s="50" t="n"/>
       <c r="O47" s="50" t="n"/>
-      <c r="P47" s="50" t="n"/>
+      <c r="P47" s="54" t="n"/>
       <c r="Q47" s="50" t="n"/>
       <c r="R47" s="50" t="n"/>
       <c r="S47" s="50" t="n"/>
-      <c r="T47" s="38" t="n"/>
-      <c r="U47" s="38" t="n"/>
+      <c r="T47" s="50" t="n"/>
+      <c r="U47" s="50" t="n"/>
       <c r="V47" s="38" t="n"/>
       <c r="W47" s="38" t="n"/>
     </row>
@@ -2657,18 +2783,18 @@
       <c r="G48" s="47" t="n"/>
       <c r="H48" s="45" t="n"/>
       <c r="I48" s="45" t="n"/>
-      <c r="J48" s="48" t="n"/>
+      <c r="J48" s="45" t="n"/>
       <c r="K48" s="45" t="n"/>
-      <c r="L48" s="45" t="n"/>
+      <c r="L48" s="48" t="n"/>
       <c r="M48" s="45" t="n"/>
-      <c r="N48" s="49" t="n"/>
+      <c r="N48" s="45" t="n"/>
       <c r="O48" s="45" t="n"/>
-      <c r="P48" s="45" t="n"/>
+      <c r="P48" s="49" t="n"/>
       <c r="Q48" s="45" t="n"/>
       <c r="R48" s="45" t="n"/>
       <c r="S48" s="45" t="n"/>
-      <c r="T48" s="38" t="n"/>
-      <c r="U48" s="38" t="n"/>
+      <c r="T48" s="45" t="n"/>
+      <c r="U48" s="45" t="n"/>
       <c r="V48" s="38" t="n"/>
       <c r="W48" s="38" t="n"/>
     </row>
@@ -2682,18 +2808,18 @@
       <c r="G49" s="52" t="n"/>
       <c r="H49" s="50" t="n"/>
       <c r="I49" s="50" t="n"/>
-      <c r="J49" s="53" t="n"/>
+      <c r="J49" s="50" t="n"/>
       <c r="K49" s="50" t="n"/>
-      <c r="L49" s="50" t="n"/>
+      <c r="L49" s="53" t="n"/>
       <c r="M49" s="50" t="n"/>
-      <c r="N49" s="54" t="n"/>
+      <c r="N49" s="50" t="n"/>
       <c r="O49" s="50" t="n"/>
-      <c r="P49" s="50" t="n"/>
+      <c r="P49" s="54" t="n"/>
       <c r="Q49" s="50" t="n"/>
       <c r="R49" s="50" t="n"/>
       <c r="S49" s="50" t="n"/>
-      <c r="T49" s="38" t="n"/>
-      <c r="U49" s="38" t="n"/>
+      <c r="T49" s="50" t="n"/>
+      <c r="U49" s="50" t="n"/>
       <c r="V49" s="38" t="n"/>
       <c r="W49" s="38" t="n"/>
     </row>
@@ -2707,18 +2833,18 @@
       <c r="G50" s="47" t="n"/>
       <c r="H50" s="45" t="n"/>
       <c r="I50" s="45" t="n"/>
-      <c r="J50" s="48" t="n"/>
+      <c r="J50" s="45" t="n"/>
       <c r="K50" s="45" t="n"/>
-      <c r="L50" s="45" t="n"/>
+      <c r="L50" s="48" t="n"/>
       <c r="M50" s="45" t="n"/>
-      <c r="N50" s="49" t="n"/>
+      <c r="N50" s="45" t="n"/>
       <c r="O50" s="45" t="n"/>
-      <c r="P50" s="45" t="n"/>
+      <c r="P50" s="49" t="n"/>
       <c r="Q50" s="45" t="n"/>
       <c r="R50" s="45" t="n"/>
       <c r="S50" s="45" t="n"/>
-      <c r="T50" s="38" t="n"/>
-      <c r="U50" s="38" t="n"/>
+      <c r="T50" s="45" t="n"/>
+      <c r="U50" s="45" t="n"/>
       <c r="V50" s="38" t="n"/>
       <c r="W50" s="38" t="n"/>
     </row>
@@ -2732,18 +2858,18 @@
       <c r="G51" s="52" t="n"/>
       <c r="H51" s="50" t="n"/>
       <c r="I51" s="50" t="n"/>
-      <c r="J51" s="53" t="n"/>
+      <c r="J51" s="50" t="n"/>
       <c r="K51" s="50" t="n"/>
-      <c r="L51" s="50" t="n"/>
+      <c r="L51" s="53" t="n"/>
       <c r="M51" s="50" t="n"/>
-      <c r="N51" s="54" t="n"/>
+      <c r="N51" s="50" t="n"/>
       <c r="O51" s="50" t="n"/>
-      <c r="P51" s="50" t="n"/>
+      <c r="P51" s="54" t="n"/>
       <c r="Q51" s="50" t="n"/>
       <c r="R51" s="50" t="n"/>
       <c r="S51" s="50" t="n"/>
-      <c r="T51" s="38" t="n"/>
-      <c r="U51" s="38" t="n"/>
+      <c r="T51" s="50" t="n"/>
+      <c r="U51" s="50" t="n"/>
       <c r="V51" s="38" t="n"/>
       <c r="W51" s="38" t="n"/>
     </row>
@@ -2757,18 +2883,18 @@
       <c r="G52" s="47" t="n"/>
       <c r="H52" s="45" t="n"/>
       <c r="I52" s="45" t="n"/>
-      <c r="J52" s="48" t="n"/>
+      <c r="J52" s="45" t="n"/>
       <c r="K52" s="45" t="n"/>
-      <c r="L52" s="45" t="n"/>
+      <c r="L52" s="48" t="n"/>
       <c r="M52" s="45" t="n"/>
-      <c r="N52" s="49" t="n"/>
+      <c r="N52" s="45" t="n"/>
       <c r="O52" s="45" t="n"/>
-      <c r="P52" s="45" t="n"/>
+      <c r="P52" s="49" t="n"/>
       <c r="Q52" s="45" t="n"/>
       <c r="R52" s="45" t="n"/>
       <c r="S52" s="45" t="n"/>
-      <c r="T52" s="38" t="n"/>
-      <c r="U52" s="38" t="n"/>
+      <c r="T52" s="45" t="n"/>
+      <c r="U52" s="45" t="n"/>
       <c r="V52" s="38" t="n"/>
       <c r="W52" s="38" t="n"/>
     </row>
@@ -2782,18 +2908,18 @@
       <c r="G53" s="52" t="n"/>
       <c r="H53" s="50" t="n"/>
       <c r="I53" s="50" t="n"/>
-      <c r="J53" s="53" t="n"/>
+      <c r="J53" s="50" t="n"/>
       <c r="K53" s="50" t="n"/>
-      <c r="L53" s="50" t="n"/>
+      <c r="L53" s="53" t="n"/>
       <c r="M53" s="50" t="n"/>
-      <c r="N53" s="54" t="n"/>
+      <c r="N53" s="50" t="n"/>
       <c r="O53" s="50" t="n"/>
-      <c r="P53" s="50" t="n"/>
+      <c r="P53" s="54" t="n"/>
       <c r="Q53" s="50" t="n"/>
       <c r="R53" s="50" t="n"/>
       <c r="S53" s="50" t="n"/>
-      <c r="T53" s="38" t="n"/>
-      <c r="U53" s="38" t="n"/>
+      <c r="T53" s="50" t="n"/>
+      <c r="U53" s="50" t="n"/>
       <c r="V53" s="38" t="n"/>
       <c r="W53" s="38" t="n"/>
     </row>
@@ -2807,18 +2933,18 @@
       <c r="G54" s="47" t="n"/>
       <c r="H54" s="45" t="n"/>
       <c r="I54" s="45" t="n"/>
-      <c r="J54" s="48" t="n"/>
+      <c r="J54" s="45" t="n"/>
       <c r="K54" s="45" t="n"/>
-      <c r="L54" s="45" t="n"/>
+      <c r="L54" s="48" t="n"/>
       <c r="M54" s="45" t="n"/>
-      <c r="N54" s="49" t="n"/>
+      <c r="N54" s="45" t="n"/>
       <c r="O54" s="45" t="n"/>
-      <c r="P54" s="45" t="n"/>
+      <c r="P54" s="49" t="n"/>
       <c r="Q54" s="45" t="n"/>
       <c r="R54" s="45" t="n"/>
       <c r="S54" s="45" t="n"/>
-      <c r="T54" s="38" t="n"/>
-      <c r="U54" s="38" t="n"/>
+      <c r="T54" s="45" t="n"/>
+      <c r="U54" s="45" t="n"/>
       <c r="V54" s="38" t="n"/>
       <c r="W54" s="38" t="n"/>
     </row>
@@ -2832,18 +2958,18 @@
       <c r="G55" s="52" t="n"/>
       <c r="H55" s="50" t="n"/>
       <c r="I55" s="50" t="n"/>
-      <c r="J55" s="53" t="n"/>
+      <c r="J55" s="50" t="n"/>
       <c r="K55" s="50" t="n"/>
-      <c r="L55" s="50" t="n"/>
+      <c r="L55" s="53" t="n"/>
       <c r="M55" s="50" t="n"/>
-      <c r="N55" s="54" t="n"/>
+      <c r="N55" s="50" t="n"/>
       <c r="O55" s="50" t="n"/>
-      <c r="P55" s="50" t="n"/>
+      <c r="P55" s="54" t="n"/>
       <c r="Q55" s="50" t="n"/>
       <c r="R55" s="50" t="n"/>
       <c r="S55" s="50" t="n"/>
-      <c r="T55" s="38" t="n"/>
-      <c r="U55" s="38" t="n"/>
+      <c r="T55" s="50" t="n"/>
+      <c r="U55" s="50" t="n"/>
       <c r="V55" s="38" t="n"/>
       <c r="W55" s="38" t="n"/>
     </row>
@@ -2857,18 +2983,18 @@
       <c r="G56" s="47" t="n"/>
       <c r="H56" s="45" t="n"/>
       <c r="I56" s="45" t="n"/>
-      <c r="J56" s="48" t="n"/>
+      <c r="J56" s="45" t="n"/>
       <c r="K56" s="45" t="n"/>
-      <c r="L56" s="45" t="n"/>
+      <c r="L56" s="48" t="n"/>
       <c r="M56" s="45" t="n"/>
-      <c r="N56" s="49" t="n"/>
+      <c r="N56" s="45" t="n"/>
       <c r="O56" s="45" t="n"/>
-      <c r="P56" s="45" t="n"/>
+      <c r="P56" s="49" t="n"/>
       <c r="Q56" s="45" t="n"/>
       <c r="R56" s="45" t="n"/>
       <c r="S56" s="45" t="n"/>
-      <c r="T56" s="38" t="n"/>
-      <c r="U56" s="38" t="n"/>
+      <c r="T56" s="45" t="n"/>
+      <c r="U56" s="45" t="n"/>
       <c r="V56" s="38" t="n"/>
       <c r="W56" s="38" t="n"/>
     </row>
@@ -2882,18 +3008,18 @@
       <c r="G57" s="52" t="n"/>
       <c r="H57" s="50" t="n"/>
       <c r="I57" s="50" t="n"/>
-      <c r="J57" s="53" t="n"/>
+      <c r="J57" s="50" t="n"/>
       <c r="K57" s="50" t="n"/>
-      <c r="L57" s="50" t="n"/>
+      <c r="L57" s="53" t="n"/>
       <c r="M57" s="50" t="n"/>
-      <c r="N57" s="54" t="n"/>
+      <c r="N57" s="50" t="n"/>
       <c r="O57" s="50" t="n"/>
-      <c r="P57" s="50" t="n"/>
+      <c r="P57" s="54" t="n"/>
       <c r="Q57" s="50" t="n"/>
       <c r="R57" s="50" t="n"/>
       <c r="S57" s="50" t="n"/>
-      <c r="T57" s="38" t="n"/>
-      <c r="U57" s="38" t="n"/>
+      <c r="T57" s="50" t="n"/>
+      <c r="U57" s="50" t="n"/>
       <c r="V57" s="38" t="n"/>
       <c r="W57" s="38" t="n"/>
     </row>
@@ -2907,18 +3033,18 @@
       <c r="G58" s="47" t="n"/>
       <c r="H58" s="45" t="n"/>
       <c r="I58" s="45" t="n"/>
-      <c r="J58" s="48" t="n"/>
+      <c r="J58" s="45" t="n"/>
       <c r="K58" s="45" t="n"/>
-      <c r="L58" s="45" t="n"/>
+      <c r="L58" s="48" t="n"/>
       <c r="M58" s="45" t="n"/>
-      <c r="N58" s="49" t="n"/>
+      <c r="N58" s="45" t="n"/>
       <c r="O58" s="45" t="n"/>
-      <c r="P58" s="45" t="n"/>
+      <c r="P58" s="49" t="n"/>
       <c r="Q58" s="45" t="n"/>
       <c r="R58" s="45" t="n"/>
       <c r="S58" s="45" t="n"/>
-      <c r="T58" s="38" t="n"/>
-      <c r="U58" s="38" t="n"/>
+      <c r="T58" s="45" t="n"/>
+      <c r="U58" s="45" t="n"/>
       <c r="V58" s="38" t="n"/>
       <c r="W58" s="38" t="n"/>
     </row>
@@ -2932,18 +3058,18 @@
       <c r="G59" s="52" t="n"/>
       <c r="H59" s="50" t="n"/>
       <c r="I59" s="50" t="n"/>
-      <c r="J59" s="53" t="n"/>
+      <c r="J59" s="50" t="n"/>
       <c r="K59" s="50" t="n"/>
-      <c r="L59" s="50" t="n"/>
+      <c r="L59" s="53" t="n"/>
       <c r="M59" s="50" t="n"/>
-      <c r="N59" s="54" t="n"/>
+      <c r="N59" s="50" t="n"/>
       <c r="O59" s="50" t="n"/>
-      <c r="P59" s="50" t="n"/>
+      <c r="P59" s="54" t="n"/>
       <c r="Q59" s="50" t="n"/>
       <c r="R59" s="50" t="n"/>
       <c r="S59" s="50" t="n"/>
-      <c r="T59" s="38" t="n"/>
-      <c r="U59" s="38" t="n"/>
+      <c r="T59" s="50" t="n"/>
+      <c r="U59" s="50" t="n"/>
       <c r="V59" s="38" t="n"/>
       <c r="W59" s="38" t="n"/>
     </row>
@@ -2957,18 +3083,18 @@
       <c r="G60" s="47" t="n"/>
       <c r="H60" s="45" t="n"/>
       <c r="I60" s="45" t="n"/>
-      <c r="J60" s="48" t="n"/>
+      <c r="J60" s="45" t="n"/>
       <c r="K60" s="45" t="n"/>
-      <c r="L60" s="45" t="n"/>
+      <c r="L60" s="48" t="n"/>
       <c r="M60" s="45" t="n"/>
-      <c r="N60" s="49" t="n"/>
+      <c r="N60" s="45" t="n"/>
       <c r="O60" s="45" t="n"/>
-      <c r="P60" s="45" t="n"/>
+      <c r="P60" s="49" t="n"/>
       <c r="Q60" s="45" t="n"/>
       <c r="R60" s="45" t="n"/>
       <c r="S60" s="45" t="n"/>
-      <c r="T60" s="38" t="n"/>
-      <c r="U60" s="38" t="n"/>
+      <c r="T60" s="45" t="n"/>
+      <c r="U60" s="45" t="n"/>
       <c r="V60" s="38" t="n"/>
       <c r="W60" s="38" t="n"/>
     </row>
@@ -2982,18 +3108,18 @@
       <c r="G61" s="52" t="n"/>
       <c r="H61" s="50" t="n"/>
       <c r="I61" s="50" t="n"/>
-      <c r="J61" s="53" t="n"/>
+      <c r="J61" s="50" t="n"/>
       <c r="K61" s="50" t="n"/>
-      <c r="L61" s="50" t="n"/>
+      <c r="L61" s="53" t="n"/>
       <c r="M61" s="50" t="n"/>
-      <c r="N61" s="54" t="n"/>
+      <c r="N61" s="50" t="n"/>
       <c r="O61" s="50" t="n"/>
-      <c r="P61" s="50" t="n"/>
+      <c r="P61" s="54" t="n"/>
       <c r="Q61" s="50" t="n"/>
       <c r="R61" s="50" t="n"/>
       <c r="S61" s="50" t="n"/>
-      <c r="T61" s="38" t="n"/>
-      <c r="U61" s="38" t="n"/>
+      <c r="T61" s="50" t="n"/>
+      <c r="U61" s="50" t="n"/>
       <c r="V61" s="38" t="n"/>
       <c r="W61" s="38" t="n"/>
     </row>
@@ -3007,18 +3133,18 @@
       <c r="G62" s="47" t="n"/>
       <c r="H62" s="45" t="n"/>
       <c r="I62" s="45" t="n"/>
-      <c r="J62" s="48" t="n"/>
+      <c r="J62" s="45" t="n"/>
       <c r="K62" s="45" t="n"/>
-      <c r="L62" s="45" t="n"/>
+      <c r="L62" s="48" t="n"/>
       <c r="M62" s="45" t="n"/>
-      <c r="N62" s="49" t="n"/>
+      <c r="N62" s="45" t="n"/>
       <c r="O62" s="45" t="n"/>
-      <c r="P62" s="45" t="n"/>
+      <c r="P62" s="49" t="n"/>
       <c r="Q62" s="45" t="n"/>
       <c r="R62" s="45" t="n"/>
       <c r="S62" s="45" t="n"/>
-      <c r="T62" s="38" t="n"/>
-      <c r="U62" s="38" t="n"/>
+      <c r="T62" s="45" t="n"/>
+      <c r="U62" s="45" t="n"/>
       <c r="V62" s="38" t="n"/>
       <c r="W62" s="38" t="n"/>
     </row>
@@ -3032,18 +3158,18 @@
       <c r="G63" s="52" t="n"/>
       <c r="H63" s="50" t="n"/>
       <c r="I63" s="50" t="n"/>
-      <c r="J63" s="53" t="n"/>
+      <c r="J63" s="50" t="n"/>
       <c r="K63" s="50" t="n"/>
-      <c r="L63" s="50" t="n"/>
+      <c r="L63" s="53" t="n"/>
       <c r="M63" s="50" t="n"/>
-      <c r="N63" s="54" t="n"/>
+      <c r="N63" s="50" t="n"/>
       <c r="O63" s="50" t="n"/>
-      <c r="P63" s="50" t="n"/>
+      <c r="P63" s="54" t="n"/>
       <c r="Q63" s="50" t="n"/>
       <c r="R63" s="50" t="n"/>
       <c r="S63" s="50" t="n"/>
-      <c r="T63" s="38" t="n"/>
-      <c r="U63" s="38" t="n"/>
+      <c r="T63" s="50" t="n"/>
+      <c r="U63" s="50" t="n"/>
       <c r="V63" s="38" t="n"/>
       <c r="W63" s="38" t="n"/>
     </row>
@@ -3057,18 +3183,18 @@
       <c r="G64" s="47" t="n"/>
       <c r="H64" s="45" t="n"/>
       <c r="I64" s="45" t="n"/>
-      <c r="J64" s="48" t="n"/>
+      <c r="J64" s="45" t="n"/>
       <c r="K64" s="45" t="n"/>
-      <c r="L64" s="45" t="n"/>
+      <c r="L64" s="48" t="n"/>
       <c r="M64" s="45" t="n"/>
-      <c r="N64" s="49" t="n"/>
+      <c r="N64" s="45" t="n"/>
       <c r="O64" s="45" t="n"/>
-      <c r="P64" s="45" t="n"/>
+      <c r="P64" s="49" t="n"/>
       <c r="Q64" s="45" t="n"/>
       <c r="R64" s="45" t="n"/>
       <c r="S64" s="45" t="n"/>
-      <c r="T64" s="38" t="n"/>
-      <c r="U64" s="38" t="n"/>
+      <c r="T64" s="45" t="n"/>
+      <c r="U64" s="45" t="n"/>
       <c r="V64" s="38" t="n"/>
       <c r="W64" s="38" t="n"/>
     </row>
@@ -3082,18 +3208,18 @@
       <c r="G65" s="52" t="n"/>
       <c r="H65" s="50" t="n"/>
       <c r="I65" s="50" t="n"/>
-      <c r="J65" s="53" t="n"/>
+      <c r="J65" s="50" t="n"/>
       <c r="K65" s="50" t="n"/>
-      <c r="L65" s="50" t="n"/>
+      <c r="L65" s="53" t="n"/>
       <c r="M65" s="50" t="n"/>
-      <c r="N65" s="54" t="n"/>
+      <c r="N65" s="50" t="n"/>
       <c r="O65" s="50" t="n"/>
-      <c r="P65" s="50" t="n"/>
+      <c r="P65" s="54" t="n"/>
       <c r="Q65" s="50" t="n"/>
       <c r="R65" s="50" t="n"/>
       <c r="S65" s="50" t="n"/>
-      <c r="T65" s="38" t="n"/>
-      <c r="U65" s="38" t="n"/>
+      <c r="T65" s="50" t="n"/>
+      <c r="U65" s="50" t="n"/>
       <c r="V65" s="38" t="n"/>
       <c r="W65" s="38" t="n"/>
     </row>
@@ -3107,18 +3233,18 @@
       <c r="G66" s="47" t="n"/>
       <c r="H66" s="45" t="n"/>
       <c r="I66" s="45" t="n"/>
-      <c r="J66" s="48" t="n"/>
+      <c r="J66" s="45" t="n"/>
       <c r="K66" s="45" t="n"/>
-      <c r="L66" s="45" t="n"/>
+      <c r="L66" s="48" t="n"/>
       <c r="M66" s="45" t="n"/>
-      <c r="N66" s="49" t="n"/>
+      <c r="N66" s="45" t="n"/>
       <c r="O66" s="45" t="n"/>
-      <c r="P66" s="45" t="n"/>
+      <c r="P66" s="49" t="n"/>
       <c r="Q66" s="45" t="n"/>
       <c r="R66" s="45" t="n"/>
       <c r="S66" s="45" t="n"/>
-      <c r="T66" s="38" t="n"/>
-      <c r="U66" s="38" t="n"/>
+      <c r="T66" s="45" t="n"/>
+      <c r="U66" s="45" t="n"/>
       <c r="V66" s="38" t="n"/>
       <c r="W66" s="38" t="n"/>
     </row>
@@ -3132,18 +3258,18 @@
       <c r="G67" s="52" t="n"/>
       <c r="H67" s="50" t="n"/>
       <c r="I67" s="50" t="n"/>
-      <c r="J67" s="53" t="n"/>
+      <c r="J67" s="50" t="n"/>
       <c r="K67" s="50" t="n"/>
-      <c r="L67" s="50" t="n"/>
+      <c r="L67" s="53" t="n"/>
       <c r="M67" s="50" t="n"/>
-      <c r="N67" s="54" t="n"/>
+      <c r="N67" s="50" t="n"/>
       <c r="O67" s="50" t="n"/>
-      <c r="P67" s="50" t="n"/>
+      <c r="P67" s="54" t="n"/>
       <c r="Q67" s="50" t="n"/>
       <c r="R67" s="50" t="n"/>
       <c r="S67" s="50" t="n"/>
-      <c r="T67" s="38" t="n"/>
-      <c r="U67" s="38" t="n"/>
+      <c r="T67" s="50" t="n"/>
+      <c r="U67" s="50" t="n"/>
       <c r="V67" s="38" t="n"/>
       <c r="W67" s="38" t="n"/>
     </row>
@@ -3157,18 +3283,18 @@
       <c r="G68" s="47" t="n"/>
       <c r="H68" s="45" t="n"/>
       <c r="I68" s="45" t="n"/>
-      <c r="J68" s="48" t="n"/>
+      <c r="J68" s="45" t="n"/>
       <c r="K68" s="45" t="n"/>
-      <c r="L68" s="45" t="n"/>
+      <c r="L68" s="48" t="n"/>
       <c r="M68" s="45" t="n"/>
-      <c r="N68" s="49" t="n"/>
+      <c r="N68" s="45" t="n"/>
       <c r="O68" s="45" t="n"/>
-      <c r="P68" s="45" t="n"/>
+      <c r="P68" s="49" t="n"/>
       <c r="Q68" s="45" t="n"/>
       <c r="R68" s="45" t="n"/>
       <c r="S68" s="45" t="n"/>
-      <c r="T68" s="38" t="n"/>
-      <c r="U68" s="38" t="n"/>
+      <c r="T68" s="45" t="n"/>
+      <c r="U68" s="45" t="n"/>
       <c r="V68" s="38" t="n"/>
       <c r="W68" s="38" t="n"/>
     </row>
@@ -3182,18 +3308,18 @@
       <c r="G69" s="52" t="n"/>
       <c r="H69" s="50" t="n"/>
       <c r="I69" s="50" t="n"/>
-      <c r="J69" s="53" t="n"/>
+      <c r="J69" s="50" t="n"/>
       <c r="K69" s="50" t="n"/>
-      <c r="L69" s="50" t="n"/>
+      <c r="L69" s="53" t="n"/>
       <c r="M69" s="50" t="n"/>
-      <c r="N69" s="54" t="n"/>
+      <c r="N69" s="50" t="n"/>
       <c r="O69" s="50" t="n"/>
-      <c r="P69" s="50" t="n"/>
+      <c r="P69" s="54" t="n"/>
       <c r="Q69" s="50" t="n"/>
       <c r="R69" s="50" t="n"/>
       <c r="S69" s="50" t="n"/>
-      <c r="T69" s="38" t="n"/>
-      <c r="U69" s="38" t="n"/>
+      <c r="T69" s="50" t="n"/>
+      <c r="U69" s="50" t="n"/>
       <c r="V69" s="38" t="n"/>
       <c r="W69" s="38" t="n"/>
     </row>
@@ -3207,18 +3333,18 @@
       <c r="G70" s="47" t="n"/>
       <c r="H70" s="45" t="n"/>
       <c r="I70" s="45" t="n"/>
-      <c r="J70" s="48" t="n"/>
+      <c r="J70" s="45" t="n"/>
       <c r="K70" s="45" t="n"/>
-      <c r="L70" s="45" t="n"/>
+      <c r="L70" s="48" t="n"/>
       <c r="M70" s="45" t="n"/>
-      <c r="N70" s="49" t="n"/>
+      <c r="N70" s="45" t="n"/>
       <c r="O70" s="45" t="n"/>
-      <c r="P70" s="45" t="n"/>
+      <c r="P70" s="49" t="n"/>
       <c r="Q70" s="45" t="n"/>
       <c r="R70" s="45" t="n"/>
       <c r="S70" s="45" t="n"/>
-      <c r="T70" s="38" t="n"/>
-      <c r="U70" s="38" t="n"/>
+      <c r="T70" s="45" t="n"/>
+      <c r="U70" s="45" t="n"/>
       <c r="V70" s="38" t="n"/>
       <c r="W70" s="38" t="n"/>
     </row>
@@ -3232,18 +3358,18 @@
       <c r="G71" s="52" t="n"/>
       <c r="H71" s="50" t="n"/>
       <c r="I71" s="50" t="n"/>
-      <c r="J71" s="53" t="n"/>
+      <c r="J71" s="50" t="n"/>
       <c r="K71" s="50" t="n"/>
-      <c r="L71" s="50" t="n"/>
+      <c r="L71" s="53" t="n"/>
       <c r="M71" s="50" t="n"/>
-      <c r="N71" s="54" t="n"/>
+      <c r="N71" s="50" t="n"/>
       <c r="O71" s="50" t="n"/>
-      <c r="P71" s="50" t="n"/>
+      <c r="P71" s="54" t="n"/>
       <c r="Q71" s="50" t="n"/>
       <c r="R71" s="50" t="n"/>
       <c r="S71" s="50" t="n"/>
-      <c r="T71" s="38" t="n"/>
-      <c r="U71" s="38" t="n"/>
+      <c r="T71" s="50" t="n"/>
+      <c r="U71" s="50" t="n"/>
       <c r="V71" s="38" t="n"/>
       <c r="W71" s="38" t="n"/>
     </row>
@@ -3257,18 +3383,18 @@
       <c r="G72" s="47" t="n"/>
       <c r="H72" s="45" t="n"/>
       <c r="I72" s="45" t="n"/>
-      <c r="J72" s="48" t="n"/>
+      <c r="J72" s="45" t="n"/>
       <c r="K72" s="45" t="n"/>
-      <c r="L72" s="45" t="n"/>
+      <c r="L72" s="48" t="n"/>
       <c r="M72" s="45" t="n"/>
-      <c r="N72" s="49" t="n"/>
+      <c r="N72" s="45" t="n"/>
       <c r="O72" s="45" t="n"/>
-      <c r="P72" s="45" t="n"/>
+      <c r="P72" s="49" t="n"/>
       <c r="Q72" s="45" t="n"/>
       <c r="R72" s="45" t="n"/>
       <c r="S72" s="45" t="n"/>
-      <c r="T72" s="38" t="n"/>
-      <c r="U72" s="38" t="n"/>
+      <c r="T72" s="45" t="n"/>
+      <c r="U72" s="45" t="n"/>
       <c r="V72" s="38" t="n"/>
       <c r="W72" s="38" t="n"/>
     </row>
@@ -3282,18 +3408,18 @@
       <c r="G73" s="52" t="n"/>
       <c r="H73" s="50" t="n"/>
       <c r="I73" s="50" t="n"/>
-      <c r="J73" s="53" t="n"/>
+      <c r="J73" s="50" t="n"/>
       <c r="K73" s="50" t="n"/>
-      <c r="L73" s="50" t="n"/>
+      <c r="L73" s="53" t="n"/>
       <c r="M73" s="50" t="n"/>
-      <c r="N73" s="54" t="n"/>
+      <c r="N73" s="50" t="n"/>
       <c r="O73" s="50" t="n"/>
-      <c r="P73" s="50" t="n"/>
+      <c r="P73" s="54" t="n"/>
       <c r="Q73" s="50" t="n"/>
       <c r="R73" s="50" t="n"/>
       <c r="S73" s="50" t="n"/>
-      <c r="T73" s="38" t="n"/>
-      <c r="U73" s="38" t="n"/>
+      <c r="T73" s="50" t="n"/>
+      <c r="U73" s="50" t="n"/>
       <c r="V73" s="38" t="n"/>
       <c r="W73" s="38" t="n"/>
     </row>
@@ -3307,18 +3433,18 @@
       <c r="G74" s="47" t="n"/>
       <c r="H74" s="45" t="n"/>
       <c r="I74" s="45" t="n"/>
-      <c r="J74" s="48" t="n"/>
+      <c r="J74" s="45" t="n"/>
       <c r="K74" s="45" t="n"/>
-      <c r="L74" s="45" t="n"/>
+      <c r="L74" s="48" t="n"/>
       <c r="M74" s="45" t="n"/>
-      <c r="N74" s="49" t="n"/>
+      <c r="N74" s="45" t="n"/>
       <c r="O74" s="45" t="n"/>
-      <c r="P74" s="45" t="n"/>
+      <c r="P74" s="49" t="n"/>
       <c r="Q74" s="45" t="n"/>
       <c r="R74" s="45" t="n"/>
       <c r="S74" s="45" t="n"/>
-      <c r="T74" s="38" t="n"/>
-      <c r="U74" s="38" t="n"/>
+      <c r="T74" s="45" t="n"/>
+      <c r="U74" s="45" t="n"/>
       <c r="V74" s="38" t="n"/>
       <c r="W74" s="38" t="n"/>
     </row>
@@ -3332,18 +3458,18 @@
       <c r="G75" s="52" t="n"/>
       <c r="H75" s="50" t="n"/>
       <c r="I75" s="50" t="n"/>
-      <c r="J75" s="53" t="n"/>
+      <c r="J75" s="50" t="n"/>
       <c r="K75" s="50" t="n"/>
-      <c r="L75" s="50" t="n"/>
+      <c r="L75" s="53" t="n"/>
       <c r="M75" s="50" t="n"/>
-      <c r="N75" s="54" t="n"/>
+      <c r="N75" s="50" t="n"/>
       <c r="O75" s="50" t="n"/>
-      <c r="P75" s="50" t="n"/>
+      <c r="P75" s="54" t="n"/>
       <c r="Q75" s="50" t="n"/>
       <c r="R75" s="50" t="n"/>
       <c r="S75" s="50" t="n"/>
-      <c r="T75" s="38" t="n"/>
-      <c r="U75" s="38" t="n"/>
+      <c r="T75" s="50" t="n"/>
+      <c r="U75" s="50" t="n"/>
       <c r="V75" s="38" t="n"/>
       <c r="W75" s="38" t="n"/>
     </row>
@@ -3357,18 +3483,18 @@
       <c r="G76" s="47" t="n"/>
       <c r="H76" s="45" t="n"/>
       <c r="I76" s="45" t="n"/>
-      <c r="J76" s="48" t="n"/>
+      <c r="J76" s="45" t="n"/>
       <c r="K76" s="45" t="n"/>
-      <c r="L76" s="45" t="n"/>
+      <c r="L76" s="48" t="n"/>
       <c r="M76" s="45" t="n"/>
-      <c r="N76" s="49" t="n"/>
+      <c r="N76" s="45" t="n"/>
       <c r="O76" s="45" t="n"/>
-      <c r="P76" s="45" t="n"/>
+      <c r="P76" s="49" t="n"/>
       <c r="Q76" s="45" t="n"/>
       <c r="R76" s="45" t="n"/>
       <c r="S76" s="45" t="n"/>
-      <c r="T76" s="38" t="n"/>
-      <c r="U76" s="38" t="n"/>
+      <c r="T76" s="45" t="n"/>
+      <c r="U76" s="45" t="n"/>
       <c r="V76" s="38" t="n"/>
       <c r="W76" s="38" t="n"/>
     </row>
@@ -3382,18 +3508,18 @@
       <c r="G77" s="52" t="n"/>
       <c r="H77" s="50" t="n"/>
       <c r="I77" s="50" t="n"/>
-      <c r="J77" s="53" t="n"/>
+      <c r="J77" s="50" t="n"/>
       <c r="K77" s="50" t="n"/>
-      <c r="L77" s="50" t="n"/>
+      <c r="L77" s="53" t="n"/>
       <c r="M77" s="50" t="n"/>
-      <c r="N77" s="54" t="n"/>
+      <c r="N77" s="50" t="n"/>
       <c r="O77" s="50" t="n"/>
-      <c r="P77" s="50" t="n"/>
+      <c r="P77" s="54" t="n"/>
       <c r="Q77" s="50" t="n"/>
       <c r="R77" s="50" t="n"/>
       <c r="S77" s="50" t="n"/>
-      <c r="T77" s="38" t="n"/>
-      <c r="U77" s="38" t="n"/>
+      <c r="T77" s="50" t="n"/>
+      <c r="U77" s="50" t="n"/>
       <c r="V77" s="38" t="n"/>
       <c r="W77" s="38" t="n"/>
     </row>
@@ -3407,18 +3533,18 @@
       <c r="G78" s="47" t="n"/>
       <c r="H78" s="45" t="n"/>
       <c r="I78" s="45" t="n"/>
-      <c r="J78" s="48" t="n"/>
+      <c r="J78" s="45" t="n"/>
       <c r="K78" s="45" t="n"/>
-      <c r="L78" s="45" t="n"/>
+      <c r="L78" s="48" t="n"/>
       <c r="M78" s="45" t="n"/>
-      <c r="N78" s="49" t="n"/>
+      <c r="N78" s="45" t="n"/>
       <c r="O78" s="45" t="n"/>
-      <c r="P78" s="45" t="n"/>
+      <c r="P78" s="49" t="n"/>
       <c r="Q78" s="45" t="n"/>
       <c r="R78" s="45" t="n"/>
       <c r="S78" s="45" t="n"/>
-      <c r="T78" s="38" t="n"/>
-      <c r="U78" s="38" t="n"/>
+      <c r="T78" s="45" t="n"/>
+      <c r="U78" s="45" t="n"/>
       <c r="V78" s="38" t="n"/>
       <c r="W78" s="38" t="n"/>
     </row>
@@ -3432,18 +3558,18 @@
       <c r="G79" s="52" t="n"/>
       <c r="H79" s="50" t="n"/>
       <c r="I79" s="50" t="n"/>
-      <c r="J79" s="53" t="n"/>
+      <c r="J79" s="50" t="n"/>
       <c r="K79" s="50" t="n"/>
-      <c r="L79" s="50" t="n"/>
+      <c r="L79" s="53" t="n"/>
       <c r="M79" s="50" t="n"/>
-      <c r="N79" s="54" t="n"/>
+      <c r="N79" s="50" t="n"/>
       <c r="O79" s="50" t="n"/>
-      <c r="P79" s="50" t="n"/>
+      <c r="P79" s="54" t="n"/>
       <c r="Q79" s="50" t="n"/>
       <c r="R79" s="50" t="n"/>
       <c r="S79" s="50" t="n"/>
-      <c r="T79" s="38" t="n"/>
-      <c r="U79" s="38" t="n"/>
+      <c r="T79" s="50" t="n"/>
+      <c r="U79" s="50" t="n"/>
       <c r="V79" s="38" t="n"/>
       <c r="W79" s="38" t="n"/>
     </row>
@@ -3457,18 +3583,18 @@
       <c r="G80" s="47" t="n"/>
       <c r="H80" s="45" t="n"/>
       <c r="I80" s="45" t="n"/>
-      <c r="J80" s="48" t="n"/>
+      <c r="J80" s="45" t="n"/>
       <c r="K80" s="45" t="n"/>
-      <c r="L80" s="45" t="n"/>
+      <c r="L80" s="48" t="n"/>
       <c r="M80" s="45" t="n"/>
-      <c r="N80" s="49" t="n"/>
+      <c r="N80" s="45" t="n"/>
       <c r="O80" s="45" t="n"/>
-      <c r="P80" s="45" t="n"/>
+      <c r="P80" s="49" t="n"/>
       <c r="Q80" s="45" t="n"/>
       <c r="R80" s="45" t="n"/>
       <c r="S80" s="45" t="n"/>
-      <c r="T80" s="38" t="n"/>
-      <c r="U80" s="38" t="n"/>
+      <c r="T80" s="45" t="n"/>
+      <c r="U80" s="45" t="n"/>
       <c r="V80" s="38" t="n"/>
       <c r="W80" s="38" t="n"/>
     </row>
@@ -3482,18 +3608,18 @@
       <c r="G81" s="52" t="n"/>
       <c r="H81" s="50" t="n"/>
       <c r="I81" s="50" t="n"/>
-      <c r="J81" s="53" t="n"/>
+      <c r="J81" s="50" t="n"/>
       <c r="K81" s="50" t="n"/>
-      <c r="L81" s="50" t="n"/>
+      <c r="L81" s="53" t="n"/>
       <c r="M81" s="50" t="n"/>
-      <c r="N81" s="54" t="n"/>
+      <c r="N81" s="50" t="n"/>
       <c r="O81" s="50" t="n"/>
-      <c r="P81" s="50" t="n"/>
+      <c r="P81" s="54" t="n"/>
       <c r="Q81" s="50" t="n"/>
       <c r="R81" s="50" t="n"/>
       <c r="S81" s="50" t="n"/>
-      <c r="T81" s="38" t="n"/>
-      <c r="U81" s="38" t="n"/>
+      <c r="T81" s="50" t="n"/>
+      <c r="U81" s="50" t="n"/>
       <c r="V81" s="38" t="n"/>
       <c r="W81" s="38" t="n"/>
     </row>
@@ -3507,18 +3633,18 @@
       <c r="G82" s="47" t="n"/>
       <c r="H82" s="45" t="n"/>
       <c r="I82" s="45" t="n"/>
-      <c r="J82" s="48" t="n"/>
+      <c r="J82" s="45" t="n"/>
       <c r="K82" s="45" t="n"/>
-      <c r="L82" s="45" t="n"/>
+      <c r="L82" s="48" t="n"/>
       <c r="M82" s="45" t="n"/>
-      <c r="N82" s="49" t="n"/>
+      <c r="N82" s="45" t="n"/>
       <c r="O82" s="45" t="n"/>
-      <c r="P82" s="45" t="n"/>
+      <c r="P82" s="49" t="n"/>
       <c r="Q82" s="45" t="n"/>
       <c r="R82" s="45" t="n"/>
       <c r="S82" s="45" t="n"/>
-      <c r="T82" s="38" t="n"/>
-      <c r="U82" s="38" t="n"/>
+      <c r="T82" s="45" t="n"/>
+      <c r="U82" s="45" t="n"/>
       <c r="V82" s="38" t="n"/>
       <c r="W82" s="38" t="n"/>
     </row>
@@ -3532,18 +3658,18 @@
       <c r="G83" s="52" t="n"/>
       <c r="H83" s="50" t="n"/>
       <c r="I83" s="50" t="n"/>
-      <c r="J83" s="53" t="n"/>
+      <c r="J83" s="50" t="n"/>
       <c r="K83" s="50" t="n"/>
-      <c r="L83" s="50" t="n"/>
+      <c r="L83" s="53" t="n"/>
       <c r="M83" s="50" t="n"/>
-      <c r="N83" s="54" t="n"/>
+      <c r="N83" s="50" t="n"/>
       <c r="O83" s="50" t="n"/>
-      <c r="P83" s="50" t="n"/>
+      <c r="P83" s="54" t="n"/>
       <c r="Q83" s="50" t="n"/>
       <c r="R83" s="50" t="n"/>
       <c r="S83" s="50" t="n"/>
-      <c r="T83" s="38" t="n"/>
-      <c r="U83" s="38" t="n"/>
+      <c r="T83" s="50" t="n"/>
+      <c r="U83" s="50" t="n"/>
       <c r="V83" s="38" t="n"/>
       <c r="W83" s="38" t="n"/>
     </row>
@@ -3557,18 +3683,18 @@
       <c r="G84" s="47" t="n"/>
       <c r="H84" s="45" t="n"/>
       <c r="I84" s="45" t="n"/>
-      <c r="J84" s="48" t="n"/>
+      <c r="J84" s="45" t="n"/>
       <c r="K84" s="45" t="n"/>
-      <c r="L84" s="45" t="n"/>
+      <c r="L84" s="48" t="n"/>
       <c r="M84" s="45" t="n"/>
-      <c r="N84" s="49" t="n"/>
+      <c r="N84" s="45" t="n"/>
       <c r="O84" s="45" t="n"/>
-      <c r="P84" s="45" t="n"/>
+      <c r="P84" s="49" t="n"/>
       <c r="Q84" s="45" t="n"/>
       <c r="R84" s="45" t="n"/>
       <c r="S84" s="45" t="n"/>
-      <c r="T84" s="38" t="n"/>
-      <c r="U84" s="38" t="n"/>
+      <c r="T84" s="45" t="n"/>
+      <c r="U84" s="45" t="n"/>
       <c r="V84" s="38" t="n"/>
       <c r="W84" s="38" t="n"/>
     </row>
@@ -3582,18 +3708,18 @@
       <c r="G85" s="52" t="n"/>
       <c r="H85" s="50" t="n"/>
       <c r="I85" s="50" t="n"/>
-      <c r="J85" s="53" t="n"/>
+      <c r="J85" s="50" t="n"/>
       <c r="K85" s="50" t="n"/>
-      <c r="L85" s="50" t="n"/>
+      <c r="L85" s="53" t="n"/>
       <c r="M85" s="50" t="n"/>
-      <c r="N85" s="54" t="n"/>
+      <c r="N85" s="50" t="n"/>
       <c r="O85" s="50" t="n"/>
-      <c r="P85" s="50" t="n"/>
+      <c r="P85" s="54" t="n"/>
       <c r="Q85" s="50" t="n"/>
       <c r="R85" s="50" t="n"/>
       <c r="S85" s="50" t="n"/>
-      <c r="T85" s="38" t="n"/>
-      <c r="U85" s="38" t="n"/>
+      <c r="T85" s="50" t="n"/>
+      <c r="U85" s="50" t="n"/>
       <c r="V85" s="38" t="n"/>
       <c r="W85" s="38" t="n"/>
     </row>
@@ -3607,18 +3733,18 @@
       <c r="G86" s="47" t="n"/>
       <c r="H86" s="45" t="n"/>
       <c r="I86" s="45" t="n"/>
-      <c r="J86" s="48" t="n"/>
+      <c r="J86" s="45" t="n"/>
       <c r="K86" s="45" t="n"/>
-      <c r="L86" s="45" t="n"/>
+      <c r="L86" s="48" t="n"/>
       <c r="M86" s="45" t="n"/>
-      <c r="N86" s="49" t="n"/>
+      <c r="N86" s="45" t="n"/>
       <c r="O86" s="45" t="n"/>
-      <c r="P86" s="45" t="n"/>
+      <c r="P86" s="49" t="n"/>
       <c r="Q86" s="45" t="n"/>
       <c r="R86" s="45" t="n"/>
       <c r="S86" s="45" t="n"/>
-      <c r="T86" s="38" t="n"/>
-      <c r="U86" s="38" t="n"/>
+      <c r="T86" s="45" t="n"/>
+      <c r="U86" s="45" t="n"/>
       <c r="V86" s="38" t="n"/>
       <c r="W86" s="38" t="n"/>
     </row>
@@ -3632,18 +3758,18 @@
       <c r="G87" s="52" t="n"/>
       <c r="H87" s="50" t="n"/>
       <c r="I87" s="50" t="n"/>
-      <c r="J87" s="53" t="n"/>
+      <c r="J87" s="50" t="n"/>
       <c r="K87" s="50" t="n"/>
-      <c r="L87" s="50" t="n"/>
+      <c r="L87" s="53" t="n"/>
       <c r="M87" s="50" t="n"/>
-      <c r="N87" s="54" t="n"/>
+      <c r="N87" s="50" t="n"/>
       <c r="O87" s="50" t="n"/>
-      <c r="P87" s="50" t="n"/>
+      <c r="P87" s="54" t="n"/>
       <c r="Q87" s="50" t="n"/>
       <c r="R87" s="50" t="n"/>
       <c r="S87" s="50" t="n"/>
-      <c r="T87" s="38" t="n"/>
-      <c r="U87" s="38" t="n"/>
+      <c r="T87" s="50" t="n"/>
+      <c r="U87" s="50" t="n"/>
       <c r="V87" s="38" t="n"/>
       <c r="W87" s="38" t="n"/>
     </row>
@@ -3657,18 +3783,18 @@
       <c r="G88" s="47" t="n"/>
       <c r="H88" s="45" t="n"/>
       <c r="I88" s="45" t="n"/>
-      <c r="J88" s="48" t="n"/>
+      <c r="J88" s="45" t="n"/>
       <c r="K88" s="45" t="n"/>
-      <c r="L88" s="45" t="n"/>
+      <c r="L88" s="48" t="n"/>
       <c r="M88" s="45" t="n"/>
-      <c r="N88" s="49" t="n"/>
+      <c r="N88" s="45" t="n"/>
       <c r="O88" s="45" t="n"/>
-      <c r="P88" s="45" t="n"/>
+      <c r="P88" s="49" t="n"/>
       <c r="Q88" s="45" t="n"/>
       <c r="R88" s="45" t="n"/>
       <c r="S88" s="45" t="n"/>
-      <c r="T88" s="38" t="n"/>
-      <c r="U88" s="38" t="n"/>
+      <c r="T88" s="45" t="n"/>
+      <c r="U88" s="45" t="n"/>
       <c r="V88" s="38" t="n"/>
       <c r="W88" s="38" t="n"/>
     </row>
@@ -3682,18 +3808,18 @@
       <c r="G89" s="52" t="n"/>
       <c r="H89" s="50" t="n"/>
       <c r="I89" s="50" t="n"/>
-      <c r="J89" s="53" t="n"/>
+      <c r="J89" s="50" t="n"/>
       <c r="K89" s="50" t="n"/>
-      <c r="L89" s="50" t="n"/>
+      <c r="L89" s="53" t="n"/>
       <c r="M89" s="50" t="n"/>
-      <c r="N89" s="54" t="n"/>
+      <c r="N89" s="50" t="n"/>
       <c r="O89" s="50" t="n"/>
-      <c r="P89" s="50" t="n"/>
+      <c r="P89" s="54" t="n"/>
       <c r="Q89" s="50" t="n"/>
       <c r="R89" s="50" t="n"/>
       <c r="S89" s="50" t="n"/>
-      <c r="T89" s="38" t="n"/>
-      <c r="U89" s="38" t="n"/>
+      <c r="T89" s="50" t="n"/>
+      <c r="U89" s="50" t="n"/>
       <c r="V89" s="38" t="n"/>
       <c r="W89" s="38" t="n"/>
     </row>
@@ -3707,18 +3833,18 @@
       <c r="G90" s="47" t="n"/>
       <c r="H90" s="45" t="n"/>
       <c r="I90" s="45" t="n"/>
-      <c r="J90" s="48" t="n"/>
+      <c r="J90" s="45" t="n"/>
       <c r="K90" s="45" t="n"/>
-      <c r="L90" s="45" t="n"/>
+      <c r="L90" s="48" t="n"/>
       <c r="M90" s="45" t="n"/>
-      <c r="N90" s="49" t="n"/>
+      <c r="N90" s="45" t="n"/>
       <c r="O90" s="45" t="n"/>
-      <c r="P90" s="45" t="n"/>
+      <c r="P90" s="49" t="n"/>
       <c r="Q90" s="45" t="n"/>
       <c r="R90" s="45" t="n"/>
       <c r="S90" s="45" t="n"/>
-      <c r="T90" s="38" t="n"/>
-      <c r="U90" s="38" t="n"/>
+      <c r="T90" s="45" t="n"/>
+      <c r="U90" s="45" t="n"/>
       <c r="V90" s="38" t="n"/>
       <c r="W90" s="38" t="n"/>
     </row>
@@ -3732,18 +3858,18 @@
       <c r="G91" s="52" t="n"/>
       <c r="H91" s="50" t="n"/>
       <c r="I91" s="50" t="n"/>
-      <c r="J91" s="53" t="n"/>
+      <c r="J91" s="50" t="n"/>
       <c r="K91" s="50" t="n"/>
-      <c r="L91" s="50" t="n"/>
+      <c r="L91" s="53" t="n"/>
       <c r="M91" s="50" t="n"/>
-      <c r="N91" s="54" t="n"/>
+      <c r="N91" s="50" t="n"/>
       <c r="O91" s="50" t="n"/>
-      <c r="P91" s="50" t="n"/>
+      <c r="P91" s="54" t="n"/>
       <c r="Q91" s="50" t="n"/>
       <c r="R91" s="50" t="n"/>
       <c r="S91" s="50" t="n"/>
-      <c r="T91" s="38" t="n"/>
-      <c r="U91" s="38" t="n"/>
+      <c r="T91" s="50" t="n"/>
+      <c r="U91" s="50" t="n"/>
       <c r="V91" s="38" t="n"/>
       <c r="W91" s="38" t="n"/>
     </row>
@@ -3757,18 +3883,18 @@
       <c r="G92" s="47" t="n"/>
       <c r="H92" s="45" t="n"/>
       <c r="I92" s="45" t="n"/>
-      <c r="J92" s="48" t="n"/>
+      <c r="J92" s="45" t="n"/>
       <c r="K92" s="45" t="n"/>
-      <c r="L92" s="45" t="n"/>
+      <c r="L92" s="48" t="n"/>
       <c r="M92" s="45" t="n"/>
-      <c r="N92" s="49" t="n"/>
+      <c r="N92" s="45" t="n"/>
       <c r="O92" s="45" t="n"/>
-      <c r="P92" s="45" t="n"/>
+      <c r="P92" s="49" t="n"/>
       <c r="Q92" s="45" t="n"/>
       <c r="R92" s="45" t="n"/>
       <c r="S92" s="45" t="n"/>
-      <c r="T92" s="38" t="n"/>
-      <c r="U92" s="38" t="n"/>
+      <c r="T92" s="45" t="n"/>
+      <c r="U92" s="45" t="n"/>
       <c r="V92" s="38" t="n"/>
       <c r="W92" s="38" t="n"/>
     </row>
@@ -3782,18 +3908,18 @@
       <c r="G93" s="52" t="n"/>
       <c r="H93" s="50" t="n"/>
       <c r="I93" s="50" t="n"/>
-      <c r="J93" s="53" t="n"/>
+      <c r="J93" s="50" t="n"/>
       <c r="K93" s="50" t="n"/>
-      <c r="L93" s="50" t="n"/>
+      <c r="L93" s="53" t="n"/>
       <c r="M93" s="50" t="n"/>
-      <c r="N93" s="54" t="n"/>
+      <c r="N93" s="50" t="n"/>
       <c r="O93" s="50" t="n"/>
-      <c r="P93" s="50" t="n"/>
+      <c r="P93" s="54" t="n"/>
       <c r="Q93" s="50" t="n"/>
       <c r="R93" s="50" t="n"/>
       <c r="S93" s="50" t="n"/>
-      <c r="T93" s="38" t="n"/>
-      <c r="U93" s="38" t="n"/>
+      <c r="T93" s="50" t="n"/>
+      <c r="U93" s="50" t="n"/>
       <c r="V93" s="38" t="n"/>
       <c r="W93" s="38" t="n"/>
     </row>
@@ -3807,18 +3933,18 @@
       <c r="G94" s="47" t="n"/>
       <c r="H94" s="45" t="n"/>
       <c r="I94" s="45" t="n"/>
-      <c r="J94" s="48" t="n"/>
+      <c r="J94" s="45" t="n"/>
       <c r="K94" s="45" t="n"/>
-      <c r="L94" s="45" t="n"/>
+      <c r="L94" s="48" t="n"/>
       <c r="M94" s="45" t="n"/>
-      <c r="N94" s="49" t="n"/>
+      <c r="N94" s="45" t="n"/>
       <c r="O94" s="45" t="n"/>
-      <c r="P94" s="45" t="n"/>
+      <c r="P94" s="49" t="n"/>
       <c r="Q94" s="45" t="n"/>
       <c r="R94" s="45" t="n"/>
       <c r="S94" s="45" t="n"/>
-      <c r="T94" s="38" t="n"/>
-      <c r="U94" s="38" t="n"/>
+      <c r="T94" s="45" t="n"/>
+      <c r="U94" s="45" t="n"/>
       <c r="V94" s="38" t="n"/>
       <c r="W94" s="38" t="n"/>
     </row>
@@ -3832,18 +3958,18 @@
       <c r="G95" s="52" t="n"/>
       <c r="H95" s="50" t="n"/>
       <c r="I95" s="50" t="n"/>
-      <c r="J95" s="53" t="n"/>
+      <c r="J95" s="50" t="n"/>
       <c r="K95" s="50" t="n"/>
-      <c r="L95" s="50" t="n"/>
+      <c r="L95" s="53" t="n"/>
       <c r="M95" s="50" t="n"/>
-      <c r="N95" s="54" t="n"/>
+      <c r="N95" s="50" t="n"/>
       <c r="O95" s="50" t="n"/>
-      <c r="P95" s="50" t="n"/>
+      <c r="P95" s="54" t="n"/>
       <c r="Q95" s="50" t="n"/>
       <c r="R95" s="50" t="n"/>
       <c r="S95" s="50" t="n"/>
-      <c r="T95" s="38" t="n"/>
-      <c r="U95" s="38" t="n"/>
+      <c r="T95" s="50" t="n"/>
+      <c r="U95" s="50" t="n"/>
       <c r="V95" s="38" t="n"/>
       <c r="W95" s="38" t="n"/>
     </row>
@@ -3857,18 +3983,18 @@
       <c r="G96" s="47" t="n"/>
       <c r="H96" s="45" t="n"/>
       <c r="I96" s="45" t="n"/>
-      <c r="J96" s="48" t="n"/>
+      <c r="J96" s="45" t="n"/>
       <c r="K96" s="45" t="n"/>
-      <c r="L96" s="45" t="n"/>
+      <c r="L96" s="48" t="n"/>
       <c r="M96" s="45" t="n"/>
-      <c r="N96" s="49" t="n"/>
+      <c r="N96" s="45" t="n"/>
       <c r="O96" s="45" t="n"/>
-      <c r="P96" s="45" t="n"/>
+      <c r="P96" s="49" t="n"/>
       <c r="Q96" s="45" t="n"/>
       <c r="R96" s="45" t="n"/>
       <c r="S96" s="45" t="n"/>
-      <c r="T96" s="38" t="n"/>
-      <c r="U96" s="38" t="n"/>
+      <c r="T96" s="45" t="n"/>
+      <c r="U96" s="45" t="n"/>
       <c r="V96" s="38" t="n"/>
       <c r="W96" s="38" t="n"/>
     </row>
@@ -3882,18 +4008,18 @@
       <c r="G97" s="52" t="n"/>
       <c r="H97" s="50" t="n"/>
       <c r="I97" s="50" t="n"/>
-      <c r="J97" s="53" t="n"/>
+      <c r="J97" s="50" t="n"/>
       <c r="K97" s="50" t="n"/>
-      <c r="L97" s="50" t="n"/>
+      <c r="L97" s="53" t="n"/>
       <c r="M97" s="50" t="n"/>
-      <c r="N97" s="54" t="n"/>
+      <c r="N97" s="50" t="n"/>
       <c r="O97" s="50" t="n"/>
-      <c r="P97" s="50" t="n"/>
+      <c r="P97" s="54" t="n"/>
       <c r="Q97" s="50" t="n"/>
       <c r="R97" s="50" t="n"/>
       <c r="S97" s="50" t="n"/>
-      <c r="T97" s="38" t="n"/>
-      <c r="U97" s="38" t="n"/>
+      <c r="T97" s="50" t="n"/>
+      <c r="U97" s="50" t="n"/>
       <c r="V97" s="38" t="n"/>
       <c r="W97" s="38" t="n"/>
     </row>
@@ -3907,18 +4033,18 @@
       <c r="G98" s="47" t="n"/>
       <c r="H98" s="45" t="n"/>
       <c r="I98" s="45" t="n"/>
-      <c r="J98" s="48" t="n"/>
+      <c r="J98" s="45" t="n"/>
       <c r="K98" s="45" t="n"/>
-      <c r="L98" s="45" t="n"/>
+      <c r="L98" s="48" t="n"/>
       <c r="M98" s="45" t="n"/>
-      <c r="N98" s="49" t="n"/>
+      <c r="N98" s="45" t="n"/>
       <c r="O98" s="45" t="n"/>
-      <c r="P98" s="45" t="n"/>
+      <c r="P98" s="49" t="n"/>
       <c r="Q98" s="45" t="n"/>
       <c r="R98" s="45" t="n"/>
       <c r="S98" s="45" t="n"/>
-      <c r="T98" s="38" t="n"/>
-      <c r="U98" s="38" t="n"/>
+      <c r="T98" s="45" t="n"/>
+      <c r="U98" s="45" t="n"/>
       <c r="V98" s="38" t="n"/>
       <c r="W98" s="38" t="n"/>
     </row>
@@ -3932,18 +4058,18 @@
       <c r="G99" s="52" t="n"/>
       <c r="H99" s="50" t="n"/>
       <c r="I99" s="50" t="n"/>
-      <c r="J99" s="53" t="n"/>
+      <c r="J99" s="50" t="n"/>
       <c r="K99" s="50" t="n"/>
-      <c r="L99" s="50" t="n"/>
+      <c r="L99" s="53" t="n"/>
       <c r="M99" s="50" t="n"/>
-      <c r="N99" s="54" t="n"/>
+      <c r="N99" s="50" t="n"/>
       <c r="O99" s="50" t="n"/>
-      <c r="P99" s="50" t="n"/>
+      <c r="P99" s="54" t="n"/>
       <c r="Q99" s="50" t="n"/>
       <c r="R99" s="50" t="n"/>
       <c r="S99" s="50" t="n"/>
-      <c r="T99" s="38" t="n"/>
-      <c r="U99" s="38" t="n"/>
+      <c r="T99" s="50" t="n"/>
+      <c r="U99" s="50" t="n"/>
       <c r="V99" s="38" t="n"/>
       <c r="W99" s="38" t="n"/>
     </row>
@@ -3957,18 +4083,18 @@
       <c r="G100" s="47" t="n"/>
       <c r="H100" s="45" t="n"/>
       <c r="I100" s="45" t="n"/>
-      <c r="J100" s="48" t="n"/>
+      <c r="J100" s="45" t="n"/>
       <c r="K100" s="45" t="n"/>
-      <c r="L100" s="45" t="n"/>
+      <c r="L100" s="48" t="n"/>
       <c r="M100" s="45" t="n"/>
-      <c r="N100" s="49" t="n"/>
+      <c r="N100" s="45" t="n"/>
       <c r="O100" s="45" t="n"/>
-      <c r="P100" s="45" t="n"/>
+      <c r="P100" s="49" t="n"/>
       <c r="Q100" s="45" t="n"/>
       <c r="R100" s="45" t="n"/>
       <c r="S100" s="45" t="n"/>
-      <c r="T100" s="38" t="n"/>
-      <c r="U100" s="38" t="n"/>
+      <c r="T100" s="45" t="n"/>
+      <c r="U100" s="45" t="n"/>
       <c r="V100" s="38" t="n"/>
       <c r="W100" s="38" t="n"/>
     </row>
@@ -3982,18 +4108,18 @@
       <c r="G101" s="52" t="n"/>
       <c r="H101" s="50" t="n"/>
       <c r="I101" s="50" t="n"/>
-      <c r="J101" s="53" t="n"/>
+      <c r="J101" s="50" t="n"/>
       <c r="K101" s="50" t="n"/>
-      <c r="L101" s="50" t="n"/>
+      <c r="L101" s="53" t="n"/>
       <c r="M101" s="50" t="n"/>
-      <c r="N101" s="54" t="n"/>
+      <c r="N101" s="50" t="n"/>
       <c r="O101" s="50" t="n"/>
-      <c r="P101" s="50" t="n"/>
+      <c r="P101" s="54" t="n"/>
       <c r="Q101" s="50" t="n"/>
       <c r="R101" s="50" t="n"/>
       <c r="S101" s="50" t="n"/>
-      <c r="T101" s="38" t="n"/>
-      <c r="U101" s="38" t="n"/>
+      <c r="T101" s="50" t="n"/>
+      <c r="U101" s="50" t="n"/>
       <c r="V101" s="38" t="n"/>
       <c r="W101" s="38" t="n"/>
     </row>
@@ -4007,18 +4133,18 @@
       <c r="G102" s="47" t="n"/>
       <c r="H102" s="45" t="n"/>
       <c r="I102" s="45" t="n"/>
-      <c r="J102" s="48" t="n"/>
+      <c r="J102" s="45" t="n"/>
       <c r="K102" s="45" t="n"/>
-      <c r="L102" s="45" t="n"/>
+      <c r="L102" s="48" t="n"/>
       <c r="M102" s="45" t="n"/>
-      <c r="N102" s="49" t="n"/>
+      <c r="N102" s="45" t="n"/>
       <c r="O102" s="45" t="n"/>
-      <c r="P102" s="45" t="n"/>
+      <c r="P102" s="49" t="n"/>
       <c r="Q102" s="45" t="n"/>
       <c r="R102" s="45" t="n"/>
       <c r="S102" s="45" t="n"/>
-      <c r="T102" s="38" t="n"/>
-      <c r="U102" s="38" t="n"/>
+      <c r="T102" s="45" t="n"/>
+      <c r="U102" s="45" t="n"/>
       <c r="V102" s="38" t="n"/>
       <c r="W102" s="38" t="n"/>
     </row>
@@ -4032,18 +4158,18 @@
       <c r="G103" s="52" t="n"/>
       <c r="H103" s="50" t="n"/>
       <c r="I103" s="50" t="n"/>
-      <c r="J103" s="53" t="n"/>
+      <c r="J103" s="50" t="n"/>
       <c r="K103" s="50" t="n"/>
-      <c r="L103" s="50" t="n"/>
+      <c r="L103" s="53" t="n"/>
       <c r="M103" s="50" t="n"/>
-      <c r="N103" s="54" t="n"/>
+      <c r="N103" s="50" t="n"/>
       <c r="O103" s="50" t="n"/>
-      <c r="P103" s="50" t="n"/>
+      <c r="P103" s="54" t="n"/>
       <c r="Q103" s="50" t="n"/>
       <c r="R103" s="50" t="n"/>
       <c r="S103" s="50" t="n"/>
-      <c r="T103" s="38" t="n"/>
-      <c r="U103" s="38" t="n"/>
+      <c r="T103" s="50" t="n"/>
+      <c r="U103" s="50" t="n"/>
       <c r="V103" s="38" t="n"/>
       <c r="W103" s="38" t="n"/>
     </row>
@@ -4057,18 +4183,18 @@
       <c r="G104" s="47" t="n"/>
       <c r="H104" s="45" t="n"/>
       <c r="I104" s="45" t="n"/>
-      <c r="J104" s="48" t="n"/>
+      <c r="J104" s="45" t="n"/>
       <c r="K104" s="45" t="n"/>
-      <c r="L104" s="45" t="n"/>
+      <c r="L104" s="48" t="n"/>
       <c r="M104" s="45" t="n"/>
-      <c r="N104" s="49" t="n"/>
+      <c r="N104" s="45" t="n"/>
       <c r="O104" s="45" t="n"/>
-      <c r="P104" s="45" t="n"/>
+      <c r="P104" s="49" t="n"/>
       <c r="Q104" s="45" t="n"/>
       <c r="R104" s="45" t="n"/>
       <c r="S104" s="45" t="n"/>
-      <c r="T104" s="38" t="n"/>
-      <c r="U104" s="38" t="n"/>
+      <c r="T104" s="45" t="n"/>
+      <c r="U104" s="45" t="n"/>
       <c r="V104" s="38" t="n"/>
       <c r="W104" s="38" t="n"/>
     </row>
@@ -4082,18 +4208,18 @@
       <c r="G105" s="52" t="n"/>
       <c r="H105" s="50" t="n"/>
       <c r="I105" s="50" t="n"/>
-      <c r="J105" s="53" t="n"/>
+      <c r="J105" s="50" t="n"/>
       <c r="K105" s="50" t="n"/>
-      <c r="L105" s="50" t="n"/>
+      <c r="L105" s="53" t="n"/>
       <c r="M105" s="50" t="n"/>
-      <c r="N105" s="54" t="n"/>
+      <c r="N105" s="50" t="n"/>
       <c r="O105" s="50" t="n"/>
-      <c r="P105" s="50" t="n"/>
+      <c r="P105" s="54" t="n"/>
       <c r="Q105" s="50" t="n"/>
       <c r="R105" s="50" t="n"/>
       <c r="S105" s="50" t="n"/>
-      <c r="T105" s="38" t="n"/>
-      <c r="U105" s="38" t="n"/>
+      <c r="T105" s="50" t="n"/>
+      <c r="U105" s="50" t="n"/>
       <c r="V105" s="38" t="n"/>
       <c r="W105" s="38" t="n"/>
     </row>
@@ -4107,18 +4233,18 @@
       <c r="G106" s="47" t="n"/>
       <c r="H106" s="45" t="n"/>
       <c r="I106" s="45" t="n"/>
-      <c r="J106" s="48" t="n"/>
+      <c r="J106" s="45" t="n"/>
       <c r="K106" s="45" t="n"/>
-      <c r="L106" s="45" t="n"/>
+      <c r="L106" s="48" t="n"/>
       <c r="M106" s="45" t="n"/>
-      <c r="N106" s="49" t="n"/>
+      <c r="N106" s="45" t="n"/>
       <c r="O106" s="45" t="n"/>
-      <c r="P106" s="45" t="n"/>
+      <c r="P106" s="49" t="n"/>
       <c r="Q106" s="45" t="n"/>
       <c r="R106" s="45" t="n"/>
       <c r="S106" s="45" t="n"/>
-      <c r="T106" s="38" t="n"/>
-      <c r="U106" s="38" t="n"/>
+      <c r="T106" s="45" t="n"/>
+      <c r="U106" s="45" t="n"/>
       <c r="V106" s="38" t="n"/>
       <c r="W106" s="38" t="n"/>
     </row>
@@ -4132,18 +4258,18 @@
       <c r="G107" s="52" t="n"/>
       <c r="H107" s="50" t="n"/>
       <c r="I107" s="50" t="n"/>
-      <c r="J107" s="53" t="n"/>
+      <c r="J107" s="50" t="n"/>
       <c r="K107" s="50" t="n"/>
-      <c r="L107" s="50" t="n"/>
+      <c r="L107" s="53" t="n"/>
       <c r="M107" s="50" t="n"/>
-      <c r="N107" s="54" t="n"/>
+      <c r="N107" s="50" t="n"/>
       <c r="O107" s="50" t="n"/>
-      <c r="P107" s="50" t="n"/>
+      <c r="P107" s="54" t="n"/>
       <c r="Q107" s="50" t="n"/>
       <c r="R107" s="50" t="n"/>
       <c r="S107" s="50" t="n"/>
-      <c r="T107" s="38" t="n"/>
-      <c r="U107" s="38" t="n"/>
+      <c r="T107" s="50" t="n"/>
+      <c r="U107" s="50" t="n"/>
       <c r="V107" s="38" t="n"/>
       <c r="W107" s="38" t="n"/>
     </row>
@@ -4157,18 +4283,18 @@
       <c r="G108" s="47" t="n"/>
       <c r="H108" s="45" t="n"/>
       <c r="I108" s="45" t="n"/>
-      <c r="J108" s="48" t="n"/>
+      <c r="J108" s="45" t="n"/>
       <c r="K108" s="45" t="n"/>
-      <c r="L108" s="45" t="n"/>
+      <c r="L108" s="48" t="n"/>
       <c r="M108" s="45" t="n"/>
-      <c r="N108" s="49" t="n"/>
+      <c r="N108" s="45" t="n"/>
       <c r="O108" s="45" t="n"/>
-      <c r="P108" s="45" t="n"/>
+      <c r="P108" s="49" t="n"/>
       <c r="Q108" s="45" t="n"/>
       <c r="R108" s="45" t="n"/>
       <c r="S108" s="45" t="n"/>
-      <c r="T108" s="38" t="n"/>
-      <c r="U108" s="38" t="n"/>
+      <c r="T108" s="45" t="n"/>
+      <c r="U108" s="45" t="n"/>
       <c r="V108" s="38" t="n"/>
       <c r="W108" s="38" t="n"/>
     </row>
@@ -4182,18 +4308,18 @@
       <c r="G109" s="52" t="n"/>
       <c r="H109" s="50" t="n"/>
       <c r="I109" s="50" t="n"/>
-      <c r="J109" s="53" t="n"/>
+      <c r="J109" s="50" t="n"/>
       <c r="K109" s="50" t="n"/>
-      <c r="L109" s="50" t="n"/>
+      <c r="L109" s="53" t="n"/>
       <c r="M109" s="50" t="n"/>
-      <c r="N109" s="54" t="n"/>
+      <c r="N109" s="50" t="n"/>
       <c r="O109" s="50" t="n"/>
-      <c r="P109" s="50" t="n"/>
+      <c r="P109" s="54" t="n"/>
       <c r="Q109" s="50" t="n"/>
       <c r="R109" s="50" t="n"/>
       <c r="S109" s="50" t="n"/>
-      <c r="T109" s="38" t="n"/>
-      <c r="U109" s="38" t="n"/>
+      <c r="T109" s="50" t="n"/>
+      <c r="U109" s="50" t="n"/>
       <c r="V109" s="38" t="n"/>
       <c r="W109" s="38" t="n"/>
     </row>
@@ -4207,18 +4333,18 @@
       <c r="G110" s="47" t="n"/>
       <c r="H110" s="45" t="n"/>
       <c r="I110" s="45" t="n"/>
-      <c r="J110" s="48" t="n"/>
+      <c r="J110" s="45" t="n"/>
       <c r="K110" s="45" t="n"/>
-      <c r="L110" s="45" t="n"/>
+      <c r="L110" s="48" t="n"/>
       <c r="M110" s="45" t="n"/>
-      <c r="N110" s="49" t="n"/>
+      <c r="N110" s="45" t="n"/>
       <c r="O110" s="45" t="n"/>
-      <c r="P110" s="45" t="n"/>
+      <c r="P110" s="49" t="n"/>
       <c r="Q110" s="45" t="n"/>
       <c r="R110" s="45" t="n"/>
       <c r="S110" s="45" t="n"/>
-      <c r="T110" s="38" t="n"/>
-      <c r="U110" s="38" t="n"/>
+      <c r="T110" s="45" t="n"/>
+      <c r="U110" s="45" t="n"/>
       <c r="V110" s="38" t="n"/>
       <c r="W110" s="38" t="n"/>
     </row>
@@ -4232,18 +4358,18 @@
       <c r="G111" s="52" t="n"/>
       <c r="H111" s="50" t="n"/>
       <c r="I111" s="50" t="n"/>
-      <c r="J111" s="53" t="n"/>
+      <c r="J111" s="50" t="n"/>
       <c r="K111" s="50" t="n"/>
-      <c r="L111" s="50" t="n"/>
+      <c r="L111" s="53" t="n"/>
       <c r="M111" s="50" t="n"/>
-      <c r="N111" s="54" t="n"/>
+      <c r="N111" s="50" t="n"/>
       <c r="O111" s="50" t="n"/>
-      <c r="P111" s="50" t="n"/>
+      <c r="P111" s="54" t="n"/>
       <c r="Q111" s="50" t="n"/>
       <c r="R111" s="50" t="n"/>
       <c r="S111" s="50" t="n"/>
-      <c r="T111" s="38" t="n"/>
-      <c r="U111" s="38" t="n"/>
+      <c r="T111" s="50" t="n"/>
+      <c r="U111" s="50" t="n"/>
       <c r="V111" s="38" t="n"/>
       <c r="W111" s="38" t="n"/>
     </row>
@@ -4257,18 +4383,18 @@
       <c r="G112" s="47" t="n"/>
       <c r="H112" s="45" t="n"/>
       <c r="I112" s="45" t="n"/>
-      <c r="J112" s="48" t="n"/>
+      <c r="J112" s="45" t="n"/>
       <c r="K112" s="45" t="n"/>
-      <c r="L112" s="45" t="n"/>
+      <c r="L112" s="48" t="n"/>
       <c r="M112" s="45" t="n"/>
-      <c r="N112" s="49" t="n"/>
+      <c r="N112" s="45" t="n"/>
       <c r="O112" s="45" t="n"/>
-      <c r="P112" s="45" t="n"/>
+      <c r="P112" s="49" t="n"/>
       <c r="Q112" s="45" t="n"/>
       <c r="R112" s="45" t="n"/>
       <c r="S112" s="45" t="n"/>
-      <c r="T112" s="38" t="n"/>
-      <c r="U112" s="38" t="n"/>
+      <c r="T112" s="45" t="n"/>
+      <c r="U112" s="45" t="n"/>
       <c r="V112" s="38" t="n"/>
       <c r="W112" s="38" t="n"/>
     </row>
@@ -4282,18 +4408,18 @@
       <c r="G113" s="52" t="n"/>
       <c r="H113" s="50" t="n"/>
       <c r="I113" s="50" t="n"/>
-      <c r="J113" s="53" t="n"/>
+      <c r="J113" s="50" t="n"/>
       <c r="K113" s="50" t="n"/>
-      <c r="L113" s="50" t="n"/>
+      <c r="L113" s="53" t="n"/>
       <c r="M113" s="50" t="n"/>
-      <c r="N113" s="54" t="n"/>
+      <c r="N113" s="50" t="n"/>
       <c r="O113" s="50" t="n"/>
-      <c r="P113" s="50" t="n"/>
+      <c r="P113" s="54" t="n"/>
       <c r="Q113" s="50" t="n"/>
       <c r="R113" s="50" t="n"/>
       <c r="S113" s="50" t="n"/>
-      <c r="T113" s="38" t="n"/>
-      <c r="U113" s="38" t="n"/>
+      <c r="T113" s="50" t="n"/>
+      <c r="U113" s="50" t="n"/>
       <c r="V113" s="38" t="n"/>
       <c r="W113" s="38" t="n"/>
     </row>
@@ -4307,18 +4433,18 @@
       <c r="G114" s="47" t="n"/>
       <c r="H114" s="45" t="n"/>
       <c r="I114" s="45" t="n"/>
-      <c r="J114" s="48" t="n"/>
+      <c r="J114" s="45" t="n"/>
       <c r="K114" s="45" t="n"/>
-      <c r="L114" s="45" t="n"/>
+      <c r="L114" s="48" t="n"/>
       <c r="M114" s="45" t="n"/>
-      <c r="N114" s="49" t="n"/>
+      <c r="N114" s="45" t="n"/>
       <c r="O114" s="45" t="n"/>
-      <c r="P114" s="45" t="n"/>
+      <c r="P114" s="49" t="n"/>
       <c r="Q114" s="45" t="n"/>
       <c r="R114" s="45" t="n"/>
       <c r="S114" s="45" t="n"/>
-      <c r="T114" s="38" t="n"/>
-      <c r="U114" s="38" t="n"/>
+      <c r="T114" s="45" t="n"/>
+      <c r="U114" s="45" t="n"/>
       <c r="V114" s="38" t="n"/>
       <c r="W114" s="38" t="n"/>
     </row>
@@ -4332,18 +4458,18 @@
       <c r="G115" s="52" t="n"/>
       <c r="H115" s="50" t="n"/>
       <c r="I115" s="50" t="n"/>
-      <c r="J115" s="53" t="n"/>
+      <c r="J115" s="50" t="n"/>
       <c r="K115" s="50" t="n"/>
-      <c r="L115" s="50" t="n"/>
+      <c r="L115" s="53" t="n"/>
       <c r="M115" s="50" t="n"/>
-      <c r="N115" s="54" t="n"/>
+      <c r="N115" s="50" t="n"/>
       <c r="O115" s="50" t="n"/>
-      <c r="P115" s="50" t="n"/>
+      <c r="P115" s="54" t="n"/>
       <c r="Q115" s="50" t="n"/>
       <c r="R115" s="50" t="n"/>
       <c r="S115" s="50" t="n"/>
-      <c r="T115" s="38" t="n"/>
-      <c r="U115" s="38" t="n"/>
+      <c r="T115" s="50" t="n"/>
+      <c r="U115" s="50" t="n"/>
       <c r="V115" s="38" t="n"/>
       <c r="W115" s="38" t="n"/>
     </row>
@@ -4357,18 +4483,18 @@
       <c r="G116" s="47" t="n"/>
       <c r="H116" s="45" t="n"/>
       <c r="I116" s="45" t="n"/>
-      <c r="J116" s="48" t="n"/>
+      <c r="J116" s="45" t="n"/>
       <c r="K116" s="45" t="n"/>
-      <c r="L116" s="45" t="n"/>
+      <c r="L116" s="48" t="n"/>
       <c r="M116" s="45" t="n"/>
-      <c r="N116" s="49" t="n"/>
+      <c r="N116" s="45" t="n"/>
       <c r="O116" s="45" t="n"/>
-      <c r="P116" s="45" t="n"/>
+      <c r="P116" s="49" t="n"/>
       <c r="Q116" s="45" t="n"/>
       <c r="R116" s="45" t="n"/>
       <c r="S116" s="45" t="n"/>
-      <c r="T116" s="38" t="n"/>
-      <c r="U116" s="38" t="n"/>
+      <c r="T116" s="45" t="n"/>
+      <c r="U116" s="45" t="n"/>
       <c r="V116" s="38" t="n"/>
       <c r="W116" s="38" t="n"/>
     </row>
@@ -4382,18 +4508,18 @@
       <c r="G117" s="52" t="n"/>
       <c r="H117" s="50" t="n"/>
       <c r="I117" s="50" t="n"/>
-      <c r="J117" s="53" t="n"/>
+      <c r="J117" s="50" t="n"/>
       <c r="K117" s="50" t="n"/>
-      <c r="L117" s="50" t="n"/>
+      <c r="L117" s="53" t="n"/>
       <c r="M117" s="50" t="n"/>
-      <c r="N117" s="54" t="n"/>
+      <c r="N117" s="50" t="n"/>
       <c r="O117" s="50" t="n"/>
-      <c r="P117" s="50" t="n"/>
+      <c r="P117" s="54" t="n"/>
       <c r="Q117" s="50" t="n"/>
       <c r="R117" s="50" t="n"/>
       <c r="S117" s="50" t="n"/>
-      <c r="T117" s="38" t="n"/>
-      <c r="U117" s="38" t="n"/>
+      <c r="T117" s="50" t="n"/>
+      <c r="U117" s="50" t="n"/>
       <c r="V117" s="38" t="n"/>
       <c r="W117" s="38" t="n"/>
     </row>
@@ -4407,18 +4533,18 @@
       <c r="G118" s="47" t="n"/>
       <c r="H118" s="45" t="n"/>
       <c r="I118" s="45" t="n"/>
-      <c r="J118" s="48" t="n"/>
+      <c r="J118" s="45" t="n"/>
       <c r="K118" s="45" t="n"/>
-      <c r="L118" s="45" t="n"/>
+      <c r="L118" s="48" t="n"/>
       <c r="M118" s="45" t="n"/>
-      <c r="N118" s="49" t="n"/>
+      <c r="N118" s="45" t="n"/>
       <c r="O118" s="45" t="n"/>
-      <c r="P118" s="45" t="n"/>
+      <c r="P118" s="49" t="n"/>
       <c r="Q118" s="45" t="n"/>
       <c r="R118" s="45" t="n"/>
       <c r="S118" s="45" t="n"/>
-      <c r="T118" s="38" t="n"/>
-      <c r="U118" s="38" t="n"/>
+      <c r="T118" s="45" t="n"/>
+      <c r="U118" s="45" t="n"/>
       <c r="V118" s="38" t="n"/>
       <c r="W118" s="38" t="n"/>
     </row>
@@ -4432,18 +4558,18 @@
       <c r="G119" s="52" t="n"/>
       <c r="H119" s="50" t="n"/>
       <c r="I119" s="50" t="n"/>
-      <c r="J119" s="53" t="n"/>
+      <c r="J119" s="50" t="n"/>
       <c r="K119" s="50" t="n"/>
-      <c r="L119" s="50" t="n"/>
+      <c r="L119" s="53" t="n"/>
       <c r="M119" s="50" t="n"/>
-      <c r="N119" s="54" t="n"/>
+      <c r="N119" s="50" t="n"/>
       <c r="O119" s="50" t="n"/>
-      <c r="P119" s="50" t="n"/>
+      <c r="P119" s="54" t="n"/>
       <c r="Q119" s="50" t="n"/>
       <c r="R119" s="50" t="n"/>
       <c r="S119" s="50" t="n"/>
-      <c r="T119" s="38" t="n"/>
-      <c r="U119" s="38" t="n"/>
+      <c r="T119" s="50" t="n"/>
+      <c r="U119" s="50" t="n"/>
       <c r="V119" s="38" t="n"/>
       <c r="W119" s="38" t="n"/>
     </row>
@@ -4457,18 +4583,18 @@
       <c r="G120" s="47" t="n"/>
       <c r="H120" s="45" t="n"/>
       <c r="I120" s="45" t="n"/>
-      <c r="J120" s="48" t="n"/>
+      <c r="J120" s="45" t="n"/>
       <c r="K120" s="45" t="n"/>
-      <c r="L120" s="45" t="n"/>
+      <c r="L120" s="48" t="n"/>
       <c r="M120" s="45" t="n"/>
-      <c r="N120" s="49" t="n"/>
+      <c r="N120" s="45" t="n"/>
       <c r="O120" s="45" t="n"/>
-      <c r="P120" s="45" t="n"/>
+      <c r="P120" s="49" t="n"/>
       <c r="Q120" s="45" t="n"/>
       <c r="R120" s="45" t="n"/>
       <c r="S120" s="45" t="n"/>
-      <c r="T120" s="38" t="n"/>
-      <c r="U120" s="38" t="n"/>
+      <c r="T120" s="45" t="n"/>
+      <c r="U120" s="45" t="n"/>
       <c r="V120" s="38" t="n"/>
       <c r="W120" s="38" t="n"/>
     </row>
@@ -4482,18 +4608,18 @@
       <c r="G121" s="52" t="n"/>
       <c r="H121" s="50" t="n"/>
       <c r="I121" s="50" t="n"/>
-      <c r="J121" s="53" t="n"/>
+      <c r="J121" s="50" t="n"/>
       <c r="K121" s="50" t="n"/>
-      <c r="L121" s="50" t="n"/>
+      <c r="L121" s="53" t="n"/>
       <c r="M121" s="50" t="n"/>
-      <c r="N121" s="54" t="n"/>
+      <c r="N121" s="50" t="n"/>
       <c r="O121" s="50" t="n"/>
-      <c r="P121" s="50" t="n"/>
+      <c r="P121" s="54" t="n"/>
       <c r="Q121" s="50" t="n"/>
       <c r="R121" s="50" t="n"/>
       <c r="S121" s="50" t="n"/>
-      <c r="T121" s="38" t="n"/>
-      <c r="U121" s="38" t="n"/>
+      <c r="T121" s="50" t="n"/>
+      <c r="U121" s="50" t="n"/>
       <c r="V121" s="38" t="n"/>
       <c r="W121" s="38" t="n"/>
     </row>
@@ -4507,18 +4633,18 @@
       <c r="G122" s="47" t="n"/>
       <c r="H122" s="45" t="n"/>
       <c r="I122" s="45" t="n"/>
-      <c r="J122" s="48" t="n"/>
+      <c r="J122" s="45" t="n"/>
       <c r="K122" s="45" t="n"/>
-      <c r="L122" s="45" t="n"/>
+      <c r="L122" s="48" t="n"/>
       <c r="M122" s="45" t="n"/>
-      <c r="N122" s="49" t="n"/>
+      <c r="N122" s="45" t="n"/>
       <c r="O122" s="45" t="n"/>
-      <c r="P122" s="45" t="n"/>
+      <c r="P122" s="49" t="n"/>
       <c r="Q122" s="45" t="n"/>
       <c r="R122" s="45" t="n"/>
       <c r="S122" s="45" t="n"/>
-      <c r="T122" s="38" t="n"/>
-      <c r="U122" s="38" t="n"/>
+      <c r="T122" s="45" t="n"/>
+      <c r="U122" s="45" t="n"/>
       <c r="V122" s="38" t="n"/>
       <c r="W122" s="38" t="n"/>
     </row>
@@ -4532,18 +4658,18 @@
       <c r="G123" s="52" t="n"/>
       <c r="H123" s="50" t="n"/>
       <c r="I123" s="50" t="n"/>
-      <c r="J123" s="53" t="n"/>
+      <c r="J123" s="50" t="n"/>
       <c r="K123" s="50" t="n"/>
-      <c r="L123" s="50" t="n"/>
+      <c r="L123" s="53" t="n"/>
       <c r="M123" s="50" t="n"/>
-      <c r="N123" s="54" t="n"/>
+      <c r="N123" s="50" t="n"/>
       <c r="O123" s="50" t="n"/>
-      <c r="P123" s="50" t="n"/>
+      <c r="P123" s="54" t="n"/>
       <c r="Q123" s="50" t="n"/>
       <c r="R123" s="50" t="n"/>
       <c r="S123" s="50" t="n"/>
-      <c r="T123" s="38" t="n"/>
-      <c r="U123" s="38" t="n"/>
+      <c r="T123" s="50" t="n"/>
+      <c r="U123" s="50" t="n"/>
       <c r="V123" s="38" t="n"/>
       <c r="W123" s="38" t="n"/>
     </row>
@@ -4557,18 +4683,18 @@
       <c r="G124" s="47" t="n"/>
       <c r="H124" s="45" t="n"/>
       <c r="I124" s="45" t="n"/>
-      <c r="J124" s="48" t="n"/>
+      <c r="J124" s="45" t="n"/>
       <c r="K124" s="45" t="n"/>
-      <c r="L124" s="45" t="n"/>
+      <c r="L124" s="48" t="n"/>
       <c r="M124" s="45" t="n"/>
-      <c r="N124" s="49" t="n"/>
+      <c r="N124" s="45" t="n"/>
       <c r="O124" s="45" t="n"/>
-      <c r="P124" s="45" t="n"/>
+      <c r="P124" s="49" t="n"/>
       <c r="Q124" s="45" t="n"/>
       <c r="R124" s="45" t="n"/>
       <c r="S124" s="45" t="n"/>
-      <c r="T124" s="38" t="n"/>
-      <c r="U124" s="38" t="n"/>
+      <c r="T124" s="45" t="n"/>
+      <c r="U124" s="45" t="n"/>
       <c r="V124" s="38" t="n"/>
       <c r="W124" s="38" t="n"/>
     </row>
@@ -4582,18 +4708,18 @@
       <c r="G125" s="52" t="n"/>
       <c r="H125" s="50" t="n"/>
       <c r="I125" s="50" t="n"/>
-      <c r="J125" s="53" t="n"/>
+      <c r="J125" s="50" t="n"/>
       <c r="K125" s="50" t="n"/>
-      <c r="L125" s="50" t="n"/>
+      <c r="L125" s="53" t="n"/>
       <c r="M125" s="50" t="n"/>
-      <c r="N125" s="54" t="n"/>
+      <c r="N125" s="50" t="n"/>
       <c r="O125" s="50" t="n"/>
-      <c r="P125" s="50" t="n"/>
+      <c r="P125" s="54" t="n"/>
       <c r="Q125" s="50" t="n"/>
       <c r="R125" s="50" t="n"/>
       <c r="S125" s="50" t="n"/>
-      <c r="T125" s="38" t="n"/>
-      <c r="U125" s="38" t="n"/>
+      <c r="T125" s="50" t="n"/>
+      <c r="U125" s="50" t="n"/>
       <c r="V125" s="38" t="n"/>
       <c r="W125" s="38" t="n"/>
     </row>
@@ -4607,18 +4733,18 @@
       <c r="G126" s="47" t="n"/>
       <c r="H126" s="45" t="n"/>
       <c r="I126" s="45" t="n"/>
-      <c r="J126" s="48" t="n"/>
+      <c r="J126" s="45" t="n"/>
       <c r="K126" s="45" t="n"/>
-      <c r="L126" s="45" t="n"/>
+      <c r="L126" s="48" t="n"/>
       <c r="M126" s="45" t="n"/>
-      <c r="N126" s="49" t="n"/>
+      <c r="N126" s="45" t="n"/>
       <c r="O126" s="45" t="n"/>
-      <c r="P126" s="45" t="n"/>
+      <c r="P126" s="49" t="n"/>
       <c r="Q126" s="45" t="n"/>
       <c r="R126" s="45" t="n"/>
       <c r="S126" s="45" t="n"/>
-      <c r="T126" s="38" t="n"/>
-      <c r="U126" s="38" t="n"/>
+      <c r="T126" s="45" t="n"/>
+      <c r="U126" s="45" t="n"/>
       <c r="V126" s="38" t="n"/>
       <c r="W126" s="38" t="n"/>
     </row>
@@ -4632,18 +4758,18 @@
       <c r="G127" s="52" t="n"/>
       <c r="H127" s="50" t="n"/>
       <c r="I127" s="50" t="n"/>
-      <c r="J127" s="53" t="n"/>
+      <c r="J127" s="50" t="n"/>
       <c r="K127" s="50" t="n"/>
-      <c r="L127" s="50" t="n"/>
+      <c r="L127" s="53" t="n"/>
       <c r="M127" s="50" t="n"/>
-      <c r="N127" s="54" t="n"/>
+      <c r="N127" s="50" t="n"/>
       <c r="O127" s="50" t="n"/>
-      <c r="P127" s="50" t="n"/>
+      <c r="P127" s="54" t="n"/>
       <c r="Q127" s="50" t="n"/>
       <c r="R127" s="50" t="n"/>
       <c r="S127" s="50" t="n"/>
-      <c r="T127" s="38" t="n"/>
-      <c r="U127" s="38" t="n"/>
+      <c r="T127" s="50" t="n"/>
+      <c r="U127" s="50" t="n"/>
       <c r="V127" s="38" t="n"/>
       <c r="W127" s="38" t="n"/>
     </row>
@@ -4657,18 +4783,18 @@
       <c r="G128" s="47" t="n"/>
       <c r="H128" s="45" t="n"/>
       <c r="I128" s="45" t="n"/>
-      <c r="J128" s="48" t="n"/>
+      <c r="J128" s="45" t="n"/>
       <c r="K128" s="45" t="n"/>
-      <c r="L128" s="45" t="n"/>
+      <c r="L128" s="48" t="n"/>
       <c r="M128" s="45" t="n"/>
-      <c r="N128" s="49" t="n"/>
+      <c r="N128" s="45" t="n"/>
       <c r="O128" s="45" t="n"/>
-      <c r="P128" s="45" t="n"/>
+      <c r="P128" s="49" t="n"/>
       <c r="Q128" s="45" t="n"/>
       <c r="R128" s="45" t="n"/>
       <c r="S128" s="45" t="n"/>
-      <c r="T128" s="38" t="n"/>
-      <c r="U128" s="38" t="n"/>
+      <c r="T128" s="45" t="n"/>
+      <c r="U128" s="45" t="n"/>
       <c r="V128" s="38" t="n"/>
       <c r="W128" s="38" t="n"/>
     </row>
@@ -4682,18 +4808,18 @@
       <c r="G129" s="52" t="n"/>
       <c r="H129" s="50" t="n"/>
       <c r="I129" s="50" t="n"/>
-      <c r="J129" s="53" t="n"/>
+      <c r="J129" s="50" t="n"/>
       <c r="K129" s="50" t="n"/>
-      <c r="L129" s="50" t="n"/>
+      <c r="L129" s="53" t="n"/>
       <c r="M129" s="50" t="n"/>
-      <c r="N129" s="54" t="n"/>
+      <c r="N129" s="50" t="n"/>
       <c r="O129" s="50" t="n"/>
-      <c r="P129" s="50" t="n"/>
+      <c r="P129" s="54" t="n"/>
       <c r="Q129" s="50" t="n"/>
       <c r="R129" s="50" t="n"/>
       <c r="S129" s="50" t="n"/>
-      <c r="T129" s="38" t="n"/>
-      <c r="U129" s="38" t="n"/>
+      <c r="T129" s="50" t="n"/>
+      <c r="U129" s="50" t="n"/>
       <c r="V129" s="38" t="n"/>
       <c r="W129" s="38" t="n"/>
     </row>
@@ -4707,18 +4833,18 @@
       <c r="G130" s="47" t="n"/>
       <c r="H130" s="45" t="n"/>
       <c r="I130" s="45" t="n"/>
-      <c r="J130" s="48" t="n"/>
+      <c r="J130" s="45" t="n"/>
       <c r="K130" s="45" t="n"/>
-      <c r="L130" s="45" t="n"/>
+      <c r="L130" s="48" t="n"/>
       <c r="M130" s="45" t="n"/>
-      <c r="N130" s="49" t="n"/>
+      <c r="N130" s="45" t="n"/>
       <c r="O130" s="45" t="n"/>
-      <c r="P130" s="45" t="n"/>
+      <c r="P130" s="49" t="n"/>
       <c r="Q130" s="45" t="n"/>
       <c r="R130" s="45" t="n"/>
       <c r="S130" s="45" t="n"/>
-      <c r="T130" s="38" t="n"/>
-      <c r="U130" s="38" t="n"/>
+      <c r="T130" s="45" t="n"/>
+      <c r="U130" s="45" t="n"/>
       <c r="V130" s="38" t="n"/>
       <c r="W130" s="38" t="n"/>
     </row>
@@ -4732,18 +4858,18 @@
       <c r="G131" s="52" t="n"/>
       <c r="H131" s="50" t="n"/>
       <c r="I131" s="50" t="n"/>
-      <c r="J131" s="53" t="n"/>
+      <c r="J131" s="50" t="n"/>
       <c r="K131" s="50" t="n"/>
-      <c r="L131" s="50" t="n"/>
+      <c r="L131" s="53" t="n"/>
       <c r="M131" s="50" t="n"/>
-      <c r="N131" s="54" t="n"/>
+      <c r="N131" s="50" t="n"/>
       <c r="O131" s="50" t="n"/>
-      <c r="P131" s="50" t="n"/>
+      <c r="P131" s="54" t="n"/>
       <c r="Q131" s="50" t="n"/>
       <c r="R131" s="50" t="n"/>
       <c r="S131" s="50" t="n"/>
-      <c r="T131" s="38" t="n"/>
-      <c r="U131" s="38" t="n"/>
+      <c r="T131" s="50" t="n"/>
+      <c r="U131" s="50" t="n"/>
       <c r="V131" s="38" t="n"/>
       <c r="W131" s="38" t="n"/>
     </row>
@@ -4757,18 +4883,18 @@
       <c r="G132" s="47" t="n"/>
       <c r="H132" s="45" t="n"/>
       <c r="I132" s="45" t="n"/>
-      <c r="J132" s="48" t="n"/>
+      <c r="J132" s="45" t="n"/>
       <c r="K132" s="45" t="n"/>
-      <c r="L132" s="45" t="n"/>
+      <c r="L132" s="48" t="n"/>
       <c r="M132" s="45" t="n"/>
-      <c r="N132" s="49" t="n"/>
+      <c r="N132" s="45" t="n"/>
       <c r="O132" s="45" t="n"/>
-      <c r="P132" s="45" t="n"/>
+      <c r="P132" s="49" t="n"/>
       <c r="Q132" s="45" t="n"/>
       <c r="R132" s="45" t="n"/>
       <c r="S132" s="45" t="n"/>
-      <c r="T132" s="38" t="n"/>
-      <c r="U132" s="38" t="n"/>
+      <c r="T132" s="45" t="n"/>
+      <c r="U132" s="45" t="n"/>
       <c r="V132" s="38" t="n"/>
       <c r="W132" s="38" t="n"/>
     </row>
@@ -4782,18 +4908,18 @@
       <c r="G133" s="52" t="n"/>
       <c r="H133" s="50" t="n"/>
       <c r="I133" s="50" t="n"/>
-      <c r="J133" s="53" t="n"/>
+      <c r="J133" s="50" t="n"/>
       <c r="K133" s="50" t="n"/>
-      <c r="L133" s="50" t="n"/>
+      <c r="L133" s="53" t="n"/>
       <c r="M133" s="50" t="n"/>
-      <c r="N133" s="54" t="n"/>
+      <c r="N133" s="50" t="n"/>
       <c r="O133" s="50" t="n"/>
-      <c r="P133" s="50" t="n"/>
+      <c r="P133" s="54" t="n"/>
       <c r="Q133" s="50" t="n"/>
       <c r="R133" s="50" t="n"/>
       <c r="S133" s="50" t="n"/>
-      <c r="T133" s="38" t="n"/>
-      <c r="U133" s="38" t="n"/>
+      <c r="T133" s="50" t="n"/>
+      <c r="U133" s="50" t="n"/>
       <c r="V133" s="38" t="n"/>
       <c r="W133" s="38" t="n"/>
     </row>
@@ -4807,18 +4933,18 @@
       <c r="G134" s="47" t="n"/>
       <c r="H134" s="45" t="n"/>
       <c r="I134" s="45" t="n"/>
-      <c r="J134" s="48" t="n"/>
+      <c r="J134" s="45" t="n"/>
       <c r="K134" s="45" t="n"/>
-      <c r="L134" s="45" t="n"/>
+      <c r="L134" s="48" t="n"/>
       <c r="M134" s="45" t="n"/>
-      <c r="N134" s="49" t="n"/>
+      <c r="N134" s="45" t="n"/>
       <c r="O134" s="45" t="n"/>
-      <c r="P134" s="45" t="n"/>
+      <c r="P134" s="49" t="n"/>
       <c r="Q134" s="45" t="n"/>
       <c r="R134" s="45" t="n"/>
       <c r="S134" s="45" t="n"/>
-      <c r="T134" s="38" t="n"/>
-      <c r="U134" s="38" t="n"/>
+      <c r="T134" s="45" t="n"/>
+      <c r="U134" s="45" t="n"/>
       <c r="V134" s="38" t="n"/>
       <c r="W134" s="38" t="n"/>
     </row>
@@ -4832,18 +4958,18 @@
       <c r="G135" s="52" t="n"/>
       <c r="H135" s="50" t="n"/>
       <c r="I135" s="50" t="n"/>
-      <c r="J135" s="53" t="n"/>
+      <c r="J135" s="50" t="n"/>
       <c r="K135" s="50" t="n"/>
-      <c r="L135" s="50" t="n"/>
+      <c r="L135" s="53" t="n"/>
       <c r="M135" s="50" t="n"/>
-      <c r="N135" s="54" t="n"/>
+      <c r="N135" s="50" t="n"/>
       <c r="O135" s="50" t="n"/>
-      <c r="P135" s="50" t="n"/>
+      <c r="P135" s="54" t="n"/>
       <c r="Q135" s="50" t="n"/>
       <c r="R135" s="50" t="n"/>
       <c r="S135" s="50" t="n"/>
-      <c r="T135" s="38" t="n"/>
-      <c r="U135" s="38" t="n"/>
+      <c r="T135" s="50" t="n"/>
+      <c r="U135" s="50" t="n"/>
       <c r="V135" s="38" t="n"/>
       <c r="W135" s="38" t="n"/>
     </row>
@@ -4857,18 +4983,18 @@
       <c r="G136" s="47" t="n"/>
       <c r="H136" s="45" t="n"/>
       <c r="I136" s="45" t="n"/>
-      <c r="J136" s="48" t="n"/>
+      <c r="J136" s="45" t="n"/>
       <c r="K136" s="45" t="n"/>
-      <c r="L136" s="45" t="n"/>
+      <c r="L136" s="48" t="n"/>
       <c r="M136" s="45" t="n"/>
-      <c r="N136" s="49" t="n"/>
+      <c r="N136" s="45" t="n"/>
       <c r="O136" s="45" t="n"/>
-      <c r="P136" s="45" t="n"/>
+      <c r="P136" s="49" t="n"/>
       <c r="Q136" s="45" t="n"/>
       <c r="R136" s="45" t="n"/>
       <c r="S136" s="45" t="n"/>
-      <c r="T136" s="38" t="n"/>
-      <c r="U136" s="38" t="n"/>
+      <c r="T136" s="45" t="n"/>
+      <c r="U136" s="45" t="n"/>
       <c r="V136" s="38" t="n"/>
       <c r="W136" s="38" t="n"/>
     </row>
@@ -4882,18 +5008,18 @@
       <c r="G137" s="52" t="n"/>
       <c r="H137" s="50" t="n"/>
       <c r="I137" s="50" t="n"/>
-      <c r="J137" s="53" t="n"/>
+      <c r="J137" s="50" t="n"/>
       <c r="K137" s="50" t="n"/>
-      <c r="L137" s="50" t="n"/>
+      <c r="L137" s="53" t="n"/>
       <c r="M137" s="50" t="n"/>
-      <c r="N137" s="54" t="n"/>
+      <c r="N137" s="50" t="n"/>
       <c r="O137" s="50" t="n"/>
-      <c r="P137" s="50" t="n"/>
+      <c r="P137" s="54" t="n"/>
       <c r="Q137" s="50" t="n"/>
       <c r="R137" s="50" t="n"/>
       <c r="S137" s="50" t="n"/>
-      <c r="T137" s="38" t="n"/>
-      <c r="U137" s="38" t="n"/>
+      <c r="T137" s="50" t="n"/>
+      <c r="U137" s="50" t="n"/>
       <c r="V137" s="38" t="n"/>
       <c r="W137" s="38" t="n"/>
     </row>
@@ -4907,18 +5033,18 @@
       <c r="G138" s="47" t="n"/>
       <c r="H138" s="45" t="n"/>
       <c r="I138" s="45" t="n"/>
-      <c r="J138" s="48" t="n"/>
+      <c r="J138" s="45" t="n"/>
       <c r="K138" s="45" t="n"/>
-      <c r="L138" s="45" t="n"/>
+      <c r="L138" s="48" t="n"/>
       <c r="M138" s="45" t="n"/>
-      <c r="N138" s="49" t="n"/>
+      <c r="N138" s="45" t="n"/>
       <c r="O138" s="45" t="n"/>
-      <c r="P138" s="45" t="n"/>
+      <c r="P138" s="49" t="n"/>
       <c r="Q138" s="45" t="n"/>
       <c r="R138" s="45" t="n"/>
       <c r="S138" s="45" t="n"/>
-      <c r="T138" s="38" t="n"/>
-      <c r="U138" s="38" t="n"/>
+      <c r="T138" s="45" t="n"/>
+      <c r="U138" s="45" t="n"/>
       <c r="V138" s="38" t="n"/>
       <c r="W138" s="38" t="n"/>
     </row>
@@ -4932,18 +5058,18 @@
       <c r="G139" s="52" t="n"/>
       <c r="H139" s="50" t="n"/>
       <c r="I139" s="50" t="n"/>
-      <c r="J139" s="53" t="n"/>
+      <c r="J139" s="50" t="n"/>
       <c r="K139" s="50" t="n"/>
-      <c r="L139" s="50" t="n"/>
+      <c r="L139" s="53" t="n"/>
       <c r="M139" s="50" t="n"/>
-      <c r="N139" s="54" t="n"/>
+      <c r="N139" s="50" t="n"/>
       <c r="O139" s="50" t="n"/>
-      <c r="P139" s="50" t="n"/>
+      <c r="P139" s="54" t="n"/>
       <c r="Q139" s="50" t="n"/>
       <c r="R139" s="50" t="n"/>
       <c r="S139" s="50" t="n"/>
-      <c r="T139" s="38" t="n"/>
-      <c r="U139" s="38" t="n"/>
+      <c r="T139" s="50" t="n"/>
+      <c r="U139" s="50" t="n"/>
       <c r="V139" s="38" t="n"/>
       <c r="W139" s="38" t="n"/>
     </row>
@@ -4957,18 +5083,18 @@
       <c r="G140" s="47" t="n"/>
       <c r="H140" s="45" t="n"/>
       <c r="I140" s="45" t="n"/>
-      <c r="J140" s="48" t="n"/>
+      <c r="J140" s="45" t="n"/>
       <c r="K140" s="45" t="n"/>
-      <c r="L140" s="45" t="n"/>
+      <c r="L140" s="48" t="n"/>
       <c r="M140" s="45" t="n"/>
-      <c r="N140" s="49" t="n"/>
+      <c r="N140" s="45" t="n"/>
       <c r="O140" s="45" t="n"/>
-      <c r="P140" s="45" t="n"/>
+      <c r="P140" s="49" t="n"/>
       <c r="Q140" s="45" t="n"/>
       <c r="R140" s="45" t="n"/>
       <c r="S140" s="45" t="n"/>
-      <c r="T140" s="38" t="n"/>
-      <c r="U140" s="38" t="n"/>
+      <c r="T140" s="45" t="n"/>
+      <c r="U140" s="45" t="n"/>
       <c r="V140" s="38" t="n"/>
       <c r="W140" s="38" t="n"/>
     </row>
@@ -4982,18 +5108,18 @@
       <c r="G141" s="52" t="n"/>
       <c r="H141" s="50" t="n"/>
       <c r="I141" s="50" t="n"/>
-      <c r="J141" s="53" t="n"/>
+      <c r="J141" s="50" t="n"/>
       <c r="K141" s="50" t="n"/>
-      <c r="L141" s="50" t="n"/>
+      <c r="L141" s="53" t="n"/>
       <c r="M141" s="50" t="n"/>
-      <c r="N141" s="54" t="n"/>
+      <c r="N141" s="50" t="n"/>
       <c r="O141" s="50" t="n"/>
-      <c r="P141" s="50" t="n"/>
+      <c r="P141" s="54" t="n"/>
       <c r="Q141" s="50" t="n"/>
       <c r="R141" s="50" t="n"/>
       <c r="S141" s="50" t="n"/>
-      <c r="T141" s="38" t="n"/>
-      <c r="U141" s="38" t="n"/>
+      <c r="T141" s="50" t="n"/>
+      <c r="U141" s="50" t="n"/>
       <c r="V141" s="38" t="n"/>
       <c r="W141" s="38" t="n"/>
     </row>
@@ -5007,18 +5133,18 @@
       <c r="G142" s="47" t="n"/>
       <c r="H142" s="45" t="n"/>
       <c r="I142" s="45" t="n"/>
-      <c r="J142" s="48" t="n"/>
+      <c r="J142" s="45" t="n"/>
       <c r="K142" s="45" t="n"/>
-      <c r="L142" s="45" t="n"/>
+      <c r="L142" s="48" t="n"/>
       <c r="M142" s="45" t="n"/>
-      <c r="N142" s="49" t="n"/>
+      <c r="N142" s="45" t="n"/>
       <c r="O142" s="45" t="n"/>
-      <c r="P142" s="45" t="n"/>
+      <c r="P142" s="49" t="n"/>
       <c r="Q142" s="45" t="n"/>
       <c r="R142" s="45" t="n"/>
       <c r="S142" s="45" t="n"/>
-      <c r="T142" s="38" t="n"/>
-      <c r="U142" s="38" t="n"/>
+      <c r="T142" s="45" t="n"/>
+      <c r="U142" s="45" t="n"/>
       <c r="V142" s="38" t="n"/>
       <c r="W142" s="38" t="n"/>
     </row>
@@ -5032,18 +5158,18 @@
       <c r="G143" s="52" t="n"/>
       <c r="H143" s="50" t="n"/>
       <c r="I143" s="50" t="n"/>
-      <c r="J143" s="53" t="n"/>
+      <c r="J143" s="50" t="n"/>
       <c r="K143" s="50" t="n"/>
-      <c r="L143" s="50" t="n"/>
+      <c r="L143" s="53" t="n"/>
       <c r="M143" s="50" t="n"/>
-      <c r="N143" s="54" t="n"/>
+      <c r="N143" s="50" t="n"/>
       <c r="O143" s="50" t="n"/>
-      <c r="P143" s="50" t="n"/>
+      <c r="P143" s="54" t="n"/>
       <c r="Q143" s="50" t="n"/>
       <c r="R143" s="50" t="n"/>
       <c r="S143" s="50" t="n"/>
-      <c r="T143" s="38" t="n"/>
-      <c r="U143" s="38" t="n"/>
+      <c r="T143" s="50" t="n"/>
+      <c r="U143" s="50" t="n"/>
       <c r="V143" s="38" t="n"/>
       <c r="W143" s="38" t="n"/>
     </row>
@@ -5057,18 +5183,18 @@
       <c r="G144" s="47" t="n"/>
       <c r="H144" s="45" t="n"/>
       <c r="I144" s="45" t="n"/>
-      <c r="J144" s="48" t="n"/>
+      <c r="J144" s="45" t="n"/>
       <c r="K144" s="45" t="n"/>
-      <c r="L144" s="45" t="n"/>
+      <c r="L144" s="48" t="n"/>
       <c r="M144" s="45" t="n"/>
-      <c r="N144" s="49" t="n"/>
+      <c r="N144" s="45" t="n"/>
       <c r="O144" s="45" t="n"/>
-      <c r="P144" s="45" t="n"/>
+      <c r="P144" s="49" t="n"/>
       <c r="Q144" s="45" t="n"/>
       <c r="R144" s="45" t="n"/>
       <c r="S144" s="45" t="n"/>
-      <c r="T144" s="38" t="n"/>
-      <c r="U144" s="38" t="n"/>
+      <c r="T144" s="45" t="n"/>
+      <c r="U144" s="45" t="n"/>
       <c r="V144" s="38" t="n"/>
       <c r="W144" s="38" t="n"/>
     </row>
@@ -5082,18 +5208,18 @@
       <c r="G145" s="52" t="n"/>
       <c r="H145" s="50" t="n"/>
       <c r="I145" s="50" t="n"/>
-      <c r="J145" s="53" t="n"/>
+      <c r="J145" s="50" t="n"/>
       <c r="K145" s="50" t="n"/>
-      <c r="L145" s="50" t="n"/>
+      <c r="L145" s="53" t="n"/>
       <c r="M145" s="50" t="n"/>
-      <c r="N145" s="54" t="n"/>
+      <c r="N145" s="50" t="n"/>
       <c r="O145" s="50" t="n"/>
-      <c r="P145" s="50" t="n"/>
+      <c r="P145" s="54" t="n"/>
       <c r="Q145" s="50" t="n"/>
       <c r="R145" s="50" t="n"/>
       <c r="S145" s="50" t="n"/>
-      <c r="T145" s="38" t="n"/>
-      <c r="U145" s="38" t="n"/>
+      <c r="T145" s="50" t="n"/>
+      <c r="U145" s="50" t="n"/>
       <c r="V145" s="38" t="n"/>
       <c r="W145" s="38" t="n"/>
     </row>
@@ -5107,18 +5233,18 @@
       <c r="G146" s="47" t="n"/>
       <c r="H146" s="45" t="n"/>
       <c r="I146" s="45" t="n"/>
-      <c r="J146" s="48" t="n"/>
+      <c r="J146" s="45" t="n"/>
       <c r="K146" s="45" t="n"/>
-      <c r="L146" s="45" t="n"/>
+      <c r="L146" s="48" t="n"/>
       <c r="M146" s="45" t="n"/>
-      <c r="N146" s="49" t="n"/>
+      <c r="N146" s="45" t="n"/>
       <c r="O146" s="45" t="n"/>
-      <c r="P146" s="45" t="n"/>
+      <c r="P146" s="49" t="n"/>
       <c r="Q146" s="45" t="n"/>
       <c r="R146" s="45" t="n"/>
       <c r="S146" s="45" t="n"/>
-      <c r="T146" s="38" t="n"/>
-      <c r="U146" s="38" t="n"/>
+      <c r="T146" s="45" t="n"/>
+      <c r="U146" s="45" t="n"/>
       <c r="V146" s="38" t="n"/>
       <c r="W146" s="38" t="n"/>
     </row>
@@ -5132,18 +5258,18 @@
       <c r="G147" s="52" t="n"/>
       <c r="H147" s="50" t="n"/>
       <c r="I147" s="50" t="n"/>
-      <c r="J147" s="53" t="n"/>
+      <c r="J147" s="50" t="n"/>
       <c r="K147" s="50" t="n"/>
-      <c r="L147" s="50" t="n"/>
+      <c r="L147" s="53" t="n"/>
       <c r="M147" s="50" t="n"/>
-      <c r="N147" s="54" t="n"/>
+      <c r="N147" s="50" t="n"/>
       <c r="O147" s="50" t="n"/>
-      <c r="P147" s="50" t="n"/>
+      <c r="P147" s="54" t="n"/>
       <c r="Q147" s="50" t="n"/>
       <c r="R147" s="50" t="n"/>
       <c r="S147" s="50" t="n"/>
-      <c r="T147" s="38" t="n"/>
-      <c r="U147" s="38" t="n"/>
+      <c r="T147" s="50" t="n"/>
+      <c r="U147" s="50" t="n"/>
       <c r="V147" s="38" t="n"/>
       <c r="W147" s="38" t="n"/>
     </row>
@@ -5157,18 +5283,18 @@
       <c r="G148" s="47" t="n"/>
       <c r="H148" s="45" t="n"/>
       <c r="I148" s="45" t="n"/>
-      <c r="J148" s="48" t="n"/>
+      <c r="J148" s="45" t="n"/>
       <c r="K148" s="45" t="n"/>
-      <c r="L148" s="45" t="n"/>
+      <c r="L148" s="48" t="n"/>
       <c r="M148" s="45" t="n"/>
-      <c r="N148" s="49" t="n"/>
+      <c r="N148" s="45" t="n"/>
       <c r="O148" s="45" t="n"/>
-      <c r="P148" s="45" t="n"/>
+      <c r="P148" s="49" t="n"/>
       <c r="Q148" s="45" t="n"/>
       <c r="R148" s="45" t="n"/>
       <c r="S148" s="45" t="n"/>
-      <c r="T148" s="38" t="n"/>
-      <c r="U148" s="38" t="n"/>
+      <c r="T148" s="45" t="n"/>
+      <c r="U148" s="45" t="n"/>
       <c r="V148" s="38" t="n"/>
       <c r="W148" s="38" t="n"/>
     </row>
@@ -5182,18 +5308,18 @@
       <c r="G149" s="52" t="n"/>
       <c r="H149" s="50" t="n"/>
       <c r="I149" s="50" t="n"/>
-      <c r="J149" s="53" t="n"/>
+      <c r="J149" s="50" t="n"/>
       <c r="K149" s="50" t="n"/>
-      <c r="L149" s="50" t="n"/>
+      <c r="L149" s="53" t="n"/>
       <c r="M149" s="50" t="n"/>
-      <c r="N149" s="54" t="n"/>
+      <c r="N149" s="50" t="n"/>
       <c r="O149" s="50" t="n"/>
-      <c r="P149" s="50" t="n"/>
+      <c r="P149" s="54" t="n"/>
       <c r="Q149" s="50" t="n"/>
       <c r="R149" s="50" t="n"/>
       <c r="S149" s="50" t="n"/>
-      <c r="T149" s="38" t="n"/>
-      <c r="U149" s="38" t="n"/>
+      <c r="T149" s="50" t="n"/>
+      <c r="U149" s="50" t="n"/>
       <c r="V149" s="38" t="n"/>
       <c r="W149" s="38" t="n"/>
     </row>
@@ -5207,18 +5333,18 @@
       <c r="G150" s="47" t="n"/>
       <c r="H150" s="45" t="n"/>
       <c r="I150" s="45" t="n"/>
-      <c r="J150" s="48" t="n"/>
+      <c r="J150" s="45" t="n"/>
       <c r="K150" s="45" t="n"/>
-      <c r="L150" s="45" t="n"/>
+      <c r="L150" s="48" t="n"/>
       <c r="M150" s="45" t="n"/>
-      <c r="N150" s="49" t="n"/>
+      <c r="N150" s="45" t="n"/>
       <c r="O150" s="45" t="n"/>
-      <c r="P150" s="45" t="n"/>
+      <c r="P150" s="49" t="n"/>
       <c r="Q150" s="45" t="n"/>
       <c r="R150" s="45" t="n"/>
       <c r="S150" s="45" t="n"/>
-      <c r="T150" s="38" t="n"/>
-      <c r="U150" s="38" t="n"/>
+      <c r="T150" s="45" t="n"/>
+      <c r="U150" s="45" t="n"/>
       <c r="V150" s="38" t="n"/>
       <c r="W150" s="38" t="n"/>
     </row>
@@ -5232,18 +5358,18 @@
       <c r="G151" s="52" t="n"/>
       <c r="H151" s="50" t="n"/>
       <c r="I151" s="50" t="n"/>
-      <c r="J151" s="53" t="n"/>
+      <c r="J151" s="50" t="n"/>
       <c r="K151" s="50" t="n"/>
-      <c r="L151" s="50" t="n"/>
+      <c r="L151" s="53" t="n"/>
       <c r="M151" s="50" t="n"/>
-      <c r="N151" s="54" t="n"/>
+      <c r="N151" s="50" t="n"/>
       <c r="O151" s="50" t="n"/>
-      <c r="P151" s="50" t="n"/>
+      <c r="P151" s="54" t="n"/>
       <c r="Q151" s="50" t="n"/>
       <c r="R151" s="50" t="n"/>
       <c r="S151" s="50" t="n"/>
-      <c r="T151" s="38" t="n"/>
-      <c r="U151" s="38" t="n"/>
+      <c r="T151" s="50" t="n"/>
+      <c r="U151" s="50" t="n"/>
       <c r="V151" s="38" t="n"/>
       <c r="W151" s="38" t="n"/>
     </row>
@@ -5257,18 +5383,18 @@
       <c r="G152" s="47" t="n"/>
       <c r="H152" s="45" t="n"/>
       <c r="I152" s="45" t="n"/>
-      <c r="J152" s="48" t="n"/>
+      <c r="J152" s="45" t="n"/>
       <c r="K152" s="45" t="n"/>
-      <c r="L152" s="45" t="n"/>
+      <c r="L152" s="48" t="n"/>
       <c r="M152" s="45" t="n"/>
-      <c r="N152" s="49" t="n"/>
+      <c r="N152" s="45" t="n"/>
       <c r="O152" s="45" t="n"/>
-      <c r="P152" s="45" t="n"/>
+      <c r="P152" s="49" t="n"/>
       <c r="Q152" s="45" t="n"/>
       <c r="R152" s="45" t="n"/>
       <c r="S152" s="45" t="n"/>
-      <c r="T152" s="38" t="n"/>
-      <c r="U152" s="38" t="n"/>
+      <c r="T152" s="45" t="n"/>
+      <c r="U152" s="45" t="n"/>
       <c r="V152" s="38" t="n"/>
       <c r="W152" s="38" t="n"/>
     </row>
@@ -5282,18 +5408,18 @@
       <c r="G153" s="52" t="n"/>
       <c r="H153" s="50" t="n"/>
       <c r="I153" s="50" t="n"/>
-      <c r="J153" s="53" t="n"/>
+      <c r="J153" s="50" t="n"/>
       <c r="K153" s="50" t="n"/>
-      <c r="L153" s="50" t="n"/>
+      <c r="L153" s="53" t="n"/>
       <c r="M153" s="50" t="n"/>
-      <c r="N153" s="54" t="n"/>
+      <c r="N153" s="50" t="n"/>
       <c r="O153" s="50" t="n"/>
-      <c r="P153" s="50" t="n"/>
+      <c r="P153" s="54" t="n"/>
       <c r="Q153" s="50" t="n"/>
       <c r="R153" s="50" t="n"/>
       <c r="S153" s="50" t="n"/>
-      <c r="T153" s="38" t="n"/>
-      <c r="U153" s="38" t="n"/>
+      <c r="T153" s="50" t="n"/>
+      <c r="U153" s="50" t="n"/>
       <c r="V153" s="38" t="n"/>
       <c r="W153" s="38" t="n"/>
     </row>
@@ -5307,18 +5433,18 @@
       <c r="G154" s="47" t="n"/>
       <c r="H154" s="45" t="n"/>
       <c r="I154" s="45" t="n"/>
-      <c r="J154" s="48" t="n"/>
+      <c r="J154" s="45" t="n"/>
       <c r="K154" s="45" t="n"/>
-      <c r="L154" s="45" t="n"/>
+      <c r="L154" s="48" t="n"/>
       <c r="M154" s="45" t="n"/>
-      <c r="N154" s="49" t="n"/>
+      <c r="N154" s="45" t="n"/>
       <c r="O154" s="45" t="n"/>
-      <c r="P154" s="45" t="n"/>
+      <c r="P154" s="49" t="n"/>
       <c r="Q154" s="45" t="n"/>
       <c r="R154" s="45" t="n"/>
       <c r="S154" s="45" t="n"/>
-      <c r="T154" s="38" t="n"/>
-      <c r="U154" s="38" t="n"/>
+      <c r="T154" s="45" t="n"/>
+      <c r="U154" s="45" t="n"/>
       <c r="V154" s="38" t="n"/>
       <c r="W154" s="38" t="n"/>
     </row>
@@ -5332,18 +5458,18 @@
       <c r="G155" s="52" t="n"/>
       <c r="H155" s="50" t="n"/>
       <c r="I155" s="50" t="n"/>
-      <c r="J155" s="53" t="n"/>
+      <c r="J155" s="50" t="n"/>
       <c r="K155" s="50" t="n"/>
-      <c r="L155" s="50" t="n"/>
+      <c r="L155" s="53" t="n"/>
       <c r="M155" s="50" t="n"/>
-      <c r="N155" s="54" t="n"/>
+      <c r="N155" s="50" t="n"/>
       <c r="O155" s="50" t="n"/>
-      <c r="P155" s="50" t="n"/>
+      <c r="P155" s="54" t="n"/>
       <c r="Q155" s="50" t="n"/>
       <c r="R155" s="50" t="n"/>
       <c r="S155" s="50" t="n"/>
-      <c r="T155" s="38" t="n"/>
-      <c r="U155" s="38" t="n"/>
+      <c r="T155" s="50" t="n"/>
+      <c r="U155" s="50" t="n"/>
       <c r="V155" s="38" t="n"/>
       <c r="W155" s="38" t="n"/>
     </row>
@@ -5357,18 +5483,18 @@
       <c r="G156" s="47" t="n"/>
       <c r="H156" s="45" t="n"/>
       <c r="I156" s="45" t="n"/>
-      <c r="J156" s="48" t="n"/>
+      <c r="J156" s="45" t="n"/>
       <c r="K156" s="45" t="n"/>
-      <c r="L156" s="45" t="n"/>
+      <c r="L156" s="48" t="n"/>
       <c r="M156" s="45" t="n"/>
-      <c r="N156" s="49" t="n"/>
+      <c r="N156" s="45" t="n"/>
       <c r="O156" s="45" t="n"/>
-      <c r="P156" s="45" t="n"/>
+      <c r="P156" s="49" t="n"/>
       <c r="Q156" s="45" t="n"/>
       <c r="R156" s="45" t="n"/>
       <c r="S156" s="45" t="n"/>
-      <c r="T156" s="38" t="n"/>
-      <c r="U156" s="38" t="n"/>
+      <c r="T156" s="45" t="n"/>
+      <c r="U156" s="45" t="n"/>
       <c r="V156" s="38" t="n"/>
       <c r="W156" s="38" t="n"/>
     </row>
@@ -5382,18 +5508,18 @@
       <c r="G157" s="52" t="n"/>
       <c r="H157" s="50" t="n"/>
       <c r="I157" s="50" t="n"/>
-      <c r="J157" s="53" t="n"/>
+      <c r="J157" s="50" t="n"/>
       <c r="K157" s="50" t="n"/>
-      <c r="L157" s="50" t="n"/>
+      <c r="L157" s="53" t="n"/>
       <c r="M157" s="50" t="n"/>
-      <c r="N157" s="54" t="n"/>
+      <c r="N157" s="50" t="n"/>
       <c r="O157" s="50" t="n"/>
-      <c r="P157" s="50" t="n"/>
+      <c r="P157" s="54" t="n"/>
       <c r="Q157" s="50" t="n"/>
       <c r="R157" s="50" t="n"/>
       <c r="S157" s="50" t="n"/>
-      <c r="T157" s="38" t="n"/>
-      <c r="U157" s="38" t="n"/>
+      <c r="T157" s="50" t="n"/>
+      <c r="U157" s="50" t="n"/>
       <c r="V157" s="38" t="n"/>
       <c r="W157" s="38" t="n"/>
     </row>
@@ -5407,18 +5533,18 @@
       <c r="G158" s="47" t="n"/>
       <c r="H158" s="45" t="n"/>
       <c r="I158" s="45" t="n"/>
-      <c r="J158" s="48" t="n"/>
+      <c r="J158" s="45" t="n"/>
       <c r="K158" s="45" t="n"/>
-      <c r="L158" s="45" t="n"/>
+      <c r="L158" s="48" t="n"/>
       <c r="M158" s="45" t="n"/>
-      <c r="N158" s="49" t="n"/>
+      <c r="N158" s="45" t="n"/>
       <c r="O158" s="45" t="n"/>
-      <c r="P158" s="45" t="n"/>
+      <c r="P158" s="49" t="n"/>
       <c r="Q158" s="45" t="n"/>
       <c r="R158" s="45" t="n"/>
       <c r="S158" s="45" t="n"/>
-      <c r="T158" s="38" t="n"/>
-      <c r="U158" s="38" t="n"/>
+      <c r="T158" s="45" t="n"/>
+      <c r="U158" s="45" t="n"/>
       <c r="V158" s="38" t="n"/>
       <c r="W158" s="38" t="n"/>
     </row>
@@ -5432,18 +5558,18 @@
       <c r="G159" s="52" t="n"/>
       <c r="H159" s="50" t="n"/>
       <c r="I159" s="50" t="n"/>
-      <c r="J159" s="53" t="n"/>
+      <c r="J159" s="50" t="n"/>
       <c r="K159" s="50" t="n"/>
-      <c r="L159" s="50" t="n"/>
+      <c r="L159" s="53" t="n"/>
       <c r="M159" s="50" t="n"/>
-      <c r="N159" s="54" t="n"/>
+      <c r="N159" s="50" t="n"/>
       <c r="O159" s="50" t="n"/>
-      <c r="P159" s="50" t="n"/>
+      <c r="P159" s="54" t="n"/>
       <c r="Q159" s="50" t="n"/>
       <c r="R159" s="50" t="n"/>
       <c r="S159" s="50" t="n"/>
-      <c r="T159" s="38" t="n"/>
-      <c r="U159" s="38" t="n"/>
+      <c r="T159" s="50" t="n"/>
+      <c r="U159" s="50" t="n"/>
       <c r="V159" s="38" t="n"/>
       <c r="W159" s="38" t="n"/>
     </row>
@@ -5457,18 +5583,18 @@
       <c r="G160" s="47" t="n"/>
       <c r="H160" s="45" t="n"/>
       <c r="I160" s="45" t="n"/>
-      <c r="J160" s="48" t="n"/>
+      <c r="J160" s="45" t="n"/>
       <c r="K160" s="45" t="n"/>
-      <c r="L160" s="45" t="n"/>
+      <c r="L160" s="48" t="n"/>
       <c r="M160" s="45" t="n"/>
-      <c r="N160" s="49" t="n"/>
+      <c r="N160" s="45" t="n"/>
       <c r="O160" s="45" t="n"/>
-      <c r="P160" s="45" t="n"/>
+      <c r="P160" s="49" t="n"/>
       <c r="Q160" s="45" t="n"/>
       <c r="R160" s="45" t="n"/>
       <c r="S160" s="45" t="n"/>
-      <c r="T160" s="38" t="n"/>
-      <c r="U160" s="38" t="n"/>
+      <c r="T160" s="45" t="n"/>
+      <c r="U160" s="45" t="n"/>
       <c r="V160" s="38" t="n"/>
       <c r="W160" s="38" t="n"/>
     </row>
@@ -5482,18 +5608,18 @@
       <c r="G161" s="52" t="n"/>
       <c r="H161" s="50" t="n"/>
       <c r="I161" s="50" t="n"/>
-      <c r="J161" s="53" t="n"/>
+      <c r="J161" s="50" t="n"/>
       <c r="K161" s="50" t="n"/>
-      <c r="L161" s="50" t="n"/>
+      <c r="L161" s="53" t="n"/>
       <c r="M161" s="50" t="n"/>
-      <c r="N161" s="54" t="n"/>
+      <c r="N161" s="50" t="n"/>
       <c r="O161" s="50" t="n"/>
-      <c r="P161" s="50" t="n"/>
+      <c r="P161" s="54" t="n"/>
       <c r="Q161" s="50" t="n"/>
       <c r="R161" s="50" t="n"/>
       <c r="S161" s="50" t="n"/>
-      <c r="T161" s="38" t="n"/>
-      <c r="U161" s="38" t="n"/>
+      <c r="T161" s="50" t="n"/>
+      <c r="U161" s="50" t="n"/>
       <c r="V161" s="38" t="n"/>
       <c r="W161" s="38" t="n"/>
     </row>
@@ -5507,18 +5633,18 @@
       <c r="G162" s="47" t="n"/>
       <c r="H162" s="45" t="n"/>
       <c r="I162" s="45" t="n"/>
-      <c r="J162" s="48" t="n"/>
+      <c r="J162" s="45" t="n"/>
       <c r="K162" s="45" t="n"/>
-      <c r="L162" s="45" t="n"/>
+      <c r="L162" s="48" t="n"/>
       <c r="M162" s="45" t="n"/>
-      <c r="N162" s="49" t="n"/>
+      <c r="N162" s="45" t="n"/>
       <c r="O162" s="45" t="n"/>
-      <c r="P162" s="45" t="n"/>
+      <c r="P162" s="49" t="n"/>
       <c r="Q162" s="45" t="n"/>
       <c r="R162" s="45" t="n"/>
       <c r="S162" s="45" t="n"/>
-      <c r="T162" s="38" t="n"/>
-      <c r="U162" s="38" t="n"/>
+      <c r="T162" s="45" t="n"/>
+      <c r="U162" s="45" t="n"/>
       <c r="V162" s="38" t="n"/>
       <c r="W162" s="38" t="n"/>
     </row>
@@ -5532,18 +5658,18 @@
       <c r="G163" s="52" t="n"/>
       <c r="H163" s="50" t="n"/>
       <c r="I163" s="50" t="n"/>
-      <c r="J163" s="53" t="n"/>
+      <c r="J163" s="50" t="n"/>
       <c r="K163" s="50" t="n"/>
-      <c r="L163" s="50" t="n"/>
+      <c r="L163" s="53" t="n"/>
       <c r="M163" s="50" t="n"/>
-      <c r="N163" s="54" t="n"/>
+      <c r="N163" s="50" t="n"/>
       <c r="O163" s="50" t="n"/>
-      <c r="P163" s="50" t="n"/>
+      <c r="P163" s="54" t="n"/>
       <c r="Q163" s="50" t="n"/>
       <c r="R163" s="50" t="n"/>
       <c r="S163" s="50" t="n"/>
-      <c r="T163" s="38" t="n"/>
-      <c r="U163" s="38" t="n"/>
+      <c r="T163" s="50" t="n"/>
+      <c r="U163" s="50" t="n"/>
       <c r="V163" s="38" t="n"/>
       <c r="W163" s="38" t="n"/>
     </row>
@@ -5557,18 +5683,18 @@
       <c r="G164" s="47" t="n"/>
       <c r="H164" s="45" t="n"/>
       <c r="I164" s="45" t="n"/>
-      <c r="J164" s="48" t="n"/>
+      <c r="J164" s="45" t="n"/>
       <c r="K164" s="45" t="n"/>
-      <c r="L164" s="45" t="n"/>
+      <c r="L164" s="48" t="n"/>
       <c r="M164" s="45" t="n"/>
-      <c r="N164" s="49" t="n"/>
+      <c r="N164" s="45" t="n"/>
       <c r="O164" s="45" t="n"/>
-      <c r="P164" s="45" t="n"/>
+      <c r="P164" s="49" t="n"/>
       <c r="Q164" s="45" t="n"/>
       <c r="R164" s="45" t="n"/>
       <c r="S164" s="45" t="n"/>
-      <c r="T164" s="38" t="n"/>
-      <c r="U164" s="38" t="n"/>
+      <c r="T164" s="45" t="n"/>
+      <c r="U164" s="45" t="n"/>
       <c r="V164" s="38" t="n"/>
       <c r="W164" s="38" t="n"/>
     </row>
@@ -5582,18 +5708,18 @@
       <c r="G165" s="52" t="n"/>
       <c r="H165" s="50" t="n"/>
       <c r="I165" s="50" t="n"/>
-      <c r="J165" s="53" t="n"/>
+      <c r="J165" s="50" t="n"/>
       <c r="K165" s="50" t="n"/>
-      <c r="L165" s="50" t="n"/>
+      <c r="L165" s="53" t="n"/>
       <c r="M165" s="50" t="n"/>
-      <c r="N165" s="54" t="n"/>
+      <c r="N165" s="50" t="n"/>
       <c r="O165" s="50" t="n"/>
-      <c r="P165" s="50" t="n"/>
+      <c r="P165" s="54" t="n"/>
       <c r="Q165" s="50" t="n"/>
       <c r="R165" s="50" t="n"/>
       <c r="S165" s="50" t="n"/>
-      <c r="T165" s="38" t="n"/>
-      <c r="U165" s="38" t="n"/>
+      <c r="T165" s="50" t="n"/>
+      <c r="U165" s="50" t="n"/>
       <c r="V165" s="38" t="n"/>
       <c r="W165" s="38" t="n"/>
     </row>
@@ -5607,18 +5733,18 @@
       <c r="G166" s="47" t="n"/>
       <c r="H166" s="45" t="n"/>
       <c r="I166" s="45" t="n"/>
-      <c r="J166" s="48" t="n"/>
+      <c r="J166" s="45" t="n"/>
       <c r="K166" s="45" t="n"/>
-      <c r="L166" s="45" t="n"/>
+      <c r="L166" s="48" t="n"/>
       <c r="M166" s="45" t="n"/>
-      <c r="N166" s="49" t="n"/>
+      <c r="N166" s="45" t="n"/>
       <c r="O166" s="45" t="n"/>
-      <c r="P166" s="45" t="n"/>
+      <c r="P166" s="49" t="n"/>
       <c r="Q166" s="45" t="n"/>
       <c r="R166" s="45" t="n"/>
       <c r="S166" s="45" t="n"/>
-      <c r="T166" s="38" t="n"/>
-      <c r="U166" s="38" t="n"/>
+      <c r="T166" s="45" t="n"/>
+      <c r="U166" s="45" t="n"/>
       <c r="V166" s="38" t="n"/>
       <c r="W166" s="38" t="n"/>
     </row>
@@ -5632,18 +5758,18 @@
       <c r="G167" s="52" t="n"/>
       <c r="H167" s="50" t="n"/>
       <c r="I167" s="50" t="n"/>
-      <c r="J167" s="53" t="n"/>
+      <c r="J167" s="50" t="n"/>
       <c r="K167" s="50" t="n"/>
-      <c r="L167" s="50" t="n"/>
+      <c r="L167" s="53" t="n"/>
       <c r="M167" s="50" t="n"/>
-      <c r="N167" s="54" t="n"/>
+      <c r="N167" s="50" t="n"/>
       <c r="O167" s="50" t="n"/>
-      <c r="P167" s="50" t="n"/>
+      <c r="P167" s="54" t="n"/>
       <c r="Q167" s="50" t="n"/>
       <c r="R167" s="50" t="n"/>
       <c r="S167" s="50" t="n"/>
-      <c r="T167" s="38" t="n"/>
-      <c r="U167" s="38" t="n"/>
+      <c r="T167" s="50" t="n"/>
+      <c r="U167" s="50" t="n"/>
       <c r="V167" s="38" t="n"/>
       <c r="W167" s="38" t="n"/>
     </row>
@@ -5657,18 +5783,18 @@
       <c r="G168" s="47" t="n"/>
       <c r="H168" s="45" t="n"/>
       <c r="I168" s="45" t="n"/>
-      <c r="J168" s="48" t="n"/>
+      <c r="J168" s="45" t="n"/>
       <c r="K168" s="45" t="n"/>
-      <c r="L168" s="45" t="n"/>
+      <c r="L168" s="48" t="n"/>
       <c r="M168" s="45" t="n"/>
-      <c r="N168" s="49" t="n"/>
+      <c r="N168" s="45" t="n"/>
       <c r="O168" s="45" t="n"/>
-      <c r="P168" s="45" t="n"/>
+      <c r="P168" s="49" t="n"/>
       <c r="Q168" s="45" t="n"/>
       <c r="R168" s="45" t="n"/>
       <c r="S168" s="45" t="n"/>
-      <c r="T168" s="38" t="n"/>
-      <c r="U168" s="38" t="n"/>
+      <c r="T168" s="45" t="n"/>
+      <c r="U168" s="45" t="n"/>
       <c r="V168" s="38" t="n"/>
       <c r="W168" s="38" t="n"/>
     </row>
@@ -5682,18 +5808,18 @@
       <c r="G169" s="52" t="n"/>
       <c r="H169" s="50" t="n"/>
       <c r="I169" s="50" t="n"/>
-      <c r="J169" s="53" t="n"/>
+      <c r="J169" s="50" t="n"/>
       <c r="K169" s="50" t="n"/>
-      <c r="L169" s="50" t="n"/>
+      <c r="L169" s="53" t="n"/>
       <c r="M169" s="50" t="n"/>
-      <c r="N169" s="54" t="n"/>
+      <c r="N169" s="50" t="n"/>
       <c r="O169" s="50" t="n"/>
-      <c r="P169" s="50" t="n"/>
+      <c r="P169" s="54" t="n"/>
       <c r="Q169" s="50" t="n"/>
       <c r="R169" s="50" t="n"/>
       <c r="S169" s="50" t="n"/>
-      <c r="T169" s="38" t="n"/>
-      <c r="U169" s="38" t="n"/>
+      <c r="T169" s="50" t="n"/>
+      <c r="U169" s="50" t="n"/>
       <c r="V169" s="38" t="n"/>
       <c r="W169" s="38" t="n"/>
     </row>
@@ -18949,15 +19075,18 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P17"/>
-  <dataValidations count="3">
-    <dataValidation sqref="K3:K1017" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="M3:M1017" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PSA,BGS,CGC,SGC,TAG,HGA,GMA,Arena Club"</formula1>
     </dataValidation>
-    <dataValidation sqref="M3:M1017" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O1017" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Near Mint,Lightly Played,Moderately Played,Heavily Played,Damaged,Factory Sealed"</formula1>
     </dataValidation>
-    <dataValidation sqref="O3:O1017" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q3:Q1017" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Available,Sold,On Hold"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J1017" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sports,TCG,Non-Sport"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -18971,7 +19100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -19276,7 +19405,7 @@
     <row r="13" ht="29" customHeight="1">
       <c r="A13" s="61" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B13" s="62" t="inlineStr">
@@ -19286,7 +19415,7 @@
       </c>
       <c r="C13" s="61" t="inlineStr">
         <is>
-          <t>Numeric: 7 · 8 · 9 · 9.5 · 10  (leave blank for raw/ungraded)</t>
+          <t>Sports, TCG, or Non-Sport</t>
         </is>
       </c>
       <c r="D13" s="62" t="inlineStr">
@@ -19296,14 +19425,14 @@
       </c>
       <c r="E13" s="61" t="inlineStr">
         <is>
-          <t>Numbers only — no letters</t>
+          <t>Broad classification — dropdown in the template. Inferred automatically from Subcategory if left blank and Subcategory matches a known value</t>
         </is>
       </c>
     </row>
     <row r="14" ht="29" customHeight="1">
       <c r="A14" s="59" t="inlineStr">
         <is>
-          <t>Grader</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="B14" s="60" t="inlineStr">
@@ -19313,7 +19442,7 @@
       </c>
       <c r="C14" s="59" t="inlineStr">
         <is>
-          <t>PSA · BGS · CGC · SGC · TAG · HGA · GMA · Arena Club  (leave blank for raw/ungraded)</t>
+          <t>See the reference list below — free text, not enforced by the spreadsheet</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
@@ -19323,14 +19452,14 @@
       </c>
       <c r="E14" s="59" t="inlineStr">
         <is>
-          <t>Dropdown in the template offers these plus any other grading company name you type in — not limited to the list</t>
+          <t>The specific sport/game/franchise, e.g. Baseball, Pokémon, Marvel. Any value not on the list is fine — it will just need a category assigned manually in the app after import, same as "Other TCG" etc. work in-app</t>
         </is>
       </c>
     </row>
     <row r="15" ht="29" customHeight="1">
       <c r="A15" s="61" t="inlineStr">
         <is>
-          <t>Cert #</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="B15" s="62" t="inlineStr">
@@ -19340,7 +19469,7 @@
       </c>
       <c r="C15" s="61" t="inlineStr">
         <is>
-          <t>8-digit cert number from the slab label e.g. 100039513</t>
+          <t>Numeric: 7 · 8 · 9 · 9.5 · 10  (leave blank for raw/ungraded)</t>
         </is>
       </c>
       <c r="D15" s="62" t="inlineStr">
@@ -19350,14 +19479,14 @@
       </c>
       <c r="E15" s="61" t="inlineStr">
         <is>
-          <t>Enables barcode scan matching in the app</t>
+          <t>Numbers only — no letters</t>
         </is>
       </c>
     </row>
     <row r="16" ht="29" customHeight="1">
       <c r="A16" s="59" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Grader</t>
         </is>
       </c>
       <c r="B16" s="60" t="inlineStr">
@@ -19367,7 +19496,7 @@
       </c>
       <c r="C16" s="59" t="inlineStr">
         <is>
-          <t>Near Mint · Lightly Played · Moderately Played · Factory Sealed</t>
+          <t>PSA · BGS · CGC · SGC · TAG · HGA · GMA · Arena Club  (leave blank for raw/ungraded)</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
@@ -19377,14 +19506,14 @@
       </c>
       <c r="E16" s="59" t="inlineStr">
         <is>
-          <t>For raw cards only — leave blank for graded slabs</t>
+          <t>Dropdown in the template offers these plus any other grading company name you type in — not limited to the list</t>
         </is>
       </c>
     </row>
     <row r="17" ht="29" customHeight="1">
       <c r="A17" s="61" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Cert #</t>
         </is>
       </c>
       <c r="B17" s="62" t="inlineStr">
@@ -19394,7 +19523,7 @@
       </c>
       <c r="C17" s="61" t="inlineStr">
         <is>
-          <t>Numbers only — no $ or commas. 450 not $450</t>
+          <t>8-digit cert number from the slab label e.g. 100039513</t>
         </is>
       </c>
       <c r="D17" s="62" t="inlineStr">
@@ -19404,14 +19533,14 @@
       </c>
       <c r="E17" s="61" t="inlineStr">
         <is>
-          <t>Asking price. Leave blank to set after import</t>
+          <t>Enables barcode scan matching in the app</t>
         </is>
       </c>
     </row>
     <row r="18" ht="29" customHeight="1">
       <c r="A18" s="59" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="B18" s="60" t="inlineStr">
@@ -19421,7 +19550,7 @@
       </c>
       <c r="C18" s="59" t="inlineStr">
         <is>
-          <t>Available (default) · Sold · On Hold</t>
+          <t>Near Mint · Lightly Played · Moderately Played · Factory Sealed</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
@@ -19431,14 +19560,14 @@
       </c>
       <c r="E18" s="59" t="inlineStr">
         <is>
-          <t>Defaults to Available if blank</t>
+          <t>For raw cards only — leave blank for graded slabs</t>
         </is>
       </c>
     </row>
     <row r="19" ht="29" customHeight="1">
       <c r="A19" s="61" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="B19" s="62" t="inlineStr">
@@ -19448,7 +19577,7 @@
       </c>
       <c r="C19" s="61" t="inlineStr">
         <is>
-          <t>Box 3 · Binder A · Case 2 · Front display case</t>
+          <t>Numbers only — no $ or commas. 450 not $450</t>
         </is>
       </c>
       <c r="D19" s="62" t="inlineStr">
@@ -19458,14 +19587,14 @@
       </c>
       <c r="E19" s="61" t="inlineStr">
         <is>
-          <t>Your private reference — buyers never see this</t>
+          <t>Asking price. Leave blank to set after import</t>
         </is>
       </c>
     </row>
     <row r="20" ht="29" customHeight="1">
       <c r="A20" s="59" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="B20" s="60" t="inlineStr">
@@ -19475,7 +19604,7 @@
       </c>
       <c r="C20" s="59" t="inlineStr">
         <is>
-          <t>Your CardShow handle</t>
+          <t>Available (default) · Sold · On Hold</t>
         </is>
       </c>
       <c r="D20" s="60" t="inlineStr">
@@ -19485,14 +19614,14 @@
       </c>
       <c r="E20" s="59" t="inlineStr">
         <is>
-          <t>Auto-filled from your account — safe to leave blank</t>
+          <t>Defaults to Available if blank</t>
         </is>
       </c>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" s="61" t="inlineStr">
         <is>
-          <t>Image URL</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B21" s="62" t="inlineStr">
@@ -19502,7 +19631,7 @@
       </c>
       <c r="C21" s="61" t="inlineStr">
         <is>
-          <t>Full public URL https://cdn.example.com/card.jpg</t>
+          <t>Box 3 · Binder A · Case 2 · Front display case</t>
         </is>
       </c>
       <c r="D21" s="62" t="inlineStr">
@@ -19512,81 +19641,113 @@
       </c>
       <c r="E21" s="61" t="inlineStr">
         <is>
-          <t>Optional card image</t>
+          <t>Your private reference — buyers never see this</t>
         </is>
       </c>
     </row>
     <row r="22" ht="29" customHeight="1">
       <c r="A22" s="59" t="inlineStr">
         <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="59" t="inlineStr">
+        <is>
+          <t>Your CardShow handle</t>
+        </is>
+      </c>
+      <c r="D22" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E22" s="59" t="inlineStr">
+        <is>
+          <t>Auto-filled from your account — safe to leave blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="29" customHeight="1">
+      <c r="A23" s="61" t="inlineStr">
+        <is>
+          <t>Image URL</t>
+        </is>
+      </c>
+      <c r="B23" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>Full public URL https://cdn.example.com/card.jpg</t>
+        </is>
+      </c>
+      <c r="D23" s="62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>Optional card image</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="29" customHeight="1">
+      <c r="A24" s="59" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C22" s="59" t="inlineStr">
+      <c r="C24" s="59" t="inlineStr">
         <is>
           <t>Any internal notes</t>
         </is>
       </c>
-      <c r="D22" s="60" t="inlineStr">
+      <c r="D24" s="60" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E22" s="59" t="inlineStr">
+      <c r="E24" s="59" t="inlineStr">
         <is>
           <t>Private — never shown to buyers or on show pages</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="38" t="n"/>
-      <c r="B23" s="38" t="n"/>
-      <c r="C23" s="38" t="n"/>
-      <c r="D23" s="38" t="n"/>
-      <c r="E23" s="38" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="63" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="38" t="n"/>
+      <c r="B25" s="38" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="38" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>TIPS FOR FAST IMPORT</t>
         </is>
       </c>
-      <c r="B24" s="64" t="n"/>
-      <c r="C24" s="64" t="n"/>
-      <c r="D24" s="64" t="n"/>
-      <c r="E24" s="64" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="65" t="inlineStr">
-        <is>
-          <t>Shopify export? Drag your Shopify CSV directly — CardShow detects it automatically and maps columns including Tags parsing.</t>
-        </is>
-      </c>
-      <c r="B25" s="66" t="n"/>
-      <c r="C25" s="66" t="n"/>
-      <c r="D25" s="66" t="n"/>
-      <c r="E25" s="66" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="65" t="inlineStr">
-        <is>
-          <t>Card Dealer Pro / Flipwise / Ludex users: export to CSV and drag that file — common column names are auto-detected.</t>
-        </is>
-      </c>
-      <c r="B26" s="66" t="n"/>
-      <c r="C26" s="66" t="n"/>
-      <c r="D26" s="66" t="n"/>
-      <c r="E26" s="66" t="n"/>
+      <c r="B26" s="64" t="n"/>
+      <c r="C26" s="64" t="n"/>
+      <c r="D26" s="64" t="n"/>
+      <c r="E26" s="64" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="65" t="inlineStr">
         <is>
-          <t>Sealed product: use Parallel/Variant = Booster Box · ETB · Tin · Blister Pack and leave Grade and Grader blank.</t>
+          <t>Shopify export? Drag your Shopify CSV directly — CardShow detects it automatically and maps columns including Tags parsing.</t>
         </is>
       </c>
       <c r="B27" s="66" t="n"/>
@@ -19597,7 +19758,7 @@
     <row r="28">
       <c r="A28" s="65" t="inlineStr">
         <is>
-          <t>Lots: use Parallel/Variant = Lot and describe the lot contents in Card Title.</t>
+          <t>Card Dealer Pro / Flipwise / Ludex users: export to CSV and drag that file — common column names are auto-detected.</t>
         </is>
       </c>
       <c r="B28" s="66" t="n"/>
@@ -19608,7 +19769,7 @@
     <row r="29">
       <c r="A29" s="65" t="inlineStr">
         <is>
-          <t>Price column: numbers only. Write 450 not $450 — the importer handles currency symbols but plain numbers are safest.</t>
+          <t>Sealed product: use Parallel/Variant = Booster Box · ETB · Tin · Blister Pack and leave Grade and Grader blank.</t>
         </is>
       </c>
       <c r="B29" s="66" t="n"/>
@@ -19619,7 +19780,7 @@
     <row r="30">
       <c r="A30" s="65" t="inlineStr">
         <is>
-          <t>Numbered parallel? Put the checklist card # in Number, the copy number in Serial Number, and the total print run in Print Run Size — e.g. Number=12, Serial Number=043, Print Run Size=99 for a card printed "12" on the front and numbered 043/99.</t>
+          <t>Lots: use Parallel/Variant = Lot and describe the lot contents in Card Title.</t>
         </is>
       </c>
       <c r="B30" s="66" t="n"/>
@@ -19630,7 +19791,7 @@
     <row r="31">
       <c r="A31" s="65" t="inlineStr">
         <is>
-          <t>You can leave most columns blank — only Card Title is required. Fill in more detail later by editing cards in the app.</t>
+          <t>Price column: numbers only. Write 450 not $450 — the importer handles currency symbols but plain numbers are safest.</t>
         </is>
       </c>
       <c r="B31" s="66" t="n"/>
@@ -19639,25 +19800,37 @@
       <c r="E31" s="66" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="n"/>
-      <c r="B32" s="38" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="38" t="n"/>
-      <c r="E32" s="38" t="n"/>
+      <c r="A32" s="65" t="inlineStr">
+        <is>
+          <t>Numbered parallel? Put the checklist card # in Number, the copy number in Serial Number, and the total print run in Print Run Size — e.g. Number=12, Serial Number=043, Print Run Size=99 for a card printed "12" on the front and numbered 043/99.</t>
+        </is>
+      </c>
+      <c r="B32" s="66" t="n"/>
+      <c r="C32" s="66" t="n"/>
+      <c r="D32" s="66" t="n"/>
+      <c r="E32" s="66" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="n"/>
-      <c r="B33" s="38" t="n"/>
-      <c r="C33" s="38" t="n"/>
-      <c r="D33" s="38" t="n"/>
-      <c r="E33" s="38" t="n"/>
+      <c r="A33" s="65" t="inlineStr">
+        <is>
+          <t>Category/Subcategory reference — Sports: Baseball, Basketball, Football, Hockey, Soccer, Golf, Boxing, MMA/UFC, Wrestling, Racing/Motorsports, Tennis, Other Sport  ·  TCG: Pokémon, Magic: The Gathering, Yu-Gi-Oh!, One Piece Card Game, Disney Lorcana, Digimon Card Game, Dragon Ball Super Fusion World, Gundam Card Game, Flesh and Blood, Star Wars Unlimited, Weiss Schwarz, Union Arena, Other TCG  ·  Non-Sport: Marvel, Star Wars, Disney, DC, Star Trek, Other Non-Sport</t>
+        </is>
+      </c>
+      <c r="B33" s="66" t="n"/>
+      <c r="C33" s="66" t="n"/>
+      <c r="D33" s="66" t="n"/>
+      <c r="E33" s="66" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="n"/>
-      <c r="B34" s="38" t="n"/>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="38" t="n"/>
+      <c r="A34" s="65" t="inlineStr">
+        <is>
+          <t>You can leave most columns blank — only Card Title is required. Fill in more detail later by editing cards in the app.</t>
+        </is>
+      </c>
+      <c r="B34" s="66" t="n"/>
+      <c r="C34" s="66" t="n"/>
+      <c r="D34" s="66" t="n"/>
+      <c r="E34" s="66" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="38" t="n"/>
@@ -19701,16 +19874,52 @@
       <c r="D40" s="38" t="n"/>
       <c r="E40" s="38" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="38" t="n"/>
+      <c r="B41" s="38" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="38" t="n"/>
+      <c r="E41" s="38" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="38" t="n"/>
+      <c r="B42" s="38" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="38" t="n"/>
+      <c r="E42" s="38" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="38" t="n"/>
+      <c r="B43" s="38" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="38" t="n"/>
+      <c r="E43" s="38" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="38" t="n"/>
+      <c r="B44" s="38" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="38" t="n"/>
+      <c r="E44" s="38" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="38" t="n"/>
+      <c r="B45" s="38" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="38" t="n"/>
+      <c r="E45" s="38" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
